--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI43"/>
+  <dimension ref="A1:AI46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -618,12 +618,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Newcastle Jets FC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -710,10 +710,10 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
@@ -728,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>46023.39583333334</v>
+        <v>46023.04166666666</v>
       </c>
     </row>
     <row r="3">
@@ -737,12 +737,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,82 +752,82 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Western Sydney Wanderers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Macarthur</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB3" t="n">
         <v>2.15</v>
       </c>
-      <c r="M3" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
@@ -847,7 +847,7 @@
         <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>46023.41666666666</v>
+        <v>46023.20833333334</v>
       </c>
     </row>
     <row r="4">
@@ -856,12 +856,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>46023.5</v>
+        <v>46023.39583333334</v>
       </c>
     </row>
     <row r="5">
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,39 +990,39 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>46023.5</v>
+        <v>46023.41666666666</v>
       </c>
     </row>
     <row r="6">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
-        <v>46023.60416666666</v>
+        <v>46023.5</v>
       </c>
     </row>
     <row r="39">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5131,7 +5131,7 @@
         <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
-        <v>46023.60416666666</v>
+        <v>46023.5</v>
       </c>
     </row>
     <row r="40">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>5.7</v>
+        <v>1.5</v>
       </c>
       <c r="M41" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="N41" t="n">
-        <v>1.55</v>
+        <v>6.2</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5369,7 +5369,7 @@
         <v>0</v>
       </c>
       <c r="AI41" s="3" t="n">
-        <v>46023.70833333334</v>
+        <v>46023.60416666666</v>
       </c>
     </row>
     <row r="42">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N42" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5488,7 +5488,7 @@
         <v>0</v>
       </c>
       <c r="AI42" s="3" t="n">
-        <v>46023.70833333334</v>
+        <v>46023.60416666666</v>
       </c>
     </row>
     <row r="43">
@@ -5608,6 +5608,363 @@
       </c>
       <c r="AI43" s="3" t="n">
         <v>46023.70833333334</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Brentford</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N44" t="n">
+        <v>3</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" s="3" t="n">
+        <v>46023.70833333334</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="M45" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N45" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" s="3" t="n">
+        <v>46023.70833333334</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>JS Kabylie</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>MC Alger</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" s="3" t="n">
+        <v>46023.875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M41" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>6.2</v>
+        <v>3.7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M42" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N42" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="M43" t="n">
-        <v>2.99</v>
+        <v>3.65</v>
       </c>
       <c r="N43" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="O43" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.25</v>
+        <v>5.7</v>
       </c>
       <c r="M44" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="N44" t="n">
-        <v>3</v>
+        <v>1.55</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>5.7</v>
+        <v>2.38</v>
       </c>
       <c r="M45" t="n">
-        <v>4.3</v>
+        <v>2.99</v>
       </c>
       <c r="N45" t="n">
-        <v>1.55</v>
+        <v>2.82</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46023.70833333334</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M41" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N41" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.25</v>
+        <v>5.7</v>
       </c>
       <c r="M43" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="N43" t="n">
-        <v>3</v>
+        <v>1.55</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>5.7</v>
+        <v>2.25</v>
       </c>
       <c r="M44" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="N44" t="n">
-        <v>1.55</v>
+        <v>3</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M41" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>6.2</v>
+        <v>3.7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>5.7</v>
+        <v>2.25</v>
       </c>
       <c r="M43" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="N43" t="n">
-        <v>1.55</v>
+        <v>3</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.25</v>
+        <v>5.7</v>
       </c>
       <c r="M44" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="N44" t="n">
-        <v>3</v>
+        <v>1.55</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M42" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N42" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.25</v>
+        <v>5.7</v>
       </c>
       <c r="M43" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="N43" t="n">
-        <v>3</v>
+        <v>1.55</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>5.7</v>
+        <v>2.25</v>
       </c>
       <c r="M44" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="N44" t="n">
-        <v>1.55</v>
+        <v>3</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>5.7</v>
+        <v>2.25</v>
       </c>
       <c r="M43" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="N43" t="n">
-        <v>1.55</v>
+        <v>3</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.25</v>
+        <v>5.7</v>
       </c>
       <c r="M44" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="N44" t="n">
-        <v>3</v>
+        <v>1.55</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>5.7</v>
+        <v>2.38</v>
       </c>
       <c r="M44" t="n">
-        <v>4.3</v>
+        <v>2.99</v>
       </c>
       <c r="N44" t="n">
-        <v>1.55</v>
+        <v>2.82</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.38</v>
+        <v>5.7</v>
       </c>
       <c r="M45" t="n">
-        <v>2.99</v>
+        <v>4.3</v>
       </c>
       <c r="N45" t="n">
-        <v>2.82</v>
+        <v>1.55</v>
       </c>
       <c r="O45" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46023.70833333334</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.27</v>
+        <v>1.91</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N12" t="n">
-        <v>2.95</v>
+        <v>3.8</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>2.06</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>2.3</v>
+        <v>3.45</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.42</v>
+        <v>2.8</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.06</v>
+        <v>3</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>3.45</v>
+        <v>2.3</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.91</v>
+        <v>2.27</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>3.8</v>
+        <v>2.95</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N19" t="n">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.01</v>
+        <v>2.7</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>3.75</v>
+        <v>2.42</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3</v>
+        <v>2.03</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N21" t="n">
-        <v>2.28</v>
+        <v>3.3</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.55</v>
+        <v>1.7</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="N22" t="n">
-        <v>2.65</v>
+        <v>4.4</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.42</v>
+        <v>1.96</v>
       </c>
       <c r="M25" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.4</v>
+        <v>1.68</v>
       </c>
       <c r="M29" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N29" t="n">
-        <v>2.09</v>
+        <v>4.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.96</v>
+        <v>2.42</v>
       </c>
       <c r="M30" t="n">
         <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>3.75</v>
+        <v>2.7</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.8</v>
+        <v>2.42</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="N31" t="n">
-        <v>2.45</v>
+        <v>3.05</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N34" t="n">
-        <v>2.8</v>
+        <v>2.28</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.03</v>
+        <v>2.22</v>
       </c>
       <c r="M36" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="M43" t="n">
-        <v>3.65</v>
+        <v>2.99</v>
       </c>
       <c r="N43" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q43" t="n">
         <v>3</v>
       </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="M44" t="n">
-        <v>2.99</v>
+        <v>3.65</v>
       </c>
       <c r="N44" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="O44" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46023.70833333334</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N7" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="M9" t="n">
         <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>2.09</v>
+        <v>2.42</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.28</v>
+        <v>2.03</v>
       </c>
       <c r="M11" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="N11" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="M12" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="N12" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="M13" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="N13" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>2.45</v>
+        <v>1.99</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3</v>
+        <v>2.42</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="M19" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>1.92</v>
+        <v>2.28</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.03</v>
+        <v>2.42</v>
       </c>
       <c r="M21" t="n">
-        <v>3.55</v>
+        <v>2.95</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.7</v>
+        <v>2.55</v>
       </c>
       <c r="M22" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>4.4</v>
+        <v>2.65</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="M25" t="n">
         <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.42</v>
+        <v>2.27</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N30" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.42</v>
+        <v>3.85</v>
       </c>
       <c r="M31" t="n">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="N31" t="n">
-        <v>3.05</v>
+        <v>1.92</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="M34" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="M35" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,10 +4705,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="M36" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="N36" t="n">
         <v>3.1</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.43</v>
+        <v>1.7</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N39" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="M7" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N9" t="n">
-        <v>2.42</v>
+        <v>3.8</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.01</v>
+        <v>1.68</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.68</v>
+        <v>2.01</v>
       </c>
       <c r="M23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N23" t="n">
         <v>3.75</v>
-      </c>
-      <c r="N23" t="n">
-        <v>4.6</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.06</v>
+        <v>2.7</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N25" t="n">
-        <v>3.45</v>
+        <v>2.42</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="M43" t="n">
-        <v>2.99</v>
+        <v>3.65</v>
       </c>
       <c r="N43" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="O43" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.25</v>
+        <v>5.7</v>
       </c>
       <c r="M44" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="N44" t="n">
-        <v>3</v>
+        <v>1.55</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>5.7</v>
+        <v>2.38</v>
       </c>
       <c r="M45" t="n">
-        <v>4.3</v>
+        <v>2.99</v>
       </c>
       <c r="N45" t="n">
-        <v>1.55</v>
+        <v>2.82</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46023.70833333334</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="M43" t="n">
-        <v>3.65</v>
+        <v>2.99</v>
       </c>
       <c r="N43" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q43" t="n">
         <v>3</v>
       </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>5.7</v>
+        <v>2.25</v>
       </c>
       <c r="M44" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="N44" t="n">
-        <v>1.55</v>
+        <v>3</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.38</v>
+        <v>5.7</v>
       </c>
       <c r="M45" t="n">
-        <v>2.99</v>
+        <v>4.3</v>
       </c>
       <c r="N45" t="n">
-        <v>2.82</v>
+        <v>1.55</v>
       </c>
       <c r="O45" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46023.70833333334</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.06</v>
+        <v>2.27</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N7" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.03</v>
+        <v>3.85</v>
       </c>
       <c r="M11" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>1.92</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.64</v>
+        <v>2.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>4.9</v>
+        <v>2.45</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.58</v>
+        <v>3.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
-        <v>5.4</v>
+        <v>2.09</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.65</v>
+        <v>2.28</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N14" t="n">
-        <v>2.03</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.45</v>
+        <v>1.64</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>1.99</v>
+        <v>4.9</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>2.28</v>
+        <v>2.03</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.42</v>
+        <v>2.22</v>
       </c>
       <c r="M21" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.96</v>
+        <v>2.7</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>2.42</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="M30" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="M31" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N31" t="n">
-        <v>1.92</v>
+        <v>2.28</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3</v>
+        <v>2.06</v>
       </c>
       <c r="M33" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>2.3</v>
+        <v>3.45</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.8</v>
+        <v>1.91</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N34" t="n">
-        <v>2.45</v>
+        <v>3.8</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="M35" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N35" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.28</v>
+        <v>2.01</v>
       </c>
       <c r="M36" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N36" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="M38" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N38" t="n">
-        <v>2.09</v>
+        <v>4.4</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.7</v>
+        <v>2.42</v>
       </c>
       <c r="M39" t="n">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="N39" t="n">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N40" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.25</v>
+        <v>5.7</v>
       </c>
       <c r="M44" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="N44" t="n">
-        <v>3</v>
+        <v>1.55</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>5.7</v>
+        <v>2.25</v>
       </c>
       <c r="M45" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="N45" t="n">
-        <v>1.55</v>
+        <v>3</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.96</v>
+        <v>2.42</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.27</v>
+        <v>1.7</v>
       </c>
       <c r="M7" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>2.95</v>
+        <v>4.4</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N10" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.85</v>
+        <v>2.42</v>
       </c>
       <c r="M11" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>1.92</v>
+        <v>2.7</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.4</v>
+        <v>2.01</v>
       </c>
       <c r="M13" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.09</v>
+        <v>3.75</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.28</v>
+        <v>1.96</v>
       </c>
       <c r="M14" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.64</v>
+        <v>2.55</v>
       </c>
       <c r="M16" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>4.9</v>
+        <v>2.65</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.65</v>
+        <v>1.91</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>2.03</v>
+        <v>3.8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.22</v>
+        <v>2.8</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.03</v>
+        <v>3.4</v>
       </c>
       <c r="M27" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N27" t="n">
-        <v>3.3</v>
+        <v>2.09</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>1.99</v>
+        <v>2.28</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="M35" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N35" t="n">
-        <v>2.3</v>
+        <v>1.99</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.7</v>
+        <v>2.28</v>
       </c>
       <c r="M38" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="N38" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.42</v>
+        <v>1.64</v>
       </c>
       <c r="M39" t="n">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="N39" t="n">
-        <v>3.05</v>
+        <v>4.9</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N40" t="n">
-        <v>6.2</v>
+        <v>3.7</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M42" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N42" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="M43" t="n">
-        <v>2.99</v>
+        <v>3.65</v>
       </c>
       <c r="N43" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="O43" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>5.7</v>
+        <v>2.38</v>
       </c>
       <c r="M44" t="n">
-        <v>4.3</v>
+        <v>2.99</v>
       </c>
       <c r="N44" t="n">
-        <v>1.55</v>
+        <v>2.82</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.25</v>
+        <v>5.7</v>
       </c>
       <c r="M45" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="N45" t="n">
-        <v>3</v>
+        <v>1.55</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1138,10 +1138,10 @@
         <v>2.42</v>
       </c>
       <c r="M6" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>4.4</v>
+        <v>2.28</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.27</v>
+        <v>2.8</v>
       </c>
       <c r="M10" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N11" t="n">
         <v>2.42</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.7</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.7</v>
+        <v>1.96</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.42</v>
+        <v>3.75</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.01</v>
+        <v>2.22</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.96</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>3.75</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.22</v>
+        <v>2.43</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.55</v>
+        <v>2.06</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>2.65</v>
+        <v>3.45</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N17" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="M18" t="n">
         <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.91</v>
+        <v>3.65</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>3.8</v>
+        <v>2.03</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.65</v>
+        <v>2.27</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>2.03</v>
+        <v>2.95</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.8</v>
+        <v>2.01</v>
       </c>
       <c r="M21" t="n">
         <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>2.45</v>
+        <v>3.75</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.06</v>
+        <v>3.85</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>3.45</v>
+        <v>1.92</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.4</v>
+        <v>1.68</v>
       </c>
       <c r="M27" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N27" t="n">
-        <v>2.09</v>
+        <v>4.6</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3</v>
+        <v>1.58</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="N28" t="n">
-        <v>2.28</v>
+        <v>5.4</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.25</v>
+        <v>5.7</v>
       </c>
       <c r="M43" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="N43" t="n">
-        <v>3</v>
+        <v>1.55</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="M44" t="n">
-        <v>2.99</v>
+        <v>3.65</v>
       </c>
       <c r="N44" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="O44" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>5.7</v>
+        <v>2.38</v>
       </c>
       <c r="M45" t="n">
-        <v>4.3</v>
+        <v>2.99</v>
       </c>
       <c r="N45" t="n">
-        <v>1.55</v>
+        <v>2.82</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46023.70833333334</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="M11" t="n">
         <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>2.42</v>
+        <v>2.09</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N12" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.22</v>
+        <v>3.65</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.1</v>
+        <v>2.03</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>2.01</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>3.75</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.43</v>
+        <v>2.22</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="M16" t="n">
         <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.91</v>
+        <v>2.27</v>
       </c>
       <c r="M17" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>3.8</v>
+        <v>2.95</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.27</v>
+        <v>3.85</v>
       </c>
       <c r="M20" t="n">
         <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>2.95</v>
+        <v>1.92</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.01</v>
+        <v>2.43</v>
       </c>
       <c r="M21" t="n">
         <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.45</v>
+        <v>2.03</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N24" t="n">
-        <v>1.99</v>
+        <v>3.3</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.03</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N25" t="n">
-        <v>3.3</v>
+        <v>2.28</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.58</v>
+        <v>2.42</v>
       </c>
       <c r="M28" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.64</v>
+        <v>2.42</v>
       </c>
       <c r="M34" t="n">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="N34" t="n">
-        <v>4.9</v>
+        <v>3.05</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>5.7</v>
+        <v>2.25</v>
       </c>
       <c r="M43" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="N43" t="n">
-        <v>1.55</v>
+        <v>3</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.25</v>
+        <v>5.7</v>
       </c>
       <c r="M44" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="N44" t="n">
-        <v>3</v>
+        <v>1.55</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.4</v>
+        <v>2.28</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="N11" t="n">
-        <v>2.09</v>
+        <v>3.1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="M12" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="N12" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="M14" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N14" t="n">
         <v>3.3</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.75</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.22</v>
+        <v>2.42</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N15" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.27</v>
+        <v>3</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>2.95</v>
+        <v>2.28</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.85</v>
+        <v>2.8</v>
       </c>
       <c r="M20" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>1.92</v>
+        <v>2.45</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.06</v>
+        <v>2.42</v>
       </c>
       <c r="M23" t="n">
         <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.03</v>
+        <v>2.7</v>
       </c>
       <c r="M24" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>3.3</v>
+        <v>2.42</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="M25" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>2.28</v>
+        <v>1.99</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.28</v>
+        <v>2.55</v>
       </c>
       <c r="M32" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N32" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.58</v>
+        <v>2.01</v>
       </c>
       <c r="M33" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>5.4</v>
+        <v>3.75</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.42</v>
+        <v>3.65</v>
       </c>
       <c r="M34" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>3.05</v>
+        <v>2.03</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="M35" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="N35" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="M36" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N36" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N37" t="n">
-        <v>2.45</v>
+        <v>4.4</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.45</v>
+        <v>2.22</v>
       </c>
       <c r="M38" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N38" t="n">
-        <v>1.99</v>
+        <v>3.1</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="M43" t="n">
-        <v>3.65</v>
+        <v>2.99</v>
       </c>
       <c r="N43" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q43" t="n">
         <v>3</v>
       </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="M45" t="n">
-        <v>2.99</v>
+        <v>3.65</v>
       </c>
       <c r="N45" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="O45" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46023.70833333334</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.28</v>
+        <v>2.43</v>
       </c>
       <c r="M11" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.03</v>
+        <v>2.8</v>
       </c>
       <c r="M14" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.06</v>
+        <v>2.55</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>3.45</v>
+        <v>2.65</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.8</v>
+        <v>3.65</v>
       </c>
       <c r="M20" t="n">
         <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>2.45</v>
+        <v>2.03</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.42</v>
+        <v>3.85</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>2.7</v>
+        <v>1.92</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.7</v>
+        <v>1.68</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N24" t="n">
-        <v>2.42</v>
+        <v>4.6</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.45</v>
+        <v>2.28</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N25" t="n">
-        <v>1.99</v>
+        <v>3.1</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.27</v>
+        <v>3.4</v>
       </c>
       <c r="M29" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N29" t="n">
-        <v>2.95</v>
+        <v>2.09</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.4</v>
+        <v>2.42</v>
       </c>
       <c r="M30" t="n">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="N30" t="n">
-        <v>2.09</v>
+        <v>3.05</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N31" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.55</v>
+        <v>3.45</v>
       </c>
       <c r="M32" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N32" t="n">
-        <v>2.65</v>
+        <v>1.99</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.01</v>
+        <v>2.7</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N33" t="n">
-        <v>3.75</v>
+        <v>2.42</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.65</v>
+        <v>2.03</v>
       </c>
       <c r="M34" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N34" t="n">
         <v>3.3</v>
-      </c>
-      <c r="N34" t="n">
-        <v>2.03</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="M35" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N35" t="n">
-        <v>3.8</v>
+        <v>2.28</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="M37" t="n">
         <v>3.75</v>
       </c>
       <c r="N37" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.22</v>
+        <v>1.7</v>
       </c>
       <c r="M38" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N38" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N40" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="M43" t="n">
-        <v>2.99</v>
+        <v>3.65</v>
       </c>
       <c r="N43" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="O43" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="M45" t="n">
-        <v>3.65</v>
+        <v>2.99</v>
       </c>
       <c r="N45" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O45" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q45" t="n">
         <v>3</v>
       </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46023.70833333334</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.01</v>
+        <v>2.8</v>
       </c>
       <c r="M10" t="n">
         <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>3.75</v>
+        <v>2.45</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.43</v>
+        <v>3.65</v>
       </c>
       <c r="M11" t="n">
         <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>2.8</v>
+        <v>2.03</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.8</v>
+        <v>2.28</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N14" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="M19" t="n">
         <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>2.65</v>
+        <v>2.28</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.65</v>
+        <v>1.96</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>2.03</v>
+        <v>3.75</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.85</v>
+        <v>2.03</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N23" t="n">
-        <v>1.92</v>
+        <v>3.3</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.68</v>
+        <v>2.42</v>
       </c>
       <c r="M24" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.96</v>
+        <v>2.42</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N27" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="M29" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N29" t="n">
-        <v>2.09</v>
+        <v>4.4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.91</v>
+        <v>2.55</v>
       </c>
       <c r="M31" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N31" t="n">
-        <v>3.8</v>
+        <v>2.65</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="M33" t="n">
         <v>3.35</v>
       </c>
       <c r="N33" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.03</v>
+        <v>1.68</v>
       </c>
       <c r="M34" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="N34" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.7</v>
+        <v>3.45</v>
       </c>
       <c r="M38" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="N38" t="n">
-        <v>4.4</v>
+        <v>1.99</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M42" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N42" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.25</v>
+        <v>5.7</v>
       </c>
       <c r="M43" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="N43" t="n">
-        <v>3</v>
+        <v>1.55</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>5.7</v>
+        <v>2.25</v>
       </c>
       <c r="M44" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="N44" t="n">
-        <v>1.55</v>
+        <v>3</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N6" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.06</v>
+        <v>3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N7" t="n">
-        <v>3.45</v>
+        <v>2.3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.43</v>
+        <v>2.8</v>
       </c>
       <c r="M9" t="n">
         <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.8</v>
+        <v>1.96</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>2.45</v>
+        <v>3.75</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="M14" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
         <v>3.1</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.4</v>
+        <v>2.43</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>2.09</v>
+        <v>2.8</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.27</v>
+        <v>3.85</v>
       </c>
       <c r="M18" t="n">
         <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>2.95</v>
+        <v>1.92</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3</v>
+        <v>2.01</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>2.28</v>
+        <v>3.75</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N23" t="n">
         <v>2.03</v>
-      </c>
-      <c r="M23" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.3</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.42</v>
+        <v>1.68</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N24" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="M26" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="N26" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.42</v>
+        <v>2.03</v>
       </c>
       <c r="M27" t="n">
-        <v>2.95</v>
+        <v>3.55</v>
       </c>
       <c r="N27" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="M31" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N31" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3</v>
+        <v>1.58</v>
       </c>
       <c r="M33" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="N33" t="n">
-        <v>2.3</v>
+        <v>5.4</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="M36" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="N36" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M41" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N41" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>5.7</v>
+        <v>2.25</v>
       </c>
       <c r="M43" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="N43" t="n">
-        <v>1.55</v>
+        <v>3</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="M44" t="n">
-        <v>3.65</v>
+        <v>2.99</v>
       </c>
       <c r="N44" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O44" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q44" t="n">
         <v>3</v>
       </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.38</v>
+        <v>5.7</v>
       </c>
       <c r="M45" t="n">
-        <v>2.99</v>
+        <v>4.3</v>
       </c>
       <c r="N45" t="n">
-        <v>2.82</v>
+        <v>1.55</v>
       </c>
       <c r="O45" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46023.70833333334</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N6" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="M7" t="n">
         <v>3.35</v>
       </c>
       <c r="N7" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.27</v>
+        <v>3.85</v>
       </c>
       <c r="M8" t="n">
         <v>3.45</v>
       </c>
       <c r="N8" t="n">
-        <v>2.95</v>
+        <v>1.92</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.22</v>
+        <v>1.91</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="M15" t="n">
         <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.58</v>
+        <v>2.01</v>
       </c>
       <c r="M33" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>5.4</v>
+        <v>3.75</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="M35" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="N35" t="n">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.7</v>
+        <v>3.45</v>
       </c>
       <c r="M36" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="N36" t="n">
-        <v>4.4</v>
+        <v>1.99</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N37" t="n">
-        <v>2.65</v>
+        <v>2.42</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.45</v>
+        <v>2.42</v>
       </c>
       <c r="M38" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="N38" t="n">
-        <v>1.99</v>
+        <v>3.05</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.38</v>
+        <v>5.7</v>
       </c>
       <c r="M44" t="n">
-        <v>2.99</v>
+        <v>4.3</v>
       </c>
       <c r="N44" t="n">
-        <v>2.82</v>
+        <v>1.55</v>
       </c>
       <c r="O44" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>5.7</v>
+        <v>2.38</v>
       </c>
       <c r="M45" t="n">
-        <v>4.3</v>
+        <v>2.99</v>
       </c>
       <c r="N45" t="n">
-        <v>1.55</v>
+        <v>2.82</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46023.70833333334</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>1.96</v>
       </c>
       <c r="M6" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>2.3</v>
+        <v>3.75</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.4</v>
+        <v>2.28</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="N7" t="n">
-        <v>2.09</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.27</v>
+        <v>2.01</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.96</v>
+        <v>2.8</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.75</v>
+        <v>2.45</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="M14" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="N14" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.22</v>
+        <v>3.45</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>3.1</v>
+        <v>1.99</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.8</v>
+        <v>2.27</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N27" t="n">
         <v>2.03</v>
-      </c>
-      <c r="M27" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3.3</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.42</v>
+        <v>1.91</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N28" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.28</v>
+        <v>1.58</v>
       </c>
       <c r="M30" t="n">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="N30" t="n">
-        <v>3.1</v>
+        <v>5.4</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.58</v>
+        <v>2.22</v>
       </c>
       <c r="M32" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>5.4</v>
+        <v>3.1</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.01</v>
+        <v>2.42</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="N33" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="M34" t="n">
         <v>3.75</v>
       </c>
       <c r="N34" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="M35" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="M36" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N36" t="n">
-        <v>1.99</v>
+        <v>2.09</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.42</v>
+        <v>2.03</v>
       </c>
       <c r="M38" t="n">
-        <v>2.95</v>
+        <v>3.55</v>
       </c>
       <c r="N38" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M41" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>6.2</v>
+        <v>3.7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.25</v>
+        <v>5.7</v>
       </c>
       <c r="M43" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="N43" t="n">
-        <v>3</v>
+        <v>1.55</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>5.7</v>
+        <v>2.38</v>
       </c>
       <c r="M44" t="n">
-        <v>4.3</v>
+        <v>2.99</v>
       </c>
       <c r="N44" t="n">
-        <v>1.55</v>
+        <v>2.82</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="M45" t="n">
-        <v>2.99</v>
+        <v>3.65</v>
       </c>
       <c r="N45" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="O45" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46023.70833333334</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.96</v>
+        <v>2.28</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="N6" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.28</v>
+        <v>1.96</v>
       </c>
       <c r="M7" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.68</v>
+        <v>2.7</v>
       </c>
       <c r="M9" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>4.6</v>
+        <v>2.42</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.43</v>
+        <v>3.85</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N11" t="n">
-        <v>2.8</v>
+        <v>1.92</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.01</v>
+        <v>2.22</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.8</v>
+        <v>2.43</v>
       </c>
       <c r="M13" t="n">
         <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.45</v>
+        <v>2.27</v>
       </c>
       <c r="M15" t="n">
         <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>1.99</v>
+        <v>2.95</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.55</v>
+        <v>1.58</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>2.65</v>
+        <v>5.4</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.27</v>
+        <v>3.4</v>
       </c>
       <c r="M20" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>2.95</v>
+        <v>2.09</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="M29" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="M30" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="N30" t="n">
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="M31" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N31" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.42</v>
+        <v>2.8</v>
       </c>
       <c r="M33" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>3.05</v>
+        <v>2.45</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.64</v>
+        <v>2.01</v>
       </c>
       <c r="M34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N34" t="n">
         <v>3.75</v>
-      </c>
-      <c r="N34" t="n">
-        <v>4.9</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4589,10 +4589,10 @@
         <v>2.42</v>
       </c>
       <c r="M35" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N35" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="M36" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N36" t="n">
-        <v>2.09</v>
+        <v>2.28</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N37" t="n">
         <v>2.7</v>
-      </c>
-      <c r="M37" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N37" t="n">
-        <v>2.42</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.03</v>
+        <v>1.64</v>
       </c>
       <c r="M38" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="N38" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3</v>
+        <v>2.03</v>
       </c>
       <c r="M39" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N39" t="n">
-        <v>2.28</v>
+        <v>3.3</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N40" t="n">
-        <v>6.2</v>
+        <v>3.7</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M41" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N41" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>5.7</v>
+        <v>2.25</v>
       </c>
       <c r="M43" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="N43" t="n">
-        <v>1.55</v>
+        <v>3</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.38</v>
+        <v>5.7</v>
       </c>
       <c r="M44" t="n">
-        <v>2.99</v>
+        <v>4.3</v>
       </c>
       <c r="N44" t="n">
-        <v>2.82</v>
+        <v>1.55</v>
       </c>
       <c r="O44" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="M45" t="n">
-        <v>3.65</v>
+        <v>2.99</v>
       </c>
       <c r="N45" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O45" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q45" t="n">
         <v>3</v>
       </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46023.70833333334</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.7</v>
+        <v>2.06</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>2.42</v>
+        <v>3.45</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.06</v>
+        <v>3.85</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N10" t="n">
-        <v>3.45</v>
+        <v>1.92</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.85</v>
+        <v>2.7</v>
       </c>
       <c r="M11" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>1.92</v>
+        <v>2.42</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.43</v>
+        <v>1.7</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>4.4</v>
+        <v>2.09</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.4</v>
+        <v>2.43</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>2.09</v>
+        <v>2.8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.42</v>
+        <v>2.03</v>
       </c>
       <c r="M37" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N37" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.64</v>
+        <v>2.42</v>
       </c>
       <c r="M38" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N38" t="n">
-        <v>4.9</v>
+        <v>2.7</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.03</v>
+        <v>1.64</v>
       </c>
       <c r="M39" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="N39" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N40" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="M43" t="n">
-        <v>3.65</v>
+        <v>2.99</v>
       </c>
       <c r="N43" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q43" t="n">
         <v>3</v>
       </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="M45" t="n">
-        <v>2.99</v>
+        <v>3.65</v>
       </c>
       <c r="N45" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="O45" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46023.70833333334</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.28</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="N6" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="M8" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>1.99</v>
+        <v>2.42</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.06</v>
+        <v>3.45</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N9" t="n">
-        <v>3.45</v>
+        <v>1.99</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.85</v>
+        <v>2.55</v>
       </c>
       <c r="M10" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>1.92</v>
+        <v>2.65</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.22</v>
+        <v>1.58</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>5.4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="M13" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.68</v>
+        <v>2.01</v>
       </c>
       <c r="M17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N17" t="n">
         <v>3.75</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4.6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.58</v>
+        <v>2.22</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>5.4</v>
+        <v>3.1</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.55</v>
+        <v>1.96</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>2.65</v>
+        <v>3.75</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.43</v>
+        <v>3.4</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>2.8</v>
+        <v>2.09</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.8</v>
+        <v>2.06</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>2.45</v>
+        <v>3.45</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.01</v>
+        <v>1.64</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N34" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.42</v>
+        <v>1.68</v>
       </c>
       <c r="M35" t="n">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="N35" t="n">
-        <v>3.05</v>
+        <v>4.6</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="M36" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N36" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.03</v>
+        <v>3.85</v>
       </c>
       <c r="M37" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N37" t="n">
-        <v>3.3</v>
+        <v>1.92</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="M38" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.64</v>
+        <v>3</v>
       </c>
       <c r="M39" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="N39" t="n">
-        <v>4.9</v>
+        <v>2.28</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N40" t="n">
-        <v>6.2</v>
+        <v>3.7</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M42" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N42" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.38</v>
+        <v>5.7</v>
       </c>
       <c r="M43" t="n">
-        <v>2.99</v>
+        <v>4.3</v>
       </c>
       <c r="N43" t="n">
-        <v>2.82</v>
+        <v>1.55</v>
       </c>
       <c r="O43" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>5.7</v>
+        <v>2.38</v>
       </c>
       <c r="M44" t="n">
-        <v>4.3</v>
+        <v>2.99</v>
       </c>
       <c r="N44" t="n">
-        <v>1.55</v>
+        <v>2.82</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46023.70833333334</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -668,46 +668,46 @@
         <v>4.4</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AC2" t="n">
         <v>2.2</v>
@@ -716,16 +716,16 @@
         <v>1.6</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46023.04166666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>2.42</v>
       </c>
       <c r="M6" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N7" t="n">
-        <v>4.4</v>
+        <v>2.42</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N8" t="n">
-        <v>2.42</v>
+        <v>1.99</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.45</v>
+        <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>1.99</v>
+        <v>2.65</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.55</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="N10" t="n">
-        <v>2.65</v>
+        <v>4.4</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.65</v>
+        <v>2.03</v>
       </c>
       <c r="M14" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N14" t="n">
         <v>3.3</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.03</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.22</v>
+        <v>2.01</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.96</v>
+        <v>2.22</v>
       </c>
       <c r="M19" t="n">
         <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.4</v>
+        <v>2.27</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>2.09</v>
+        <v>2.95</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.27</v>
+        <v>1.96</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.42</v>
+        <v>3.4</v>
       </c>
       <c r="M22" t="n">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>3.05</v>
+        <v>2.09</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.28</v>
+        <v>3.65</v>
       </c>
       <c r="M23" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>2.03</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="N24" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.03</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N25" t="n">
-        <v>3.3</v>
+        <v>2.28</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.43</v>
+        <v>2.8</v>
       </c>
       <c r="M38" t="n">
         <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N42" t="n">
-        <v>6.2</v>
+        <v>3.7</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>5.7</v>
+        <v>2.25</v>
       </c>
       <c r="M43" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="N43" t="n">
-        <v>1.55</v>
+        <v>3</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.25</v>
+        <v>5.7</v>
       </c>
       <c r="M45" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="N45" t="n">
-        <v>3</v>
+        <v>1.55</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1138,10 +1138,10 @@
         <v>2.42</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>2.42</v>
+        <v>2.65</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.55</v>
+        <v>1.7</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="N9" t="n">
-        <v>2.65</v>
+        <v>4.4</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="M10" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="N10" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N14" t="n">
         <v>2.03</v>
-      </c>
-      <c r="M14" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>2.3</v>
+        <v>1.99</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
         <v>3.75</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.22</v>
+        <v>3.85</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N19" t="n">
-        <v>3.1</v>
+        <v>1.92</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.27</v>
+        <v>3.4</v>
       </c>
       <c r="M20" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>2.95</v>
+        <v>2.09</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.96</v>
+        <v>2.27</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.4</v>
+        <v>2.28</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="N22" t="n">
-        <v>2.09</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.28</v>
+        <v>2.7</v>
       </c>
       <c r="M24" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>2.42</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>2.42</v>
       </c>
       <c r="M25" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>2.28</v>
+        <v>2.7</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.85</v>
+        <v>1.64</v>
       </c>
       <c r="M37" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="N37" t="n">
-        <v>1.92</v>
+        <v>4.9</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.8</v>
+        <v>2.43</v>
       </c>
       <c r="M38" t="n">
         <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.38</v>
+        <v>5.7</v>
       </c>
       <c r="M44" t="n">
-        <v>2.99</v>
+        <v>4.3</v>
       </c>
       <c r="N44" t="n">
-        <v>2.82</v>
+        <v>1.55</v>
       </c>
       <c r="O44" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>5.7</v>
+        <v>2.38</v>
       </c>
       <c r="M45" t="n">
-        <v>4.3</v>
+        <v>2.99</v>
       </c>
       <c r="N45" t="n">
-        <v>1.55</v>
+        <v>2.82</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46023.70833333334</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="M2" t="n">
         <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="O2" t="n">
         <v>2.15</v>
@@ -710,10 +710,10 @@
         <v>2.57</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AE2" t="n">
         <v>1.45</v>
@@ -784,67 +784,67 @@
         <v>3.8</v>
       </c>
       <c r="N3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46023.20833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.42</v>
+        <v>1.96</v>
       </c>
       <c r="M6" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N7" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>2.01</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>2.3</v>
+        <v>3.75</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.7</v>
+        <v>3.65</v>
       </c>
       <c r="M9" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>4.4</v>
+        <v>2.03</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.58</v>
+        <v>2.27</v>
       </c>
       <c r="M10" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="N10" t="n">
-        <v>5.4</v>
+        <v>2.95</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.91</v>
+        <v>2.22</v>
       </c>
       <c r="M13" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.65</v>
+        <v>1.91</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N14" t="n">
-        <v>2.03</v>
+        <v>3.8</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>1.99</v>
+        <v>2.28</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.01</v>
+        <v>2.42</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.75</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.06</v>
+        <v>2.43</v>
       </c>
       <c r="M33" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="M34" t="n">
         <v>3.75</v>
       </c>
       <c r="N34" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="M35" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N35" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.03</v>
+        <v>3.45</v>
       </c>
       <c r="M36" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N36" t="n">
-        <v>3.3</v>
+        <v>1.99</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.64</v>
+        <v>2.7</v>
       </c>
       <c r="M37" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N37" t="n">
-        <v>4.9</v>
+        <v>2.42</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.43</v>
+        <v>1.64</v>
       </c>
       <c r="M38" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N38" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>2.28</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="N7" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.01</v>
+        <v>1.58</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="N8" t="n">
-        <v>3.75</v>
+        <v>5.4</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.65</v>
+        <v>1.7</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N9" t="n">
-        <v>2.03</v>
+        <v>4.4</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.27</v>
+        <v>3.4</v>
       </c>
       <c r="M10" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>2.95</v>
+        <v>2.09</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>2.09</v>
+        <v>2.65</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.91</v>
+        <v>2.42</v>
       </c>
       <c r="M14" t="n">
-        <v>3.55</v>
+        <v>2.95</v>
       </c>
       <c r="N14" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.03</v>
+        <v>2.8</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="M28" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="N28" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.58</v>
+        <v>2.22</v>
       </c>
       <c r="M29" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>5.4</v>
+        <v>3.1</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.42</v>
+        <v>3.65</v>
       </c>
       <c r="M31" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>3.05</v>
+        <v>2.03</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.06</v>
+        <v>3</v>
       </c>
       <c r="M32" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N32" t="n">
-        <v>3.45</v>
+        <v>2.3</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="M34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N34" t="n">
         <v>3.75</v>
-      </c>
-      <c r="N34" t="n">
-        <v>4.4</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.64</v>
+        <v>2.01</v>
       </c>
       <c r="M38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N38" t="n">
         <v>3.75</v>
-      </c>
-      <c r="N38" t="n">
-        <v>4.9</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M41" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>6.2</v>
+        <v>3.7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M42" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N42" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>5.7</v>
+        <v>2.38</v>
       </c>
       <c r="M44" t="n">
-        <v>4.3</v>
+        <v>2.99</v>
       </c>
       <c r="N44" t="n">
-        <v>1.55</v>
+        <v>2.82</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.38</v>
+        <v>5.7</v>
       </c>
       <c r="M45" t="n">
-        <v>2.99</v>
+        <v>4.3</v>
       </c>
       <c r="N45" t="n">
-        <v>2.82</v>
+        <v>1.55</v>
       </c>
       <c r="O45" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46023.70833333334</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="M2" t="n">
         <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="O2" t="n">
         <v>2.15</v>
@@ -710,10 +710,10 @@
         <v>2.57</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AE2" t="n">
         <v>1.45</v>
@@ -784,7 +784,7 @@
         <v>3.8</v>
       </c>
       <c r="N3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O3" t="n">
         <v>2.32</v>
@@ -823,10 +823,10 @@
         <v>4.47</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AC3" t="n">
         <v>2.63</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.28</v>
+        <v>3.45</v>
       </c>
       <c r="M7" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>1.99</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.58</v>
+        <v>2.55</v>
       </c>
       <c r="M8" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>5.4</v>
+        <v>2.65</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="M9" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>4.4</v>
+        <v>2.42</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N10" t="n">
-        <v>2.09</v>
+        <v>4.4</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.85</v>
+        <v>2.27</v>
       </c>
       <c r="M11" t="n">
         <v>3.45</v>
       </c>
       <c r="N11" t="n">
-        <v>1.92</v>
+        <v>2.95</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.55</v>
+        <v>2.89</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="N12" t="n">
-        <v>2.65</v>
+        <v>2.41</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.42</v>
+        <v>3.4</v>
       </c>
       <c r="M14" t="n">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>3.05</v>
+        <v>2.09</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.45</v>
+        <v>2.28</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>1.99</v>
+        <v>3.1</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.43</v>
+        <v>2.32</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="N19" t="n">
-        <v>2.8</v>
+        <v>3.03</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.06</v>
+        <v>1.68</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.42</v>
+        <v>3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>2.7</v>
+        <v>2.28</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.03</v>
+        <v>1.64</v>
       </c>
       <c r="M22" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="N22" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.68</v>
+        <v>3.85</v>
       </c>
       <c r="M23" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>4.6</v>
+        <v>1.92</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>2.22</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>2.28</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.64</v>
+        <v>2.03</v>
       </c>
       <c r="M25" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="N25" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="M27" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N27" t="n">
-        <v>2.42</v>
+        <v>3.8</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.91</v>
+        <v>3.65</v>
       </c>
       <c r="M28" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>3.8</v>
+        <v>2.03</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.22</v>
+        <v>3</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N29" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.65</v>
+        <v>1.83</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>3.68</v>
       </c>
       <c r="N31" t="n">
-        <v>2.03</v>
+        <v>3.99</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="M32" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N32" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="M34" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
         <v>3.75</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.01</v>
+        <v>1.35</v>
       </c>
       <c r="M38" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="N38" t="n">
-        <v>3.75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,16 +4988,16 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M41" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N41" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="M42" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="N42" t="n">
-        <v>6.2</v>
+        <v>3.81</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -659,19 +659,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="M2" t="n">
         <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="O2" t="n">
         <v>2.15</v>
       </c>
       <c r="P2" t="n">
-        <v>2.67</v>
+        <v>2.51</v>
       </c>
       <c r="Q2" t="n">
         <v>4.2</v>
@@ -686,7 +686,7 @@
         <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="V2" t="n">
         <v>4.2</v>
@@ -710,10 +710,10 @@
         <v>2.57</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AE2" t="n">
         <v>1.45</v>
@@ -722,10 +722,10 @@
         <v>2.62</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46023.04166666666</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="M3" t="n">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="N3" t="n">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="O3" t="n">
         <v>2.32</v>
@@ -796,7 +796,7 @@
         <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S3" t="n">
         <v>3.3</v>
@@ -811,7 +811,7 @@
         <v>5.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X3" t="n">
         <v>1.02</v>
@@ -823,10 +823,10 @@
         <v>4.47</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AC3" t="n">
         <v>2.63</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="M4" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="N4" t="n">
-        <v>3.53</v>
+        <v>3.42</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46023.39583333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB6" t="n">
         <v>1.96</v>
       </c>
-      <c r="M6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46023.5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.45</v>
+        <v>2.55</v>
       </c>
       <c r="M7" t="n">
         <v>3.45</v>
       </c>
       <c r="N7" t="n">
-        <v>1.99</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="M8" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="N8" t="n">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46023.5</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.7</v>
+        <v>2.39</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>3.02</v>
       </c>
       <c r="N9" t="n">
-        <v>2.42</v>
+        <v>3.2</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46023.5</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="M10" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>4.4</v>
+        <v>1.85</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46023.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.27</v>
+        <v>3.6</v>
       </c>
       <c r="M11" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>2.95</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46023.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.89</v>
+        <v>1.49</v>
       </c>
       <c r="M12" t="n">
-        <v>3.23</v>
+        <v>4.15</v>
       </c>
       <c r="N12" t="n">
-        <v>2.41</v>
+        <v>6.6</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.42</v>
+        <v>1.94</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46023.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.09</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46023.5</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.68</v>
+        <v>3.79</v>
       </c>
       <c r="M15" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="N15" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46023.5</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.58</v>
+        <v>3.45</v>
       </c>
       <c r="M16" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>5.4</v>
+        <v>2.02</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46023.5</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.28</v>
+        <v>1.5</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>3.1</v>
+        <v>5.92</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46023.5</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.48</v>
+        <v>1.36</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
-        <v>2.9</v>
+        <v>8.75</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.13</v>
+        <v>1.77</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.65</v>
+        <v>2.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46023.5</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.32</v>
+        <v>2.95</v>
       </c>
       <c r="M19" t="n">
-        <v>3.23</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>3.03</v>
+        <v>2.38</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46023.5</v>
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="N20" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>5.82</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46023.5</v>
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46023.5</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.64</v>
+        <v>2.24</v>
       </c>
       <c r="M22" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.85</v>
+        <v>1.58</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="N23" t="n">
-        <v>1.92</v>
+        <v>5.6</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46023.5</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>3.01</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="M25" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.91</v>
+        <v>2.85</v>
       </c>
       <c r="M27" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N27" t="n">
-        <v>3.8</v>
+        <v>2.49</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.65</v>
+        <v>2.72</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N28" t="n">
-        <v>2.03</v>
+        <v>2.42</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46023.5</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="M29" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46023.5</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.54</v>
+        <v>1.73</v>
       </c>
       <c r="M30" t="n">
-        <v>3.83</v>
+        <v>3.68</v>
       </c>
       <c r="N30" t="n">
-        <v>6.3</v>
+        <v>4.6</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA30" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE30" t="n">
         <v>1.79</v>
       </c>
-      <c r="AB30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46023.5</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.83</v>
+        <v>3.05</v>
       </c>
       <c r="M31" t="n">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="N31" t="n">
-        <v>3.99</v>
+        <v>2.34</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.63</v>
+        <v>1.91</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46023.5</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="M32" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="N32" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.23</v>
+        <v>1.85</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>3.76</v>
       </c>
       <c r="N33" t="n">
-        <v>3.15</v>
+        <v>3.82</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.79</v>
+        <v>2.17</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46023.5</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46023.5</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.42</v>
+        <v>1.67</v>
       </c>
       <c r="M35" t="n">
-        <v>3.4</v>
+        <v>3.82</v>
       </c>
       <c r="N35" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="M36" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N36" t="n">
-        <v>1.81</v>
+        <v>2.7</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.69</v>
+        <v>2.36</v>
       </c>
       <c r="M37" t="n">
-        <v>3.68</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>4.9</v>
+        <v>2.92</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R38" t="n">
         <v>1.35</v>
       </c>
-      <c r="M38" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N38" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46023.5</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N39" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46023.5</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N40" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>6</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V40" t="n">
+        <v>5</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF40" t="n">
         <v>2</v>
       </c>
-      <c r="M40" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N40" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>0</v>
-      </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46023.60416666666</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="M41" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="N41" t="n">
-        <v>6.2</v>
+        <v>3.81</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N42" t="n">
-        <v>3.81</v>
+        <v>3.7</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46023.60416666666</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="M2" t="n">
         <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="O2" t="n">
         <v>2.15</v>
@@ -710,10 +710,10 @@
         <v>2.57</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AE2" t="n">
         <v>1.45</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="M3" t="n">
-        <v>3.76</v>
+        <v>3.8</v>
       </c>
       <c r="N3" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="O3" t="n">
         <v>2.32</v>
@@ -823,10 +823,10 @@
         <v>4.47</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AC3" t="n">
         <v>2.63</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.75</v>
+        <v>3.79</v>
       </c>
       <c r="M6" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="N6" t="n">
-        <v>4.42</v>
+        <v>1.9</v>
       </c>
       <c r="O6" t="n">
-        <v>2.23</v>
+        <v>4.1</v>
       </c>
       <c r="P6" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.7</v>
+        <v>2.45</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="S6" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="T6" t="n">
-        <v>2.56</v>
+        <v>2.85</v>
       </c>
       <c r="U6" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="V6" t="n">
-        <v>5.85</v>
+        <v>7.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.21</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>2.04</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46023.5</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="M7" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N7" t="n">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="M8" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="N8" t="n">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="O8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46023.5</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.39</v>
+        <v>2.72</v>
       </c>
       <c r="M9" t="n">
-        <v>3.02</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O9" t="n">
         <v>3.2</v>
       </c>
-      <c r="O9" t="n">
-        <v>3.12</v>
-      </c>
       <c r="P9" t="n">
-        <v>1.88</v>
+        <v>2.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.04</v>
+        <v>2.95</v>
       </c>
       <c r="R9" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="S9" t="n">
-        <v>2.33</v>
+        <v>2.95</v>
       </c>
       <c r="T9" t="n">
-        <v>3.52</v>
+        <v>2.59</v>
       </c>
       <c r="U9" t="n">
-        <v>1.23</v>
+        <v>1.43</v>
       </c>
       <c r="V9" t="n">
-        <v>9.800000000000001</v>
+        <v>6.15</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.52</v>
+        <v>1.24</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.6</v>
+        <v>1.79</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.43</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.95</v>
+        <v>2.88</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.11</v>
+        <v>1.63</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.65</v>
+        <v>2.14</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46023.5</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.2</v>
+        <v>1.73</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="N10" t="n">
-        <v>1.85</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
-        <v>5.06</v>
+        <v>2.29</v>
       </c>
       <c r="P10" t="n">
-        <v>2.07</v>
+        <v>2.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.41</v>
+        <v>5.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S10" t="n">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="T10" t="n">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="U10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
-        <v>6</v>
+        <v>6.55</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.18</v>
+        <v>2.06</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46023.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.6</v>
+        <v>1.89</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="O11" t="n">
-        <v>3.85</v>
+        <v>2.4</v>
       </c>
       <c r="P11" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.53</v>
+        <v>4.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>2.98</v>
+        <v>2.81</v>
       </c>
       <c r="T11" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="U11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="V11" t="n">
-        <v>6.45</v>
+        <v>6.25</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="AA11" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB11" t="n">
         <v>1.81</v>
       </c>
-      <c r="AB11" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AC11" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.24</v>
+        <v>1.81</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46023.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.49</v>
+        <v>3.45</v>
       </c>
       <c r="M12" t="n">
-        <v>4.15</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>6.6</v>
+        <v>2.02</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA12" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.7</v>
       </c>
-      <c r="AB12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46023.5</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.94</v>
+        <v>1.62</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N13" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.48</v>
+        <v>2.18</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.95</v>
+        <v>5.82</v>
       </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="T13" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U13" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="V13" t="n">
-        <v>6.5</v>
+        <v>6.35</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.76</v>
+        <v>2.06</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46023.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,70 +2087,70 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O14" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P14" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="T14" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="V14" t="n">
-        <v>6.45</v>
+        <v>6.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="AA14" t="n">
         <v>1.94</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
         <v>1.49</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.79</v>
+        <v>1.98</v>
       </c>
       <c r="M15" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>1.9</v>
+        <v>3.65</v>
       </c>
       <c r="O15" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46023.5</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.45</v>
+        <v>2.55</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="N16" t="n">
-        <v>2.02</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46023.5</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="N17" t="n">
-        <v>5.92</v>
+        <v>4.42</v>
       </c>
       <c r="O17" t="n">
-        <v>2.11</v>
+        <v>2.23</v>
       </c>
       <c r="P17" t="n">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.04</v>
+        <v>4.7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>2.89</v>
+        <v>2.98</v>
       </c>
       <c r="T17" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="U17" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="V17" t="n">
-        <v>6.25</v>
+        <v>5.85</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z17" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="AD17" t="n">
         <v>1.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46023.5</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.36</v>
+        <v>2.15</v>
       </c>
       <c r="M18" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>8.75</v>
+        <v>3.25</v>
       </c>
       <c r="O18" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="P18" t="n">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="Q18" t="n">
-        <v>8.25</v>
+        <v>3.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="T18" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="U18" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V18" t="n">
-        <v>6.05</v>
+        <v>6.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.01</v>
+        <v>1.76</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.14</v>
+        <v>1.6</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46023.5</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.95</v>
+        <v>1.49</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>4.15</v>
       </c>
       <c r="N19" t="n">
-        <v>2.38</v>
+        <v>6.6</v>
       </c>
       <c r="O19" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB19" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB19" t="n">
-        <v>1.71</v>
-      </c>
       <c r="AC19" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46023.5</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.62</v>
+        <v>4.2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>5</v>
+        <v>1.85</v>
       </c>
       <c r="O20" t="n">
-        <v>2.18</v>
+        <v>5.06</v>
       </c>
       <c r="P20" t="n">
-        <v>2.33</v>
+        <v>2.07</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.82</v>
+        <v>2.41</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S20" t="n">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="T20" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="U20" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="V20" t="n">
-        <v>6.35</v>
+        <v>6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.42</v>
+        <v>3.9</v>
       </c>
       <c r="AA20" t="n">
         <v>1.83</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC20" t="n">
         <v>3.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.06</v>
+        <v>1.18</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46023.5</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.25</v>
+        <v>2.31</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>2.15</v>
+        <v>3.01</v>
       </c>
       <c r="O21" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46023.5</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.24</v>
+        <v>2.39</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>3.02</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.85</v>
+        <v>1.43</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46023.5</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.58</v>
+        <v>2.36</v>
       </c>
       <c r="M23" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>5.6</v>
+        <v>2.92</v>
       </c>
       <c r="O23" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.01</v>
+        <v>1.75</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46023.5</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.31</v>
+        <v>1.98</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>3.01</v>
+        <v>3.8</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>3.65</v>
+        <v>2.8</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.35</v>
+        <v>1.94</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.57</v>
+        <v>1.86</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46023.5</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.98</v>
+        <v>1.5</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N26" t="n">
-        <v>3.8</v>
+        <v>5.92</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB26" t="n">
         <v>2</v>
       </c>
-      <c r="AB26" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46023.5</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.85</v>
+        <v>1.58</v>
       </c>
       <c r="M27" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="N27" t="n">
-        <v>2.49</v>
+        <v>5.6</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.75</v>
+        <v>2.01</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46023.5</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.72</v>
+        <v>3.25</v>
       </c>
       <c r="M28" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>2.42</v>
+        <v>2.15</v>
       </c>
       <c r="O28" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V28" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z28" t="n">
         <v>3.2</v>
       </c>
-      <c r="P28" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V28" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y28" t="n">
+      <c r="AA28" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB28" t="n">
+      <c r="AE28" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF28" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC28" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.14</v>
-      </c>
       <c r="AG28" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46023.5</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,22 +3872,22 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="O29" t="n">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="P29" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="R29" t="n">
         <v>1.35</v>
@@ -3896,13 +3896,13 @@
         <v>2.88</v>
       </c>
       <c r="T29" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U29" t="n">
         <v>1.38</v>
       </c>
       <c r="V29" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="W29" t="n">
         <v>1.07</v>
@@ -3914,31 +3914,31 @@
         <v>1.28</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.76</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.6</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46023.5</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.73</v>
+        <v>2.95</v>
       </c>
       <c r="M30" t="n">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>4.6</v>
+        <v>2.38</v>
       </c>
       <c r="O30" t="n">
-        <v>2.29</v>
+        <v>3.74</v>
       </c>
       <c r="P30" t="n">
-        <v>2.33</v>
+        <v>2.02</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.2</v>
+        <v>3.01</v>
       </c>
       <c r="R30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V30" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH30" t="n">
         <v>1.37</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V30" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>2.06</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46023.5</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="M31" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N31" t="n">
-        <v>2.34</v>
+        <v>2.7</v>
       </c>
       <c r="O31" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46023.5</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="M32" t="n">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="N32" t="n">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46023.5</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.85</v>
+        <v>3.6</v>
       </c>
       <c r="M33" t="n">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>3.82</v>
+        <v>2</v>
       </c>
       <c r="O33" t="n">
-        <v>2.37</v>
+        <v>3.85</v>
       </c>
       <c r="P33" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.37</v>
+        <v>2.53</v>
       </c>
       <c r="R33" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S33" t="n">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="T33" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="U33" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="V33" t="n">
-        <v>5.5</v>
+        <v>6.45</v>
       </c>
       <c r="W33" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X33" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.2</v>
+        <v>3.58</v>
       </c>
       <c r="AA33" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE33" t="n">
         <v>1.67</v>
       </c>
-      <c r="AB33" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AF33" t="n">
-        <v>2.21</v>
+        <v>2.08</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.91</v>
+        <v>1.24</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46023.5</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,34 +4467,34 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.89</v>
+        <v>3.05</v>
       </c>
       <c r="M34" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N34" t="n">
-        <v>3.7</v>
+        <v>2.34</v>
       </c>
       <c r="O34" t="n">
-        <v>2.4</v>
+        <v>3.45</v>
       </c>
       <c r="P34" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="R34" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S34" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="T34" t="n">
         <v>2.65</v>
       </c>
       <c r="U34" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V34" t="n">
         <v>6.25</v>
@@ -4503,37 +4503,37 @@
         <v>1.08</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.81</v>
+        <v>1.33</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46023.5</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.67</v>
+        <v>3.6</v>
       </c>
       <c r="M35" t="n">
-        <v>3.82</v>
+        <v>3.2</v>
       </c>
       <c r="N35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.72</v>
+        <v>2.08</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46023.5</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.6</v>
+        <v>1.36</v>
       </c>
       <c r="M36" t="n">
-        <v>3.35</v>
+        <v>5</v>
       </c>
       <c r="N36" t="n">
-        <v>2.7</v>
+        <v>8.75</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA36" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.8</v>
+        <v>2.01</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46023.5</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.36</v>
+        <v>1.85</v>
       </c>
       <c r="M38" t="n">
-        <v>3.2</v>
+        <v>3.76</v>
       </c>
       <c r="N38" t="n">
-        <v>2.75</v>
+        <v>3.82</v>
       </c>
       <c r="O38" t="n">
-        <v>2.9</v>
+        <v>2.37</v>
       </c>
       <c r="P38" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.25</v>
+        <v>4.37</v>
       </c>
       <c r="R38" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="S38" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="T38" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="U38" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="V38" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="W38" t="n">
         <v>1.07</v>
       </c>
       <c r="X38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.97</v>
+        <v>2.21</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.49</v>
+        <v>1.91</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46023.5</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.6</v>
+        <v>1.67</v>
       </c>
       <c r="M39" t="n">
-        <v>3.2</v>
+        <v>3.82</v>
       </c>
       <c r="N39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB39" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q39" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V39" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AC39" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46023.5</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="M43" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="N43" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q43" t="n">
         <v>3</v>
       </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.38</v>
+        <v>5.7</v>
       </c>
       <c r="M44" t="n">
-        <v>2.99</v>
+        <v>4.3</v>
       </c>
       <c r="N44" t="n">
-        <v>2.82</v>
+        <v>1.55</v>
       </c>
       <c r="O44" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>5.7</v>
+        <v>2.25</v>
       </c>
       <c r="M45" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="N45" t="n">
-        <v>1.55</v>
+        <v>3</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="M4" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="N4" t="n">
-        <v>3.42</v>
+        <v>3.53</v>
       </c>
       <c r="O4" t="n">
         <v>2.7</v>
@@ -912,46 +912,46 @@
         <v>2.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.22</v>
+        <v>3.8</v>
       </c>
       <c r="R4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.4</v>
       </c>
-      <c r="S4" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.36</v>
-      </c>
       <c r="V4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="W4" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
         <v>1.27</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC4" t="n">
         <v>3.55</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE4" t="n">
         <v>1.76</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.79</v>
+        <v>2.65</v>
       </c>
       <c r="M6" t="n">
-        <v>3.55</v>
+        <v>3.11</v>
       </c>
       <c r="N6" t="n">
-        <v>1.9</v>
+        <v>2.37</v>
       </c>
       <c r="O6" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46023.5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.85</v>
+        <v>1.62</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>2.49</v>
+        <v>4.3</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46023.5</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="M8" t="n">
-        <v>3.45</v>
+        <v>3.08</v>
       </c>
       <c r="N8" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA8" t="n">
         <v>1.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46023.5</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.72</v>
+        <v>1.57</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N9" t="n">
-        <v>2.42</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
-        <v>3.2</v>
+        <v>2.18</v>
       </c>
       <c r="P9" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.95</v>
+        <v>5.82</v>
       </c>
       <c r="R9" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="T9" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="U9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>6.15</v>
+        <v>6.3</v>
       </c>
       <c r="W9" t="n">
         <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH9" t="n">
-        <v>1.38</v>
+        <v>2.06</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46023.5</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="M10" t="n">
-        <v>3.68</v>
+        <v>3.07</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>2.86</v>
       </c>
       <c r="O10" t="n">
-        <v>2.29</v>
+        <v>2.9</v>
       </c>
       <c r="P10" t="n">
-        <v>2.33</v>
+        <v>2.02</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="R10" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="S10" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="T10" t="n">
-        <v>2.73</v>
+        <v>2.89</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.38</v>
+        <v>3.12</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.97</v>
+        <v>1.76</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.06</v>
+        <v>1.49</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46023.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.89</v>
+        <v>2.48</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="O11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.87</v>
+        <v>2.13</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46023.5</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.45</v>
+        <v>2.41</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="N12" t="n">
-        <v>2.02</v>
+        <v>2.56</v>
       </c>
       <c r="O12" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46023.5</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="M13" t="n">
-        <v>3.8</v>
+        <v>2.99</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="O13" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.82</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.83</v>
+        <v>2.27</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>1.56</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46023.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="N14" t="n">
-        <v>2.75</v>
+        <v>3.03</v>
       </c>
       <c r="O14" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P14" t="n">
-        <v>2.16</v>
+        <v>1.86</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="R14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.35</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH14" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46023.5</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="N15" t="n">
-        <v>3.65</v>
+        <v>3.87</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.35</v>
+        <v>1.86</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.57</v>
+        <v>1.84</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46023.5</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="M16" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>2.41</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46023.5</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,22 +2444,22 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.75</v>
+        <v>3.4</v>
       </c>
       <c r="M17" t="n">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="N17" t="n">
-        <v>4.42</v>
+        <v>1.92</v>
       </c>
       <c r="O17" t="n">
-        <v>2.23</v>
+        <v>3.85</v>
       </c>
       <c r="P17" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.7</v>
+        <v>2.52</v>
       </c>
       <c r="R17" t="n">
         <v>1.33</v>
@@ -2468,49 +2468,49 @@
         <v>2.98</v>
       </c>
       <c r="T17" t="n">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="U17" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V17" t="n">
-        <v>5.85</v>
+        <v>6.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA17" t="n">
         <v>1.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.04</v>
+        <v>1.24</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46023.5</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>3.57</v>
       </c>
       <c r="N18" t="n">
-        <v>3.25</v>
+        <v>5.1</v>
       </c>
       <c r="O18" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S18" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="T18" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="U18" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.6</v>
+        <v>2.04</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46023.5</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.49</v>
+        <v>2.84</v>
       </c>
       <c r="M19" t="n">
-        <v>4.15</v>
+        <v>3.13</v>
       </c>
       <c r="N19" t="n">
-        <v>6.6</v>
+        <v>2.23</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46023.5</v>
@@ -2804,13 +2804,13 @@
         <v>4.2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N20" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="O20" t="n">
-        <v>5.06</v>
+        <v>4.9</v>
       </c>
       <c r="P20" t="n">
         <v>2.07</v>
@@ -2819,16 +2819,16 @@
         <v>2.41</v>
       </c>
       <c r="R20" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="T20" t="n">
         <v>2.55</v>
       </c>
       <c r="U20" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="V20" t="n">
         <v>6</v>
@@ -2840,16 +2840,16 @@
         <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.9</v>
+        <v>3.44</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC20" t="n">
         <v>3.1</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.31</v>
+        <v>1.35</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>4.7</v>
       </c>
       <c r="N21" t="n">
-        <v>3.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA21" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE21" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46023.5</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.39</v>
+        <v>1.83</v>
       </c>
       <c r="M22" t="n">
-        <v>3.02</v>
+        <v>3.68</v>
       </c>
       <c r="N22" t="n">
-        <v>3.2</v>
+        <v>3.99</v>
       </c>
       <c r="O22" t="n">
-        <v>3.12</v>
+        <v>2.37</v>
       </c>
       <c r="P22" t="n">
-        <v>1.88</v>
+        <v>2.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.04</v>
+        <v>4.42</v>
       </c>
       <c r="R22" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>2.33</v>
+        <v>3.22</v>
       </c>
       <c r="T22" t="n">
-        <v>3.52</v>
+        <v>2.47</v>
       </c>
       <c r="U22" t="n">
-        <v>1.23</v>
+        <v>1.48</v>
       </c>
       <c r="V22" t="n">
-        <v>9.800000000000001</v>
+        <v>5.95</v>
       </c>
       <c r="W22" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.52</v>
+        <v>1.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.6</v>
+        <v>1.63</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.43</v>
+        <v>2.15</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.95</v>
+        <v>2.61</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.11</v>
+        <v>1.39</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.11</v>
+        <v>1.61</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.65</v>
+        <v>2.14</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.53</v>
+        <v>1.92</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46023.5</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.36</v>
+        <v>2.89</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="N23" t="n">
-        <v>2.92</v>
+        <v>2.41</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AA23" t="n">
         <v>2.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46023.5</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.98</v>
+        <v>2.23</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.45</v>
+        <v>1.69</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>3.68</v>
       </c>
       <c r="N25" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="O25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46023.5</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.5</v>
+        <v>3.39</v>
       </c>
       <c r="M26" t="n">
-        <v>4.2</v>
+        <v>3.23</v>
       </c>
       <c r="N26" t="n">
-        <v>5.92</v>
+        <v>1.94</v>
       </c>
       <c r="O26" t="n">
-        <v>2.11</v>
+        <v>4.22</v>
       </c>
       <c r="P26" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="Q26" t="n">
-        <v>6.04</v>
+        <v>2.62</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S26" t="n">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="T26" t="n">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="U26" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="V26" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="W26" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X26" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z26" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="AB26" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF26" t="n">
         <v>2</v>
       </c>
-      <c r="AC26" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AG26" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.4</v>
+        <v>1.27</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46023.5</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.58</v>
+        <v>2.17</v>
       </c>
       <c r="M27" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="N27" t="n">
-        <v>5.6</v>
+        <v>2.97</v>
       </c>
       <c r="O27" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.76</v>
+        <v>2.07</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.01</v>
+        <v>1.67</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46023.5</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="M28" t="n">
         <v>3.25</v>
       </c>
-      <c r="M28" t="n">
-        <v>3.45</v>
-      </c>
       <c r="N28" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="O28" t="n">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="P28" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.76</v>
+        <v>2.45</v>
       </c>
       <c r="R28" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="S28" t="n">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="T28" t="n">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="U28" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="V28" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="W28" t="n">
         <v>1.03</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG28" t="n">
         <v>1.26</v>
       </c>
-      <c r="Z28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH28" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46023.5</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
         <v>1.94</v>
       </c>
-      <c r="M29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AB29" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46023.5</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.95</v>
+        <v>1.92</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>3.21</v>
       </c>
       <c r="N30" t="n">
-        <v>2.38</v>
+        <v>3.47</v>
       </c>
       <c r="O30" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46023.5</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.6</v>
+        <v>1.53</v>
       </c>
       <c r="M31" t="n">
-        <v>3.35</v>
+        <v>3.87</v>
       </c>
       <c r="N31" t="n">
-        <v>2.7</v>
+        <v>4.75</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA31" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.8</v>
+        <v>2.01</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46023.5</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.56</v>
+        <v>2.32</v>
       </c>
       <c r="M32" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="N32" t="n">
-        <v>2.61</v>
+        <v>3.03</v>
       </c>
       <c r="O32" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P32" t="n">
         <v>2.04</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="R32" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S32" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="T32" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="U32" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="V32" t="n">
-        <v>7.5</v>
+        <v>6.45</v>
       </c>
       <c r="W32" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X32" t="n">
         <v>1.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.14</v>
+        <v>3.24</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.42</v>
+        <v>3.05</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46023.5</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.6</v>
+        <v>2.97</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="N33" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="O33" t="n">
-        <v>3.85</v>
+        <v>4.01</v>
       </c>
       <c r="P33" t="n">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="R33" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S33" t="n">
-        <v>2.98</v>
+        <v>2.77</v>
       </c>
       <c r="T33" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="U33" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="V33" t="n">
-        <v>6.45</v>
+        <v>7.2</v>
       </c>
       <c r="W33" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X33" t="n">
         <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46023.5</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.05</v>
+        <v>2.18</v>
       </c>
       <c r="M34" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="N34" t="n">
-        <v>2.34</v>
+        <v>2.9</v>
       </c>
       <c r="O34" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46023.5</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.6</v>
+        <v>2.27</v>
       </c>
       <c r="M35" t="n">
-        <v>3.2</v>
+        <v>3.03</v>
       </c>
       <c r="N35" t="n">
-        <v>2</v>
+        <v>2.86</v>
       </c>
       <c r="O35" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="P35" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.55</v>
+        <v>3.5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S35" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="T35" t="n">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="U35" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V35" t="n">
-        <v>8.300000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="W35" t="n">
         <v>1.02</v>
       </c>
       <c r="X35" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z35" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.23</v>
+        <v>1.6</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46023.5</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="M36" t="n">
-        <v>5</v>
+        <v>3.13</v>
       </c>
       <c r="N36" t="n">
-        <v>8.75</v>
+        <v>3.66</v>
       </c>
       <c r="O36" t="n">
-        <v>1.83</v>
+        <v>2.48</v>
       </c>
       <c r="P36" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>8.25</v>
+        <v>4.59</v>
       </c>
       <c r="R36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U36" t="n">
         <v>1.34</v>
       </c>
-      <c r="S36" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V36" t="n">
-        <v>6.05</v>
+        <v>6.5</v>
       </c>
       <c r="W36" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X36" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.7</v>
+        <v>3.08</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.77</v>
+        <v>2.01</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.01</v>
+        <v>1.71</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.95</v>
+        <v>3.52</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.66</v>
+        <v>1.87</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AH36" t="n">
-        <v>3.14</v>
+        <v>1.79</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46023.5</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.24</v>
+        <v>1.46</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>3.91</v>
       </c>
       <c r="N37" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="O38" t="n">
+        <v>4</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V38" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE38" t="n">
         <v>1.85</v>
       </c>
-      <c r="M38" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="N38" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="O38" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V38" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AF38" t="n">
-        <v>2.21</v>
+        <v>1.82</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.91</v>
+        <v>1.26</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46023.5</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="M39" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="N39" t="n">
-        <v>5</v>
+        <v>6.3</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46023.5</v>
@@ -5214,7 +5214,7 @@
         <v>5</v>
       </c>
       <c r="W40" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X40" t="n">
         <v>1.01</v>
@@ -5235,7 +5235,7 @@
         <v>2.55</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AE40" t="n">
         <v>1.72</v>
@@ -5244,7 +5244,7 @@
         <v>2</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AH40" t="n">
         <v>2.53</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="M41" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>3.81</v>
+        <v>3.7</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46023.60416666666</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="M42" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N42" t="n">
-        <v>3.7</v>
+        <v>3.81</v>
       </c>
       <c r="O42" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC42" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46023.60416666666</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.35</v>
+        <v>5.7</v>
       </c>
       <c r="M43" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="N43" t="n">
-        <v>2.8</v>
+        <v>1.55</v>
       </c>
       <c r="O43" t="n">
-        <v>3.14</v>
+        <v>4.64</v>
       </c>
       <c r="P43" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q43" t="n">
-        <v>3</v>
+        <v>1.93</v>
       </c>
       <c r="R43" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S43" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="T43" t="n">
-        <v>2.33</v>
+        <v>2.54</v>
       </c>
       <c r="U43" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="V43" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="W43" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X43" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AA43" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF43" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB43" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AC43" t="n">
+      <c r="AG43" t="n">
         <v>2.6</v>
       </c>
-      <c r="AD43" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH43" t="n">
-        <v>1.4</v>
+        <v>1.09</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>5.7</v>
+        <v>2.35</v>
       </c>
       <c r="M44" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="N44" t="n">
-        <v>1.55</v>
+        <v>2.8</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5785,40 +5785,40 @@
         <v>3</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA45" t="n">
         <v>1.87</v>
@@ -5827,22 +5827,22 @@
         <v>1.93</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46023.70833333334</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.65</v>
+        <v>1.92</v>
       </c>
       <c r="M6" t="n">
-        <v>3.11</v>
+        <v>3.21</v>
       </c>
       <c r="N6" t="n">
-        <v>2.37</v>
+        <v>3.47</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.62</v>
+        <v>2.28</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>2.84</v>
       </c>
       <c r="N7" t="n">
-        <v>4.3</v>
+        <v>3.03</v>
       </c>
       <c r="O7" t="n">
-        <v>2.23</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
-        <v>2.38</v>
+        <v>1.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.34</v>
+        <v>1.56</v>
       </c>
       <c r="S7" t="n">
-        <v>2.95</v>
+        <v>2.31</v>
       </c>
       <c r="T7" t="n">
-        <v>2.56</v>
+        <v>3.52</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="V7" t="n">
-        <v>5.85</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.79</v>
+        <v>2.52</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.91</v>
+        <v>1.46</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.73</v>
+        <v>2.11</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.04</v>
+        <v>1.54</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46023.5</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.47</v>
+        <v>1.78</v>
       </c>
       <c r="M8" t="n">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="N8" t="n">
-        <v>2.56</v>
+        <v>3.87</v>
       </c>
       <c r="O8" t="n">
-        <v>3.2</v>
+        <v>2.44</v>
       </c>
       <c r="P8" t="n">
-        <v>2.03</v>
+        <v>2.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.2</v>
+        <v>4.84</v>
       </c>
       <c r="R8" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="T8" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="U8" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="V8" t="n">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.34</v>
+        <v>3.12</v>
       </c>
       <c r="AD8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1.46</v>
+        <v>1.81</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46023.5</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.57</v>
+        <v>2.58</v>
       </c>
       <c r="M9" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>4.6</v>
+        <v>2.41</v>
       </c>
       <c r="O9" t="n">
-        <v>2.18</v>
+        <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.82</v>
+        <v>2.95</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="T9" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="V9" t="n">
-        <v>6.3</v>
+        <v>6.15</v>
       </c>
       <c r="W9" t="n">
         <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.87</v>
+        <v>2.17</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.06</v>
+        <v>1.38</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46023.5</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="M10" t="n">
-        <v>3.07</v>
+        <v>3.28</v>
       </c>
       <c r="N10" t="n">
-        <v>2.86</v>
+        <v>1.92</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9</v>
+        <v>3.85</v>
       </c>
       <c r="P10" t="n">
-        <v>2.02</v>
+        <v>2.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.8</v>
+        <v>2.52</v>
       </c>
       <c r="R10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U10" t="n">
         <v>1.42</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.36</v>
       </c>
       <c r="V10" t="n">
         <v>6.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.12</v>
+        <v>3.58</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46023.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="N11" t="n">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46023.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.41</v>
+        <v>1.62</v>
       </c>
       <c r="M12" t="n">
-        <v>3.18</v>
+        <v>3.75</v>
       </c>
       <c r="N12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T12" t="n">
         <v>2.56</v>
       </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46023.5</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="M13" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S13" t="n">
         <v>2.99</v>
       </c>
-      <c r="N13" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH13" t="n">
         <v>2.27</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46023.5</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.28</v>
+        <v>1.57</v>
       </c>
       <c r="M14" t="n">
-        <v>2.84</v>
+        <v>3.75</v>
       </c>
       <c r="N14" t="n">
-        <v>3.03</v>
+        <v>4.6</v>
       </c>
       <c r="O14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC14" t="n">
         <v>3.1</v>
       </c>
-      <c r="P14" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="V14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AD14" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.11</v>
+        <v>1.83</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.54</v>
+        <v>2.06</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46023.5</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="M15" t="n">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="N15" t="n">
-        <v>3.87</v>
+        <v>4.9</v>
       </c>
       <c r="O15" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46023.5</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.58</v>
+        <v>2.84</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="N16" t="n">
-        <v>2.41</v>
+        <v>2.23</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>3.62</v>
       </c>
       <c r="P16" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="T16" t="n">
-        <v>2.59</v>
+        <v>2.89</v>
       </c>
       <c r="U16" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>6.15</v>
+        <v>6.25</v>
       </c>
       <c r="W16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X16" t="n">
         <v>1.06</v>
       </c>
-      <c r="X16" t="n">
-        <v>1</v>
-      </c>
       <c r="Y16" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46023.5</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="M17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC17" t="n">
         <v>3.28</v>
       </c>
-      <c r="N17" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.92</v>
-      </c>
       <c r="AD17" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46023.5</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.68</v>
+        <v>2.23</v>
       </c>
       <c r="M18" t="n">
-        <v>3.57</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>5.1</v>
+        <v>3.15</v>
       </c>
       <c r="O18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46023.5</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.84</v>
+        <v>2.27</v>
       </c>
       <c r="M19" t="n">
-        <v>3.13</v>
+        <v>3.03</v>
       </c>
       <c r="N19" t="n">
-        <v>2.23</v>
+        <v>2.86</v>
       </c>
       <c r="O19" t="n">
-        <v>3.62</v>
+        <v>2.75</v>
       </c>
       <c r="P19" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="R19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V19" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.27</v>
       </c>
       <c r="Z19" t="n">
         <v>3.3</v>
       </c>
       <c r="AA19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF19" t="n">
         <v>1.94</v>
       </c>
-      <c r="AB19" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD19" t="n">
+      <c r="AG19" t="n">
         <v>1.28</v>
       </c>
-      <c r="AE19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH19" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46023.5</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.2</v>
+        <v>2.17</v>
       </c>
       <c r="M20" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>1.81</v>
+        <v>2.97</v>
       </c>
       <c r="O20" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
         <v>2.07</v>
       </c>
-      <c r="Q20" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V20" t="n">
-        <v>6</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AB20" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46023.5</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="M21" t="n">
-        <v>4.7</v>
+        <v>3.91</v>
       </c>
       <c r="N21" t="n">
-        <v>8.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="O21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46023.5</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.83</v>
+        <v>3.39</v>
       </c>
       <c r="M22" t="n">
-        <v>3.68</v>
+        <v>3.23</v>
       </c>
       <c r="N22" t="n">
-        <v>3.99</v>
+        <v>1.94</v>
       </c>
       <c r="O22" t="n">
-        <v>2.37</v>
+        <v>4.22</v>
       </c>
       <c r="P22" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.42</v>
+        <v>2.62</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>3.22</v>
+        <v>2.81</v>
       </c>
       <c r="T22" t="n">
-        <v>2.47</v>
+        <v>2.81</v>
       </c>
       <c r="U22" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="V22" t="n">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.63</v>
+        <v>1.89</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.15</v>
+        <v>1.81</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.61</v>
+        <v>3.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.92</v>
+        <v>1.27</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46023.5</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.89</v>
+        <v>3.93</v>
       </c>
       <c r="M23" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>2.41</v>
+        <v>1.8</v>
       </c>
       <c r="O23" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="P23" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Q23" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T23" t="n">
         <v>2.99</v>
       </c>
-      <c r="R23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.02</v>
-      </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V23" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W23" t="n">
         <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.89</v>
+        <v>3.15</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.55</v>
+        <v>1.26</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46023.5</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="N24" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.69</v>
+        <v>1.9</v>
       </c>
       <c r="M25" t="n">
-        <v>3.68</v>
+        <v>3.13</v>
       </c>
       <c r="N25" t="n">
-        <v>4.9</v>
+        <v>3.66</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.7</v>
+        <v>2.01</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.05</v>
+        <v>1.71</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46023.5</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.39</v>
+        <v>3.47</v>
       </c>
       <c r="M26" t="n">
-        <v>3.23</v>
+        <v>3.04</v>
       </c>
       <c r="N26" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="O26" t="n">
-        <v>4.22</v>
+        <v>4</v>
       </c>
       <c r="P26" t="n">
-        <v>2.23</v>
+        <v>1.96</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="R26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V26" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y26" t="n">
         <v>1.38</v>
       </c>
-      <c r="S26" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V26" t="n">
-        <v>6</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y26" t="n">
+      <c r="Z26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH26" t="n">
         <v>1.26</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.27</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46023.5</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.17</v>
+        <v>2.65</v>
       </c>
       <c r="M27" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="N27" t="n">
-        <v>2.97</v>
+        <v>2.37</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.93</v>
+        <v>2.48</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N28" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="O28" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46023.5</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3875,46 +3875,46 @@
         <v>2.25</v>
       </c>
       <c r="M29" t="n">
-        <v>3.13</v>
+        <v>3.07</v>
       </c>
       <c r="N29" t="n">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA29" t="n">
         <v>1.94</v>
@@ -3923,22 +3923,22 @@
         <v>1.76</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46023.5</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="M30" t="n">
-        <v>3.21</v>
+        <v>3.13</v>
       </c>
       <c r="N30" t="n">
-        <v>3.47</v>
+        <v>2.81</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.53</v>
+        <v>2.41</v>
       </c>
       <c r="M31" t="n">
-        <v>3.87</v>
+        <v>3.18</v>
       </c>
       <c r="N31" t="n">
-        <v>4.75</v>
+        <v>2.56</v>
       </c>
       <c r="O31" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46023.5</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.32</v>
+        <v>1.35</v>
       </c>
       <c r="M32" t="n">
-        <v>3.23</v>
+        <v>4.7</v>
       </c>
       <c r="N32" t="n">
-        <v>3.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O32" t="n">
-        <v>3.1</v>
+        <v>1.83</v>
       </c>
       <c r="P32" t="n">
-        <v>2.04</v>
+        <v>2.34</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.42</v>
+        <v>7</v>
       </c>
       <c r="R32" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S32" t="n">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="T32" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="U32" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="V32" t="n">
-        <v>6.45</v>
+        <v>5.8</v>
       </c>
       <c r="W32" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X32" t="n">
         <v>1.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.24</v>
+        <v>3.7</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC32" t="n">
         <v>3.05</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.06</v>
+        <v>1.66</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.49</v>
+        <v>3.14</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46023.5</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.97</v>
+        <v>1.68</v>
       </c>
       <c r="M33" t="n">
-        <v>3.15</v>
+        <v>3.57</v>
       </c>
       <c r="N33" t="n">
-        <v>2.15</v>
+        <v>5.1</v>
       </c>
       <c r="O33" t="n">
-        <v>4.01</v>
+        <v>2.3</v>
       </c>
       <c r="P33" t="n">
-        <v>2.05</v>
+        <v>2.32</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="R33" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S33" t="n">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="T33" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="U33" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V33" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="W33" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X33" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AD33" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB33" t="n">
+      <c r="AE33" t="n">
         <v>1.79</v>
       </c>
-      <c r="AC33" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AF33" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.3</v>
+        <v>2.04</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46023.5</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.18</v>
+        <v>4.2</v>
       </c>
       <c r="M34" t="n">
-        <v>3.16</v>
+        <v>3.55</v>
       </c>
       <c r="N34" t="n">
-        <v>2.9</v>
+        <v>1.81</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46023.5</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
         <v>2.27</v>
       </c>
-      <c r="M35" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="N35" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="O35" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V35" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2</v>
-      </c>
       <c r="AB35" t="n">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46023.5</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="M36" t="n">
-        <v>3.13</v>
+        <v>3.68</v>
       </c>
       <c r="N36" t="n">
-        <v>3.66</v>
+        <v>3.99</v>
       </c>
       <c r="O36" t="n">
-        <v>2.48</v>
+        <v>2.37</v>
       </c>
       <c r="P36" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.59</v>
+        <v>4.42</v>
       </c>
       <c r="R36" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S36" t="n">
-        <v>2.65</v>
+        <v>3.22</v>
       </c>
       <c r="T36" t="n">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="U36" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="V36" t="n">
-        <v>6.5</v>
+        <v>5.95</v>
       </c>
       <c r="W36" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.08</v>
+        <v>4.2</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.01</v>
+        <v>1.63</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.71</v>
+        <v>2.15</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.52</v>
+        <v>2.61</v>
       </c>
       <c r="AD36" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AG36" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE36" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH36" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46023.5</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="M37" t="n">
-        <v>3.91</v>
+        <v>3.83</v>
       </c>
       <c r="N37" t="n">
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AB37" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46023.5</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.47</v>
+        <v>2.89</v>
       </c>
       <c r="M38" t="n">
-        <v>3.04</v>
+        <v>3.23</v>
       </c>
       <c r="N38" t="n">
-        <v>1.98</v>
+        <v>2.41</v>
       </c>
       <c r="O38" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="P38" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.55</v>
+        <v>2.99</v>
       </c>
       <c r="R38" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S38" t="n">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="T38" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="U38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V38" t="n">
+        <v>7</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y38" t="n">
         <v>1.32</v>
       </c>
-      <c r="V38" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.38</v>
-      </c>
       <c r="Z38" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46023.5</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.54</v>
+        <v>2.32</v>
       </c>
       <c r="M39" t="n">
-        <v>3.83</v>
+        <v>3.23</v>
       </c>
       <c r="N39" t="n">
-        <v>6.3</v>
+        <v>3.03</v>
       </c>
       <c r="O39" t="n">
-        <v>2.11</v>
+        <v>3.1</v>
       </c>
       <c r="P39" t="n">
-        <v>2.19</v>
+        <v>2.04</v>
       </c>
       <c r="Q39" t="n">
-        <v>6.04</v>
+        <v>3.42</v>
       </c>
       <c r="R39" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S39" t="n">
-        <v>2.89</v>
+        <v>2.73</v>
       </c>
       <c r="T39" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="U39" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="V39" t="n">
-        <v>6.25</v>
+        <v>6.45</v>
       </c>
       <c r="W39" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X39" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.54</v>
+        <v>3.24</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.4</v>
+        <v>1.49</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46023.5</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N40" t="n">
-        <v>6.2</v>
+        <v>3.7</v>
       </c>
       <c r="O40" t="n">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="P40" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="Q40" t="n">
-        <v>6</v>
+        <v>4.23</v>
       </c>
       <c r="R40" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V40" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AD40" t="n">
         <v>1.3</v>
       </c>
-      <c r="S40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V40" t="n">
-        <v>5</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AE40" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AF40" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AH40" t="n">
-        <v>2.53</v>
+        <v>1.75</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46023.60416666666</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M41" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N41" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>6</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V41" t="n">
+        <v>5</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF41" t="n">
         <v>2</v>
       </c>
-      <c r="M41" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N41" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O41" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P41" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V41" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AG41" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.75</v>
+        <v>2.53</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46023.60416666666</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>5.7</v>
+        <v>2.25</v>
       </c>
       <c r="M43" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="N43" t="n">
-        <v>1.55</v>
+        <v>3</v>
       </c>
       <c r="O43" t="n">
-        <v>4.64</v>
+        <v>2.92</v>
       </c>
       <c r="P43" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.93</v>
+        <v>3.6</v>
       </c>
       <c r="R43" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S43" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="T43" t="n">
-        <v>2.54</v>
+        <v>2.65</v>
       </c>
       <c r="U43" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="V43" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="W43" t="n">
         <v>1.09</v>
       </c>
       <c r="X43" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="Z43" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.61</v>
+        <v>3.14</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.6</v>
+        <v>1.42</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.09</v>
+        <v>1.67</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.35</v>
+        <v>5.7</v>
       </c>
       <c r="M44" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="N44" t="n">
-        <v>2.8</v>
+        <v>1.55</v>
       </c>
       <c r="O44" t="n">
-        <v>3.14</v>
+        <v>4.64</v>
       </c>
       <c r="P44" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
+        <v>1.93</v>
       </c>
       <c r="R44" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S44" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="T44" t="n">
-        <v>2.33</v>
+        <v>2.54</v>
       </c>
       <c r="U44" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="V44" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="W44" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X44" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AA44" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF44" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB44" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AC44" t="n">
+      <c r="AG44" t="n">
         <v>2.6</v>
       </c>
-      <c r="AD44" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH44" t="n">
-        <v>1.4</v>
+        <v>1.09</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="M45" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="N45" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="O45" t="n">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="P45" t="n">
         <v>2.2</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="R45" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="T45" t="n">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="U45" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="V45" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="W45" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X45" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.14</v>
+        <v>2.6</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46023.70833333334</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -686,10 +686,10 @@
         <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="V2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="W2" t="n">
         <v>1.15</v>
@@ -698,16 +698,16 @@
         <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.55</v>
+        <v>5.65</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="AC2" t="n">
         <v>2.2</v>
@@ -716,7 +716,7 @@
         <v>1.6</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AF2" t="n">
         <v>2.62</v>
@@ -808,7 +808,7 @@
         <v>1.53</v>
       </c>
       <c r="V3" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="W3" t="n">
         <v>1.1</v>
@@ -817,10 +817,10 @@
         <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.47</v>
+        <v>4.36</v>
       </c>
       <c r="AA3" t="n">
         <v>1.63</v>
@@ -841,7 +841,7 @@
         <v>2.26</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH3" t="n">
         <v>1.94</v>
@@ -912,31 +912,31 @@
         <v>2.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.8</v>
+        <v>4.22</v>
       </c>
       <c r="R4" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="S4" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="T4" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
         <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z4" t="n">
         <v>3.25</v>
@@ -957,10 +957,10 @@
         <v>1.76</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH4" t="n">
         <v>1.7</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.92</v>
+        <v>1.69</v>
       </c>
       <c r="M6" t="n">
-        <v>3.21</v>
+        <v>3.68</v>
       </c>
       <c r="N6" t="n">
-        <v>3.47</v>
+        <v>4.9</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.28</v>
+        <v>1.92</v>
       </c>
       <c r="M7" t="n">
-        <v>2.84</v>
+        <v>3.21</v>
       </c>
       <c r="N7" t="n">
-        <v>3.03</v>
+        <v>3.47</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.52</v>
+        <v>1.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.46</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46023.5</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="M8" t="n">
-        <v>3.34</v>
+        <v>3.13</v>
       </c>
       <c r="N8" t="n">
-        <v>3.87</v>
+        <v>3.66</v>
       </c>
       <c r="O8" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="P8" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.84</v>
+        <v>4.45</v>
       </c>
       <c r="R8" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="T8" t="n">
-        <v>2.65</v>
+        <v>2.99</v>
       </c>
       <c r="U8" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="V8" t="n">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.26</v>
       </c>
-      <c r="Z8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46023.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.58</v>
+        <v>2.23</v>
       </c>
       <c r="M9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N9" t="n">
         <v>3.15</v>
       </c>
-      <c r="N9" t="n">
-        <v>2.41</v>
-      </c>
       <c r="O9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46023.5</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.4</v>
+        <v>2.84</v>
       </c>
       <c r="M10" t="n">
-        <v>3.28</v>
+        <v>3.13</v>
       </c>
       <c r="N10" t="n">
-        <v>1.92</v>
+        <v>2.23</v>
       </c>
       <c r="O10" t="n">
-        <v>3.85</v>
+        <v>3.62</v>
       </c>
       <c r="P10" t="n">
-        <v>2.33</v>
+        <v>2.04</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.52</v>
+        <v>2.97</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>2.98</v>
+        <v>2.7</v>
       </c>
       <c r="T10" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="U10" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V10" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="AD10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.31</v>
       </c>
-      <c r="AE10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH10" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46023.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="M11" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="N11" t="n">
-        <v>2.56</v>
+        <v>2.86</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="S11" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="T11" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
         <v>1.36</v>
       </c>
       <c r="V11" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46023.5</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="M12" t="n">
-        <v>3.75</v>
+        <v>3.91</v>
       </c>
       <c r="N12" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="O12" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46023.5</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.53</v>
+        <v>2.17</v>
       </c>
       <c r="M13" t="n">
-        <v>3.87</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>4.75</v>
+        <v>2.97</v>
       </c>
       <c r="O13" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.71</v>
+        <v>2.07</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.01</v>
+        <v>1.67</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46023.5</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="M14" t="n">
         <v>3.75</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="O14" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.82</v>
+        <v>4.7</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S14" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="T14" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="U14" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V14" t="n">
-        <v>6.3</v>
+        <v>5.85</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.42</v>
+        <v>3.85</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46023.5</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.69</v>
+        <v>2.48</v>
       </c>
       <c r="M15" t="n">
-        <v>3.68</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>4.9</v>
+        <v>2.9</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.7</v>
+        <v>2.13</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="M16" t="n">
         <v>2.84</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.13</v>
-      </c>
       <c r="N16" t="n">
-        <v>2.23</v>
+        <v>3.03</v>
       </c>
       <c r="O16" t="n">
-        <v>3.62</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="S16" t="n">
-        <v>2.73</v>
+        <v>2.31</v>
       </c>
       <c r="T16" t="n">
-        <v>2.89</v>
+        <v>3.52</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="V16" t="n">
-        <v>6.25</v>
+        <v>11</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
         <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.94</v>
+        <v>2.52</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.76</v>
+        <v>1.46</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.73</v>
+        <v>2.11</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46023.5</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>3.28</v>
       </c>
       <c r="N17" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="O17" t="n">
-        <v>4.01</v>
+        <v>3.85</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>2.33</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>2.77</v>
+        <v>2.98</v>
       </c>
       <c r="T17" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="U17" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="V17" t="n">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.28</v>
+        <v>2.92</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46023.5</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.23</v>
+        <v>2.58</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>3.15</v>
+        <v>2.41</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46023.5</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.27</v>
+        <v>2.97</v>
       </c>
       <c r="M19" t="n">
-        <v>3.03</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>2.86</v>
+        <v>2.15</v>
       </c>
       <c r="O19" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q19" t="n">
         <v>2.75</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.5</v>
-      </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S19" t="n">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="T19" t="n">
-        <v>2.99</v>
+        <v>2.7</v>
       </c>
       <c r="U19" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="V19" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="W19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X19" t="n">
         <v>1.02</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46023.5</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.17</v>
+        <v>1.53</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>3.87</v>
       </c>
       <c r="N20" t="n">
-        <v>2.97</v>
+        <v>4.75</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.07</v>
+        <v>1.71</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.67</v>
+        <v>2.01</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46023.5</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.46</v>
+        <v>2.27</v>
       </c>
       <c r="M21" t="n">
-        <v>3.91</v>
+        <v>3.03</v>
       </c>
       <c r="N21" t="n">
-        <v>5.5</v>
+        <v>2.86</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB21" t="n">
         <v>1.72</v>
       </c>
-      <c r="AB21" t="n">
-        <v>2</v>
-      </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46023.5</v>
@@ -3048,7 +3048,7 @@
         <v>1.94</v>
       </c>
       <c r="O22" t="n">
-        <v>4.22</v>
+        <v>3.85</v>
       </c>
       <c r="P22" t="n">
         <v>2.23</v>
@@ -3066,7 +3066,7 @@
         <v>2.81</v>
       </c>
       <c r="U22" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="V22" t="n">
         <v>6</v>
@@ -3075,13 +3075,13 @@
         <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
         <v>1.26</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AA22" t="n">
         <v>1.89</v>
@@ -3194,7 +3194,7 @@
         <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
         <v>1.3</v>
@@ -3209,16 +3209,16 @@
         <v>1.71</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE23" t="n">
         <v>1.84</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AG23" t="n">
         <v>1.26</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="M25" t="n">
-        <v>3.13</v>
+        <v>3.75</v>
       </c>
       <c r="N25" t="n">
-        <v>3.66</v>
+        <v>4.6</v>
       </c>
       <c r="O25" t="n">
-        <v>2.48</v>
+        <v>2.17</v>
       </c>
       <c r="P25" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.59</v>
+        <v>5.6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="T25" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U25" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="V25" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="W25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X25" t="n">
         <v>1.02</v>
       </c>
-      <c r="X25" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y25" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.08</v>
+        <v>3.42</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.01</v>
+        <v>1.81</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.71</v>
+        <v>1.89</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AF25" t="n">
         <v>1.87</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.79</v>
+        <v>2.06</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46023.5</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.47</v>
+        <v>2.65</v>
       </c>
       <c r="M26" t="n">
-        <v>3.04</v>
+        <v>3.11</v>
       </c>
       <c r="N26" t="n">
-        <v>1.98</v>
+        <v>2.37</v>
       </c>
       <c r="O26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
         <v>1.96</v>
       </c>
-      <c r="Q26" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V26" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AB26" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46023.5</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T27" t="n">
         <v>2.65</v>
       </c>
-      <c r="M27" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46023.5</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="M28" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="N28" t="n">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46023.5</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.25</v>
+        <v>3.47</v>
       </c>
       <c r="M29" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="N29" t="n">
-        <v>2.86</v>
+        <v>1.98</v>
       </c>
       <c r="O29" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="P29" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.8</v>
+        <v>2.55</v>
       </c>
       <c r="R29" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="T29" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="V29" t="n">
-        <v>6.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W29" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="AD29" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.26</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.49</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46023.5</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N31" t="n">
         <v>2.41</v>
       </c>
-      <c r="M31" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2.56</v>
-      </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF31" t="n">
         <v>1.9</v>
       </c>
-      <c r="AB31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46023.5</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.35</v>
+        <v>1.83</v>
       </c>
       <c r="M32" t="n">
-        <v>4.7</v>
+        <v>3.68</v>
       </c>
       <c r="N32" t="n">
-        <v>8.800000000000001</v>
+        <v>3.99</v>
       </c>
       <c r="O32" t="n">
-        <v>1.83</v>
+        <v>2.37</v>
       </c>
       <c r="P32" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="Q32" t="n">
-        <v>7</v>
+        <v>4.42</v>
       </c>
       <c r="R32" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="T32" t="n">
-        <v>2.59</v>
+        <v>2.47</v>
       </c>
       <c r="U32" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="V32" t="n">
-        <v>5.8</v>
+        <v>5.95</v>
       </c>
       <c r="W32" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X32" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.1</v>
+        <v>1.61</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.66</v>
+        <v>2.14</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AH32" t="n">
-        <v>3.14</v>
+        <v>1.92</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46023.5</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.68</v>
+        <v>2.41</v>
       </c>
       <c r="M33" t="n">
-        <v>3.57</v>
+        <v>3.18</v>
       </c>
       <c r="N33" t="n">
-        <v>5.1</v>
+        <v>2.56</v>
       </c>
       <c r="O33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46023.5</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>4.2</v>
+        <v>2.32</v>
       </c>
       <c r="M34" t="n">
-        <v>3.55</v>
+        <v>3.23</v>
       </c>
       <c r="N34" t="n">
-        <v>1.81</v>
+        <v>3.03</v>
       </c>
       <c r="O34" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="P34" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.41</v>
+        <v>3.42</v>
       </c>
       <c r="R34" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S34" t="n">
-        <v>3.2</v>
+        <v>2.73</v>
       </c>
       <c r="T34" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="U34" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="V34" t="n">
-        <v>6</v>
+        <v>6.45</v>
       </c>
       <c r="W34" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X34" t="n">
         <v>1.03</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.44</v>
+        <v>3.24</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.18</v>
+        <v>1.49</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46023.5</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M35" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N35" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V35" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB35" t="n">
         <v>1.95</v>
       </c>
-      <c r="M35" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="N35" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46023.5</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.83</v>
+        <v>4.2</v>
       </c>
       <c r="M36" t="n">
-        <v>3.68</v>
+        <v>3.55</v>
       </c>
       <c r="N36" t="n">
-        <v>3.99</v>
+        <v>1.81</v>
       </c>
       <c r="O36" t="n">
-        <v>2.37</v>
+        <v>5.06</v>
       </c>
       <c r="P36" t="n">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.42</v>
+        <v>2.43</v>
       </c>
       <c r="R36" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="S36" t="n">
-        <v>3.22</v>
+        <v>2.77</v>
       </c>
       <c r="T36" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="U36" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="V36" t="n">
-        <v>5.95</v>
+        <v>6.25</v>
       </c>
       <c r="W36" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X36" t="n">
         <v>1.03</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="Z36" t="n">
-        <v>4.2</v>
+        <v>3.38</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.61</v>
+        <v>3.1</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.25</v>
+        <v>1.93</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.92</v>
+        <v>1.2</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46023.5</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="M37" t="n">
-        <v>3.83</v>
+        <v>3.57</v>
       </c>
       <c r="N37" t="n">
-        <v>6.3</v>
+        <v>5.1</v>
       </c>
       <c r="O37" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="P37" t="n">
-        <v>2.19</v>
+        <v>2.32</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.04</v>
+        <v>4.4</v>
       </c>
       <c r="R37" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S37" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="T37" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="U37" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="V37" t="n">
-        <v>6.25</v>
+        <v>6.6</v>
       </c>
       <c r="W37" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X37" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.54</v>
+        <v>3.38</v>
       </c>
       <c r="AA37" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE37" t="n">
         <v>1.79</v>
       </c>
-      <c r="AB37" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AF37" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46023.5</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="N38" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O38" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S38" t="n">
         <v>2.89</v>
       </c>
-      <c r="M38" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="N38" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="O38" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.59</v>
-      </c>
       <c r="T38" t="n">
-        <v>3.02</v>
+        <v>2.62</v>
       </c>
       <c r="U38" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V38" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD38" t="n">
         <v>1.33</v>
       </c>
-      <c r="V38" t="n">
-        <v>7</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AE38" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.36</v>
+        <v>2.4</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46023.5</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="M39" t="n">
-        <v>3.23</v>
+        <v>2.99</v>
       </c>
       <c r="N39" t="n">
-        <v>3.03</v>
+        <v>3.65</v>
       </c>
       <c r="O39" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.91</v>
+        <v>2.27</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46023.5</v>
@@ -5190,13 +5190,13 @@
         <v>3.7</v>
       </c>
       <c r="O40" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="P40" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.23</v>
+        <v>4.13</v>
       </c>
       <c r="R40" t="n">
         <v>1.35</v>
@@ -5205,25 +5205,25 @@
         <v>3</v>
       </c>
       <c r="T40" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="U40" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="V40" t="n">
-        <v>6.25</v>
+        <v>6.95</v>
       </c>
       <c r="W40" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X40" t="n">
         <v>1.02</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.61</v>
+        <v>3.26</v>
       </c>
       <c r="AA40" t="n">
         <v>1.9</v>
@@ -5247,7 +5247,7 @@
         <v>1.28</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46023.60416666666</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="M41" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="N41" t="n">
-        <v>6.2</v>
+        <v>3.81</v>
       </c>
       <c r="O41" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46023.60416666666</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="M42" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="N42" t="n">
-        <v>3.81</v>
+        <v>6.2</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46023.60416666666</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="M43" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="N43" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="O43" t="n">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="P43" t="n">
         <v>2.2</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="R43" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="T43" t="n">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="U43" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="V43" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="W43" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X43" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AC43" t="n">
-        <v>3.14</v>
+        <v>2.6</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5666,22 +5666,22 @@
         <v>1.55</v>
       </c>
       <c r="O44" t="n">
-        <v>4.64</v>
+        <v>4.67</v>
       </c>
       <c r="P44" t="n">
         <v>2.4</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="R44" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S44" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="T44" t="n">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="U44" t="n">
         <v>1.53</v>
@@ -5690,16 +5690,16 @@
         <v>5.4</v>
       </c>
       <c r="W44" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X44" t="n">
         <v>1.01</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z44" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA44" t="n">
         <v>1.72</v>
@@ -5708,10 +5708,10 @@
         <v>2.13</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.61</v>
+        <v>2.55</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE44" t="n">
         <v>1.8</v>
@@ -5720,10 +5720,10 @@
         <v>1.95</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.6</v>
+        <v>1.16</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="M45" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="N45" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="O45" t="n">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="P45" t="n">
         <v>2.2</v>
       </c>
       <c r="Q45" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S45" t="n">
         <v>3</v>
       </c>
-      <c r="R45" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S45" t="n">
-        <v>3.16</v>
-      </c>
       <c r="T45" t="n">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="U45" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="V45" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="W45" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X45" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.6</v>
+        <v>3.08</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46023.70833333334</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.69</v>
+        <v>1.92</v>
       </c>
       <c r="M6" t="n">
-        <v>3.68</v>
+        <v>3.21</v>
       </c>
       <c r="N6" t="n">
-        <v>4.9</v>
+        <v>3.47</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.92</v>
+        <v>2.47</v>
       </c>
       <c r="M7" t="n">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.47</v>
+        <v>2.56</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46023.5</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.9</v>
+        <v>2.65</v>
       </c>
       <c r="M8" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="N8" t="n">
-        <v>3.66</v>
+        <v>2.37</v>
       </c>
       <c r="O8" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46023.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.23</v>
+        <v>1.46</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>3.91</v>
       </c>
       <c r="N9" t="n">
-        <v>3.15</v>
+        <v>5.5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.84</v>
+        <v>1.69</v>
       </c>
       <c r="M10" t="n">
-        <v>3.13</v>
+        <v>3.68</v>
       </c>
       <c r="N10" t="n">
-        <v>2.23</v>
+        <v>4.9</v>
       </c>
       <c r="O10" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46023.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="M11" t="n">
-        <v>3.07</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46023.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.46</v>
+        <v>3.93</v>
       </c>
       <c r="M12" t="n">
-        <v>3.91</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>5.5</v>
+        <v>1.8</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.72</v>
+        <v>2.01</v>
       </c>
       <c r="AB12" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46023.5</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.17</v>
+        <v>1.78</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="N13" t="n">
-        <v>2.97</v>
+        <v>3.87</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.07</v>
+        <v>1.86</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46023.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.62</v>
+        <v>2.84</v>
       </c>
       <c r="M14" t="n">
-        <v>3.75</v>
+        <v>3.13</v>
       </c>
       <c r="N14" t="n">
-        <v>4.3</v>
+        <v>2.23</v>
       </c>
       <c r="O14" t="n">
-        <v>2.25</v>
+        <v>3.62</v>
       </c>
       <c r="P14" t="n">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.7</v>
+        <v>2.97</v>
       </c>
       <c r="R14" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="T14" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="U14" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V14" t="n">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE14" t="n">
         <v>1.73</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.04</v>
+        <v>1.36</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46023.5</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="O15" t="n">
         <v>2.48</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46023.5</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.28</v>
+        <v>1.62</v>
       </c>
       <c r="M16" t="n">
-        <v>2.84</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>3.03</v>
+        <v>4.3</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="P16" t="n">
-        <v>1.86</v>
+        <v>2.38</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="R16" t="n">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="S16" t="n">
-        <v>2.31</v>
+        <v>2.95</v>
       </c>
       <c r="T16" t="n">
-        <v>3.52</v>
+        <v>2.56</v>
       </c>
       <c r="U16" t="n">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="V16" t="n">
-        <v>11</v>
+        <v>5.85</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.4</v>
+        <v>3.85</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.52</v>
+        <v>1.79</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.46</v>
+        <v>1.91</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.11</v>
+        <v>1.73</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.54</v>
+        <v>2.04</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46023.5</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="M17" t="n">
-        <v>3.28</v>
+        <v>3.07</v>
       </c>
       <c r="N17" t="n">
-        <v>1.92</v>
+        <v>2.86</v>
       </c>
       <c r="O17" t="n">
-        <v>3.85</v>
+        <v>2.9</v>
       </c>
       <c r="P17" t="n">
-        <v>2.33</v>
+        <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.52</v>
+        <v>3.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>2.98</v>
+        <v>2.65</v>
       </c>
       <c r="T17" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="U17" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
         <v>6.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.7</v>
+        <v>3.12</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46023.5</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.58</v>
+        <v>3.47</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="N18" t="n">
-        <v>2.41</v>
+        <v>1.98</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>2.28</v>
+        <v>1.96</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.9</v>
+        <v>2.53</v>
       </c>
       <c r="T18" t="n">
-        <v>2.59</v>
+        <v>3.1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="V18" t="n">
-        <v>6.15</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.58</v>
+        <v>3</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.78</v>
+        <v>2.08</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.95</v>
+        <v>3.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.16</v>
+        <v>1.82</v>
       </c>
       <c r="AG18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.26</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.38</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46023.5</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.53</v>
+        <v>3.4</v>
       </c>
       <c r="M20" t="n">
-        <v>3.87</v>
+        <v>3.28</v>
       </c>
       <c r="N20" t="n">
-        <v>4.75</v>
+        <v>1.92</v>
       </c>
       <c r="O20" t="n">
-        <v>2.14</v>
+        <v>3.85</v>
       </c>
       <c r="P20" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="Q20" t="n">
-        <v>5</v>
+        <v>2.52</v>
       </c>
       <c r="R20" t="n">
         <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U20" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="V20" t="n">
-        <v>5.55</v>
+        <v>6.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.27</v>
+        <v>1.24</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46023.5</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="M21" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="N21" t="n">
         <v>3.03</v>
       </c>
-      <c r="N21" t="n">
-        <v>2.86</v>
-      </c>
       <c r="O21" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>2.16</v>
+        <v>1.86</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="R21" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="S21" t="n">
-        <v>2.65</v>
+        <v>2.31</v>
       </c>
       <c r="T21" t="n">
-        <v>2.99</v>
+        <v>3.52</v>
       </c>
       <c r="U21" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="V21" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="W21" t="n">
         <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>2</v>
+        <v>2.52</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.72</v>
+        <v>1.46</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.76</v>
+        <v>2.11</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.96</v>
+        <v>1.65</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46023.5</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.39</v>
+        <v>2.48</v>
       </c>
       <c r="M22" t="n">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="O22" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.89</v>
+        <v>2.13</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46023.5</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.93</v>
+        <v>1.57</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="N23" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="O23" t="n">
-        <v>4.1</v>
+        <v>2.17</v>
       </c>
       <c r="P23" t="n">
-        <v>2.05</v>
+        <v>2.33</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.45</v>
+        <v>5.6</v>
       </c>
       <c r="R23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U23" t="n">
         <v>1.42</v>
       </c>
-      <c r="S23" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.34</v>
-      </c>
       <c r="V23" t="n">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z23" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AE23" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.21</v>
+        <v>2.06</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46023.5</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.57</v>
+        <v>3.39</v>
       </c>
       <c r="M25" t="n">
-        <v>3.75</v>
+        <v>3.23</v>
       </c>
       <c r="N25" t="n">
-        <v>4.6</v>
+        <v>1.94</v>
       </c>
       <c r="O25" t="n">
-        <v>2.17</v>
+        <v>3.85</v>
       </c>
       <c r="P25" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.6</v>
+        <v>2.62</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="T25" t="n">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="U25" t="n">
         <v>1.42</v>
       </c>
       <c r="V25" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="W25" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="AA25" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1.81</v>
       </c>
-      <c r="AB25" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AC25" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.06</v>
+        <v>1.27</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46023.5</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.65</v>
+        <v>1.53</v>
       </c>
       <c r="M26" t="n">
-        <v>3.11</v>
+        <v>3.87</v>
       </c>
       <c r="N26" t="n">
-        <v>2.37</v>
+        <v>4.75</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA26" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF26" t="n">
         <v>1.96</v>
       </c>
-      <c r="AB26" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46023.5</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.78</v>
+        <v>2.27</v>
       </c>
       <c r="M27" t="n">
-        <v>3.34</v>
+        <v>3.03</v>
       </c>
       <c r="N27" t="n">
-        <v>3.87</v>
+        <v>2.86</v>
       </c>
       <c r="O27" t="n">
-        <v>2.44</v>
+        <v>2.75</v>
       </c>
       <c r="P27" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.84</v>
+        <v>3.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S27" t="n">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="T27" t="n">
-        <v>2.65</v>
+        <v>2.99</v>
       </c>
       <c r="U27" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="V27" t="n">
-        <v>7.1</v>
+        <v>6.4</v>
       </c>
       <c r="W27" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
         <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46023.5</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.47</v>
+        <v>2.17</v>
       </c>
       <c r="M28" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="N28" t="n">
-        <v>2.56</v>
+        <v>2.97</v>
       </c>
       <c r="O28" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46023.5</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.47</v>
+        <v>2.58</v>
       </c>
       <c r="M29" t="n">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="N29" t="n">
-        <v>1.98</v>
+        <v>2.41</v>
       </c>
       <c r="O29" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="P29" t="n">
-        <v>1.96</v>
+        <v>2.28</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="R29" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S29" t="n">
-        <v>2.53</v>
+        <v>2.9</v>
       </c>
       <c r="T29" t="n">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="U29" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="V29" t="n">
-        <v>8.300000000000001</v>
+        <v>6.15</v>
       </c>
       <c r="W29" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.38</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.26</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46023.5</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.89</v>
+        <v>1.83</v>
       </c>
       <c r="M31" t="n">
-        <v>3.23</v>
+        <v>3.68</v>
       </c>
       <c r="N31" t="n">
-        <v>2.41</v>
+        <v>3.99</v>
       </c>
       <c r="O31" t="n">
-        <v>3.74</v>
+        <v>2.37</v>
       </c>
       <c r="P31" t="n">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.01</v>
+        <v>4.42</v>
       </c>
       <c r="R31" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
-        <v>2.59</v>
+        <v>3.22</v>
       </c>
       <c r="T31" t="n">
-        <v>2.9</v>
+        <v>2.47</v>
       </c>
       <c r="U31" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="V31" t="n">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="W31" t="n">
         <v>1.07</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="Z31" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.85</v>
+        <v>2.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.37</v>
+        <v>1.92</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46023.5</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="M32" t="n">
-        <v>3.68</v>
+        <v>2.99</v>
       </c>
       <c r="N32" t="n">
-        <v>3.99</v>
+        <v>3.65</v>
       </c>
       <c r="O32" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.63</v>
+        <v>2.27</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.15</v>
+        <v>1.56</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46023.5</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.41</v>
+        <v>2.32</v>
       </c>
       <c r="M33" t="n">
-        <v>3.18</v>
+        <v>3.23</v>
       </c>
       <c r="N33" t="n">
-        <v>2.56</v>
+        <v>3.03</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46023.5</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
       <c r="M34" t="n">
-        <v>3.23</v>
+        <v>3.18</v>
       </c>
       <c r="N34" t="n">
-        <v>3.03</v>
+        <v>2.56</v>
       </c>
       <c r="O34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46023.5</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.35</v>
+        <v>1.68</v>
       </c>
       <c r="M35" t="n">
-        <v>4.7</v>
+        <v>3.57</v>
       </c>
       <c r="N35" t="n">
-        <v>8.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="O35" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="P35" t="n">
-        <v>2.55</v>
+        <v>2.32</v>
       </c>
       <c r="Q35" t="n">
-        <v>8.25</v>
+        <v>4.4</v>
       </c>
       <c r="R35" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="S35" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V35" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC35" t="n">
         <v>2.99</v>
       </c>
-      <c r="T35" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V35" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA35" t="n">
+      <c r="AD35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE35" t="n">
         <v>1.79</v>
       </c>
-      <c r="AB35" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AF35" t="n">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AH35" t="n">
-        <v>3.14</v>
+        <v>2.04</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46023.5</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4.2</v>
+        <v>1.35</v>
       </c>
       <c r="M36" t="n">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="N36" t="n">
-        <v>1.81</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O36" t="n">
-        <v>5.06</v>
+        <v>1.83</v>
       </c>
       <c r="P36" t="n">
-        <v>2.06</v>
+        <v>2.55</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.43</v>
+        <v>8.25</v>
       </c>
       <c r="R36" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="S36" t="n">
-        <v>2.77</v>
+        <v>2.99</v>
       </c>
       <c r="T36" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="U36" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="V36" t="n">
-        <v>6.25</v>
+        <v>6.05</v>
       </c>
       <c r="W36" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.38</v>
+        <v>3.7</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.97</v>
+        <v>1.66</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.93</v>
+        <v>1.16</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.2</v>
+        <v>3.14</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46023.5</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.68</v>
+        <v>2.89</v>
       </c>
       <c r="M37" t="n">
-        <v>3.57</v>
+        <v>3.23</v>
       </c>
       <c r="N37" t="n">
-        <v>5.1</v>
+        <v>2.41</v>
       </c>
       <c r="O37" t="n">
-        <v>2.3</v>
+        <v>3.74</v>
       </c>
       <c r="P37" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.4</v>
+        <v>3.01</v>
       </c>
       <c r="R37" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="S37" t="n">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="T37" t="n">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="U37" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V37" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="W37" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X37" t="n">
         <v>1.05</v>
       </c>
       <c r="Y37" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AD37" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z37" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE37" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.04</v>
+        <v>1.37</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46023.5</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.54</v>
+        <v>4.2</v>
       </c>
       <c r="M38" t="n">
-        <v>3.83</v>
+        <v>3.55</v>
       </c>
       <c r="N38" t="n">
-        <v>6.3</v>
+        <v>1.81</v>
       </c>
       <c r="O38" t="n">
-        <v>2.11</v>
+        <v>5.06</v>
       </c>
       <c r="P38" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="Q38" t="n">
-        <v>6.04</v>
+        <v>2.43</v>
       </c>
       <c r="R38" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S38" t="n">
-        <v>2.89</v>
+        <v>2.77</v>
       </c>
       <c r="T38" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="U38" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="V38" t="n">
         <v>6.25</v>
       </c>
       <c r="W38" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.54</v>
+        <v>3.38</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.23</v>
+        <v>1.93</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46023.5</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="N39" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V39" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB39" t="n">
         <v>1.95</v>
       </c>
-      <c r="M39" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="N39" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46023.5</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="M41" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="N41" t="n">
-        <v>3.81</v>
+        <v>6.2</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46023.60416666666</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="M42" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="N42" t="n">
-        <v>6.2</v>
+        <v>3.81</v>
       </c>
       <c r="O42" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46023.60416666666</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="M43" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="N43" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="O43" t="n">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="P43" t="n">
         <v>2.2</v>
       </c>
       <c r="Q43" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S43" t="n">
         <v>3</v>
       </c>
-      <c r="R43" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S43" t="n">
-        <v>3.16</v>
-      </c>
       <c r="T43" t="n">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="U43" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="V43" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="W43" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X43" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.6</v>
+        <v>3.08</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="M45" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="N45" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="O45" t="n">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="P45" t="n">
         <v>2.2</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="R45" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="T45" t="n">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="U45" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="V45" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="W45" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X45" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.08</v>
+        <v>2.6</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46023.70833333334</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -662,10 +662,10 @@
         <v>1.7</v>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="N2" t="n">
-        <v>4.4</v>
+        <v>4.05</v>
       </c>
       <c r="O2" t="n">
         <v>2.15</v>
@@ -677,19 +677,19 @@
         <v>4.2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S2" t="n">
         <v>3.75</v>
       </c>
       <c r="T2" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V2" t="n">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="W2" t="n">
         <v>1.15</v>
@@ -710,16 +710,16 @@
         <v>2.61</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AE2" t="n">
         <v>1.44</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="AG2" t="n">
         <v>1.24</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="M3" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="N3" t="n">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="O3" t="n">
         <v>2.32</v>
@@ -793,7 +793,7 @@
         <v>2.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R3" t="n">
         <v>1.28</v>
@@ -802,7 +802,7 @@
         <v>3.3</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="U3" t="n">
         <v>1.53</v>
@@ -823,10 +823,10 @@
         <v>4.36</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AC3" t="n">
         <v>2.63</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.92</v>
+        <v>2.84</v>
       </c>
       <c r="M6" t="n">
-        <v>3.21</v>
+        <v>3.13</v>
       </c>
       <c r="N6" t="n">
-        <v>3.47</v>
+        <v>2.23</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46023.5</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.47</v>
+        <v>3.4</v>
       </c>
       <c r="M7" t="n">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="N7" t="n">
-        <v>2.56</v>
+        <v>1.92</v>
       </c>
       <c r="O7" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="P7" t="n">
-        <v>2.03</v>
+        <v>2.33</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.2</v>
+        <v>2.52</v>
       </c>
       <c r="R7" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>2.73</v>
+        <v>2.98</v>
       </c>
       <c r="T7" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="U7" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V7" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.27</v>
       </c>
-      <c r="Z7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH7" t="n">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46023.5</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.65</v>
+        <v>2.17</v>
       </c>
       <c r="M8" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.37</v>
+        <v>2.97</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.46</v>
+        <v>2.97</v>
       </c>
       <c r="M9" t="n">
-        <v>3.91</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>5.5</v>
+        <v>2.15</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46023.5</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.69</v>
+        <v>2.23</v>
       </c>
       <c r="M10" t="n">
-        <v>3.68</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>4.9</v>
+        <v>3.15</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.23</v>
+        <v>1.92</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="N11" t="n">
-        <v>3.15</v>
+        <v>3.47</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.93</v>
+        <v>2.48</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="O12" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46023.5</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.78</v>
+        <v>2.47</v>
       </c>
       <c r="M13" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC13" t="n">
         <v>3.34</v>
       </c>
-      <c r="N13" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V13" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AD13" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.81</v>
+        <v>1.46</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46023.5</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.84</v>
+        <v>2.65</v>
       </c>
       <c r="M14" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="N14" t="n">
-        <v>2.23</v>
+        <v>2.37</v>
       </c>
       <c r="O14" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46023.5</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,22 +2206,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="M15" t="n">
-        <v>3.13</v>
+        <v>3.07</v>
       </c>
       <c r="N15" t="n">
-        <v>3.66</v>
+        <v>2.86</v>
       </c>
       <c r="O15" t="n">
-        <v>2.48</v>
+        <v>2.9</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.45</v>
+        <v>3.8</v>
       </c>
       <c r="R15" t="n">
         <v>1.42</v>
@@ -2230,49 +2230,49 @@
         <v>2.65</v>
       </c>
       <c r="T15" t="n">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="U15" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
         <v>6.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.79</v>
+        <v>1.49</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46023.5</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.62</v>
+        <v>3.39</v>
       </c>
       <c r="M16" t="n">
-        <v>3.75</v>
+        <v>3.23</v>
       </c>
       <c r="N16" t="n">
-        <v>4.3</v>
+        <v>1.94</v>
       </c>
       <c r="O16" t="n">
-        <v>2.25</v>
+        <v>3.85</v>
       </c>
       <c r="P16" t="n">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.7</v>
+        <v>2.62</v>
       </c>
       <c r="R16" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="S16" t="n">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="T16" t="n">
-        <v>2.56</v>
+        <v>2.81</v>
       </c>
       <c r="U16" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V16" t="n">
-        <v>5.85</v>
+        <v>6</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.04</v>
+        <v>1.27</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46023.5</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,22 +2444,22 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.25</v>
+        <v>3.93</v>
       </c>
       <c r="M17" t="n">
-        <v>3.07</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>2.86</v>
+        <v>1.8</v>
       </c>
       <c r="O17" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="P17" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.8</v>
+        <v>2.45</v>
       </c>
       <c r="R17" t="n">
         <v>1.42</v>
@@ -2468,49 +2468,49 @@
         <v>2.65</v>
       </c>
       <c r="T17" t="n">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="U17" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="V17" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="W17" t="n">
         <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="AD17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.26</v>
       </c>
-      <c r="AE17" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.49</v>
+        <v>1.21</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46023.5</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.47</v>
+        <v>1.78</v>
       </c>
       <c r="M18" t="n">
-        <v>3.04</v>
+        <v>3.34</v>
       </c>
       <c r="N18" t="n">
-        <v>1.98</v>
+        <v>3.87</v>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>2.44</v>
       </c>
       <c r="P18" t="n">
-        <v>1.96</v>
+        <v>2.23</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.55</v>
+        <v>4.84</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>2.53</v>
+        <v>2.81</v>
       </c>
       <c r="T18" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="U18" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="V18" t="n">
-        <v>8.300000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="Z18" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.08</v>
+        <v>1.86</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.26</v>
+        <v>1.81</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46023.5</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.97</v>
+        <v>2.28</v>
       </c>
       <c r="M19" t="n">
-        <v>3.15</v>
+        <v>2.84</v>
       </c>
       <c r="N19" t="n">
-        <v>2.15</v>
+        <v>3.03</v>
       </c>
       <c r="O19" t="n">
-        <v>4.01</v>
+        <v>3.1</v>
       </c>
       <c r="P19" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.75</v>
+        <v>4.2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="S19" t="n">
-        <v>2.77</v>
+        <v>2.31</v>
       </c>
       <c r="T19" t="n">
-        <v>2.7</v>
+        <v>3.52</v>
       </c>
       <c r="U19" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="V19" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.91</v>
+        <v>2.52</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.79</v>
+        <v>1.46</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.28</v>
+        <v>4.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.74</v>
+        <v>2.11</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46023.5</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.4</v>
+        <v>2.58</v>
       </c>
       <c r="M20" t="n">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V20" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB20" t="n">
         <v>1.92</v>
       </c>
-      <c r="O20" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="R20" t="n">
+      <c r="AC20" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.33</v>
       </c>
-      <c r="S20" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AE20" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46023.5</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.28</v>
+        <v>1.46</v>
       </c>
       <c r="M21" t="n">
-        <v>2.84</v>
+        <v>3.91</v>
       </c>
       <c r="N21" t="n">
-        <v>3.03</v>
+        <v>5.5</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.52</v>
+        <v>1.72</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46023.5</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.48</v>
+        <v>3.47</v>
       </c>
       <c r="M22" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T22" t="n">
         <v>3.1</v>
       </c>
-      <c r="N22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46023.5</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="M23" t="n">
-        <v>3.75</v>
+        <v>3.13</v>
       </c>
       <c r="N23" t="n">
-        <v>4.6</v>
+        <v>3.66</v>
       </c>
       <c r="O23" t="n">
-        <v>2.17</v>
+        <v>2.48</v>
       </c>
       <c r="P23" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.6</v>
+        <v>4.45</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="T23" t="n">
-        <v>2.63</v>
+        <v>2.99</v>
       </c>
       <c r="U23" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="V23" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.81</v>
+        <v>2.01</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.89</v>
+        <v>1.71</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AF23" t="n">
         <v>1.87</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.06</v>
+        <v>1.79</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46023.5</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.18</v>
+        <v>1.62</v>
       </c>
       <c r="M24" t="n">
-        <v>3.16</v>
+        <v>3.75</v>
       </c>
       <c r="N24" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46023.5</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.39</v>
+        <v>1.57</v>
       </c>
       <c r="M25" t="n">
-        <v>3.23</v>
+        <v>3.75</v>
       </c>
       <c r="N25" t="n">
-        <v>1.94</v>
+        <v>4.6</v>
       </c>
       <c r="O25" t="n">
-        <v>3.85</v>
+        <v>2.17</v>
       </c>
       <c r="P25" t="n">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.62</v>
+        <v>5.6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="T25" t="n">
-        <v>2.81</v>
+        <v>2.63</v>
       </c>
       <c r="U25" t="n">
         <v>1.42</v>
       </c>
       <c r="V25" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="W25" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="AA25" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1.89</v>
       </c>
-      <c r="AB25" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AC25" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AF25" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.27</v>
+        <v>2.06</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46023.5</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.53</v>
+        <v>2.18</v>
       </c>
       <c r="M26" t="n">
-        <v>3.87</v>
+        <v>3.16</v>
       </c>
       <c r="N26" t="n">
-        <v>4.75</v>
+        <v>2.9</v>
       </c>
       <c r="O26" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.01</v>
+        <v>1.82</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46023.5</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,61 +3634,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.27</v>
+        <v>1.53</v>
       </c>
       <c r="M27" t="n">
-        <v>3.03</v>
+        <v>3.87</v>
       </c>
       <c r="N27" t="n">
-        <v>2.86</v>
+        <v>4.75</v>
       </c>
       <c r="O27" t="n">
-        <v>2.75</v>
+        <v>2.14</v>
       </c>
       <c r="P27" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>2.65</v>
+        <v>2.99</v>
       </c>
       <c r="T27" t="n">
-        <v>2.99</v>
+        <v>2.5</v>
       </c>
       <c r="U27" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="V27" t="n">
-        <v>6.4</v>
+        <v>5.55</v>
       </c>
       <c r="W27" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.3</v>
+        <v>3.74</v>
       </c>
       <c r="AA27" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.72</v>
+        <v>2.01</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.3</v>
+        <v>2.66</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AE27" t="n">
         <v>1.76</v>
@@ -3697,10 +3697,10 @@
         <v>1.96</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.6</v>
+        <v>2.27</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46023.5</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.17</v>
+        <v>1.69</v>
       </c>
       <c r="M28" t="n">
-        <v>3.1</v>
+        <v>3.68</v>
       </c>
       <c r="N28" t="n">
-        <v>2.97</v>
+        <v>4.9</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.07</v>
+        <v>1.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.58</v>
+        <v>2.27</v>
       </c>
       <c r="M29" t="n">
-        <v>3.15</v>
+        <v>3.03</v>
       </c>
       <c r="N29" t="n">
-        <v>2.41</v>
+        <v>2.86</v>
       </c>
       <c r="O29" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="P29" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="R29" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S29" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="T29" t="n">
-        <v>2.59</v>
+        <v>2.99</v>
       </c>
       <c r="U29" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="V29" t="n">
-        <v>6.15</v>
+        <v>6.4</v>
       </c>
       <c r="W29" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46023.5</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="M31" t="n">
-        <v>3.68</v>
+        <v>3.57</v>
       </c>
       <c r="N31" t="n">
-        <v>3.99</v>
+        <v>5.1</v>
       </c>
       <c r="O31" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="P31" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.42</v>
+        <v>4.4</v>
       </c>
       <c r="R31" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AD31" t="n">
         <v>1.3</v>
       </c>
-      <c r="S31" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V31" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AE31" t="n">
-        <v>1.61</v>
+        <v>1.79</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.14</v>
+        <v>1.92</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46023.5</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="M32" t="n">
-        <v>2.99</v>
+        <v>3.23</v>
       </c>
       <c r="N32" t="n">
-        <v>3.65</v>
+        <v>3.03</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.27</v>
+        <v>1.91</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46023.5</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.32</v>
+        <v>1.83</v>
       </c>
       <c r="M33" t="n">
-        <v>3.23</v>
+        <v>3.68</v>
       </c>
       <c r="N33" t="n">
-        <v>3.03</v>
+        <v>3.99</v>
       </c>
       <c r="O33" t="n">
-        <v>3.1</v>
+        <v>2.37</v>
       </c>
       <c r="P33" t="n">
-        <v>2.04</v>
+        <v>2.24</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.42</v>
+        <v>4.42</v>
       </c>
       <c r="R33" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S33" t="n">
-        <v>2.73</v>
+        <v>3.22</v>
       </c>
       <c r="T33" t="n">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="U33" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="V33" t="n">
-        <v>6.45</v>
+        <v>5.95</v>
       </c>
       <c r="W33" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X33" t="n">
         <v>1.03</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.24</v>
+        <v>4.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.49</v>
+        <v>1.92</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46023.5</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.41</v>
+        <v>1.95</v>
       </c>
       <c r="M34" t="n">
-        <v>3.18</v>
+        <v>2.99</v>
       </c>
       <c r="N34" t="n">
-        <v>2.56</v>
+        <v>3.65</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.9</v>
+        <v>2.27</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.68</v>
+        <v>2.89</v>
       </c>
       <c r="M35" t="n">
-        <v>3.57</v>
+        <v>3.23</v>
       </c>
       <c r="N35" t="n">
-        <v>5.1</v>
+        <v>2.41</v>
       </c>
       <c r="O35" t="n">
-        <v>2.3</v>
+        <v>3.74</v>
       </c>
       <c r="P35" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.4</v>
+        <v>3.01</v>
       </c>
       <c r="R35" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="S35" t="n">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="T35" t="n">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="U35" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V35" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="W35" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X35" t="n">
         <v>1.05</v>
       </c>
       <c r="Y35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AD35" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z35" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE35" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.04</v>
+        <v>1.37</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46023.5</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.35</v>
+        <v>2.41</v>
       </c>
       <c r="M36" t="n">
-        <v>4.7</v>
+        <v>3.18</v>
       </c>
       <c r="N36" t="n">
-        <v>8.800000000000001</v>
+        <v>2.56</v>
       </c>
       <c r="O36" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46023.5</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="N37" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S37" t="n">
         <v>2.89</v>
       </c>
-      <c r="M37" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="N37" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="O37" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.59</v>
-      </c>
       <c r="T37" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="U37" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="V37" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X37" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="Z37" t="n">
-        <v>3</v>
+        <v>3.54</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.85</v>
+        <v>2.95</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.37</v>
+        <v>2.4</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46023.5</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,49 +5062,49 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.54</v>
+        <v>1.35</v>
       </c>
       <c r="M39" t="n">
-        <v>3.83</v>
+        <v>4.7</v>
       </c>
       <c r="N39" t="n">
-        <v>6.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O39" t="n">
-        <v>2.11</v>
+        <v>1.83</v>
       </c>
       <c r="P39" t="n">
-        <v>2.19</v>
+        <v>2.55</v>
       </c>
       <c r="Q39" t="n">
-        <v>6.04</v>
+        <v>8.25</v>
       </c>
       <c r="R39" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S39" t="n">
-        <v>2.89</v>
+        <v>2.99</v>
       </c>
       <c r="T39" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="U39" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="V39" t="n">
-        <v>6.25</v>
+        <v>6.05</v>
       </c>
       <c r="W39" t="n">
         <v>1.06</v>
       </c>
       <c r="X39" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="AA39" t="n">
         <v>1.79</v>
@@ -5113,22 +5113,22 @@
         <v>1.95</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.4</v>
+        <v>3.14</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46023.5</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.25</v>
+        <v>5.7</v>
       </c>
       <c r="M43" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="N43" t="n">
-        <v>3</v>
+        <v>1.55</v>
       </c>
       <c r="O43" t="n">
-        <v>2.92</v>
+        <v>4.67</v>
       </c>
       <c r="P43" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.6</v>
+        <v>1.85</v>
       </c>
       <c r="R43" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="T43" t="n">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
       <c r="U43" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="V43" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="W43" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X43" t="n">
         <v>1.01</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="AC43" t="n">
-        <v>3.08</v>
+        <v>2.55</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.64</v>
+        <v>1.07</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>5.7</v>
+        <v>2.25</v>
       </c>
       <c r="M44" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="N44" t="n">
-        <v>1.55</v>
+        <v>3</v>
       </c>
       <c r="O44" t="n">
-        <v>4.67</v>
+        <v>2.92</v>
       </c>
       <c r="P44" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.85</v>
+        <v>3.6</v>
       </c>
       <c r="R44" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S44" t="n">
-        <v>3.36</v>
+        <v>3</v>
       </c>
       <c r="T44" t="n">
-        <v>2.49</v>
+        <v>2.65</v>
       </c>
       <c r="U44" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="V44" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="W44" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X44" t="n">
         <v>1.01</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="Z44" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.55</v>
+        <v>3.08</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.07</v>
+        <v>1.64</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46023.70833333334</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.84</v>
+        <v>1.92</v>
       </c>
       <c r="M6" t="n">
-        <v>3.13</v>
+        <v>3.21</v>
       </c>
       <c r="N6" t="n">
-        <v>2.23</v>
+        <v>3.47</v>
       </c>
       <c r="O6" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46023.5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="M7" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="N7" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="O7" t="n">
         <v>3.85</v>
       </c>
       <c r="P7" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>2.98</v>
+        <v>2.81</v>
       </c>
       <c r="T7" t="n">
-        <v>2.45</v>
+        <v>2.81</v>
       </c>
       <c r="U7" t="n">
         <v>1.42</v>
       </c>
       <c r="V7" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
         <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AG7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH7" t="n">
         <v>1.27</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.24</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46023.5</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.17</v>
+        <v>1.78</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="N8" t="n">
-        <v>2.97</v>
+        <v>3.87</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.07</v>
+        <v>1.86</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46023.5</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.97</v>
+        <v>1.57</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="N9" t="n">
-        <v>2.15</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
-        <v>4.01</v>
+        <v>2.17</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>2.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.75</v>
+        <v>5.6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="T9" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="U9" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.3</v>
+        <v>2.06</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46023.5</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.23</v>
+        <v>2.58</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
-        <v>3.15</v>
+        <v>2.41</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46023.5</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.92</v>
+        <v>2.28</v>
       </c>
       <c r="M11" t="n">
-        <v>3.21</v>
+        <v>2.84</v>
       </c>
       <c r="N11" t="n">
-        <v>3.47</v>
+        <v>3.03</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.9</v>
+        <v>2.52</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>1.46</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46023.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.48</v>
+        <v>3.4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="N12" t="n">
-        <v>2.9</v>
+        <v>1.92</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.13</v>
+        <v>1.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46023.5</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.47</v>
+        <v>1.62</v>
       </c>
       <c r="M13" t="n">
-        <v>3.08</v>
+        <v>3.75</v>
       </c>
       <c r="N13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T13" t="n">
         <v>2.56</v>
       </c>
-      <c r="O13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.85</v>
-      </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="V13" t="n">
-        <v>7.4</v>
+        <v>5.85</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="AA13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF13" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.46</v>
+        <v>2.04</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46023.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="M14" t="n">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="N14" t="n">
-        <v>2.37</v>
+        <v>2.56</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46023.5</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="M15" t="n">
-        <v>3.07</v>
+        <v>3.87</v>
       </c>
       <c r="N15" t="n">
-        <v>2.86</v>
+        <v>4.75</v>
       </c>
       <c r="O15" t="n">
-        <v>2.9</v>
+        <v>2.14</v>
       </c>
       <c r="P15" t="n">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>2.65</v>
+        <v>2.99</v>
       </c>
       <c r="T15" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="V15" t="n">
-        <v>6.5</v>
+        <v>5.55</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.12</v>
+        <v>3.74</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.94</v>
+        <v>1.71</v>
       </c>
       <c r="AB15" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.76</v>
       </c>
-      <c r="AC15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AF15" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.49</v>
+        <v>2.27</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46023.5</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.39</v>
+        <v>1.69</v>
       </c>
       <c r="M16" t="n">
-        <v>3.23</v>
+        <v>3.68</v>
       </c>
       <c r="N16" t="n">
-        <v>1.94</v>
+        <v>4.9</v>
       </c>
       <c r="O16" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46023.5</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.93</v>
+        <v>2.97</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="O17" t="n">
-        <v>4.1</v>
+        <v>4.01</v>
       </c>
       <c r="P17" t="n">
         <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="T17" t="n">
-        <v>2.99</v>
+        <v>2.7</v>
       </c>
       <c r="U17" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="V17" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="W17" t="n">
         <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.21</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46023.5</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.78</v>
+        <v>2.23</v>
       </c>
       <c r="M18" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.87</v>
+        <v>3.15</v>
       </c>
       <c r="O18" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46023.5</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.28</v>
+        <v>3.93</v>
       </c>
       <c r="M19" t="n">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>3.03</v>
+        <v>1.8</v>
       </c>
       <c r="O19" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="P19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF19" t="n">
         <v>1.86</v>
       </c>
-      <c r="Q19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="V19" t="n">
-        <v>11</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AG19" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.54</v>
+        <v>1.21</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46023.5</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.58</v>
+        <v>2.17</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>2.41</v>
+        <v>2.97</v>
       </c>
       <c r="O20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.78</v>
+        <v>2.07</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46023.5</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.47</v>
+        <v>2.84</v>
       </c>
       <c r="M22" t="n">
-        <v>3.04</v>
+        <v>3.13</v>
       </c>
       <c r="N22" t="n">
-        <v>1.98</v>
+        <v>2.23</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>3.62</v>
       </c>
       <c r="P22" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.55</v>
+        <v>2.97</v>
       </c>
       <c r="R22" t="n">
         <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="T22" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="U22" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="V22" t="n">
-        <v>8.300000000000001</v>
+        <v>6.25</v>
       </c>
       <c r="W22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="Z22" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46023.5</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.62</v>
+        <v>2.27</v>
       </c>
       <c r="M24" t="n">
-        <v>3.75</v>
+        <v>3.03</v>
       </c>
       <c r="N24" t="n">
-        <v>4.3</v>
+        <v>2.86</v>
       </c>
       <c r="O24" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="P24" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="R24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U24" t="n">
         <v>1.34</v>
       </c>
-      <c r="S24" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V24" t="n">
-        <v>5.85</v>
+        <v>6.4</v>
       </c>
       <c r="W24" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.04</v>
+        <v>1.6</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46023.5</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.57</v>
+        <v>2.18</v>
       </c>
       <c r="M25" t="n">
-        <v>3.75</v>
+        <v>3.16</v>
       </c>
       <c r="N25" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="O25" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46023.5</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.18</v>
+        <v>3.47</v>
       </c>
       <c r="M26" t="n">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="N26" t="n">
-        <v>2.9</v>
+        <v>1.98</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="AB26" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF26" t="n">
         <v>1.82</v>
       </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46023.5</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.53</v>
+        <v>2.65</v>
       </c>
       <c r="M27" t="n">
-        <v>3.87</v>
+        <v>3.11</v>
       </c>
       <c r="N27" t="n">
-        <v>4.75</v>
+        <v>2.37</v>
       </c>
       <c r="O27" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.71</v>
+        <v>1.96</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.01</v>
+        <v>1.74</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46023.5</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.69</v>
+        <v>2.48</v>
       </c>
       <c r="M28" t="n">
-        <v>3.68</v>
+        <v>3.1</v>
       </c>
       <c r="N28" t="n">
-        <v>4.9</v>
+        <v>2.9</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.7</v>
+        <v>2.13</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,22 +3872,22 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="M29" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="N29" t="n">
         <v>2.86</v>
       </c>
       <c r="O29" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="P29" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R29" t="n">
         <v>1.42</v>
@@ -3896,49 +3896,49 @@
         <v>2.65</v>
       </c>
       <c r="T29" t="n">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="U29" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V29" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="AA29" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AC29" t="n">
         <v>3.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AG29" t="n">
         <v>1.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46023.5</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="M32" t="n">
-        <v>3.23</v>
+        <v>2.99</v>
       </c>
       <c r="N32" t="n">
-        <v>3.03</v>
+        <v>3.65</v>
       </c>
       <c r="O32" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.91</v>
+        <v>2.27</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46023.5</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.83</v>
+        <v>2.41</v>
       </c>
       <c r="M33" t="n">
-        <v>3.68</v>
+        <v>3.18</v>
       </c>
       <c r="N33" t="n">
-        <v>3.99</v>
+        <v>2.56</v>
       </c>
       <c r="O33" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46023.5</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M34" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N34" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V34" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB34" t="n">
         <v>1.95</v>
       </c>
-      <c r="M34" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="N34" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46023.5</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.89</v>
+        <v>4.2</v>
       </c>
       <c r="M35" t="n">
-        <v>3.23</v>
+        <v>3.55</v>
       </c>
       <c r="N35" t="n">
-        <v>2.41</v>
+        <v>1.81</v>
       </c>
       <c r="O35" t="n">
-        <v>3.74</v>
+        <v>5.06</v>
       </c>
       <c r="P35" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.01</v>
+        <v>2.43</v>
       </c>
       <c r="R35" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S35" t="n">
-        <v>2.59</v>
+        <v>2.77</v>
       </c>
       <c r="T35" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="U35" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="V35" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="W35" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X35" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="Z35" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.32</v>
+        <v>1.93</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46023.5</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.41</v>
+        <v>1.54</v>
       </c>
       <c r="M36" t="n">
-        <v>3.18</v>
+        <v>3.83</v>
       </c>
       <c r="N36" t="n">
-        <v>2.56</v>
+        <v>6.3</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46023.5</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.54</v>
+        <v>1.83</v>
       </c>
       <c r="M37" t="n">
-        <v>3.83</v>
+        <v>3.68</v>
       </c>
       <c r="N37" t="n">
-        <v>6.3</v>
+        <v>3.99</v>
       </c>
       <c r="O37" t="n">
-        <v>2.11</v>
+        <v>2.37</v>
       </c>
       <c r="P37" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.04</v>
+        <v>4.42</v>
       </c>
       <c r="R37" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S37" t="n">
-        <v>2.89</v>
+        <v>3.22</v>
       </c>
       <c r="T37" t="n">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="U37" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="V37" t="n">
-        <v>6.25</v>
+        <v>5.95</v>
       </c>
       <c r="W37" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X37" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.54</v>
+        <v>4.25</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.84</v>
+        <v>1.61</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46023.5</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.2</v>
+        <v>2.89</v>
       </c>
       <c r="M38" t="n">
-        <v>3.55</v>
+        <v>3.23</v>
       </c>
       <c r="N38" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V38" t="n">
+        <v>7</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE38" t="n">
         <v>1.81</v>
       </c>
-      <c r="O38" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V38" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AF38" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.93</v>
+        <v>1.32</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46023.5</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.35</v>
+        <v>2.32</v>
       </c>
       <c r="M39" t="n">
-        <v>4.7</v>
+        <v>3.23</v>
       </c>
       <c r="N39" t="n">
-        <v>8.800000000000001</v>
+        <v>3.03</v>
       </c>
       <c r="O39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V39" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB39" t="n">
         <v>1.83</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V39" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.95</v>
       </c>
       <c r="AC39" t="n">
         <v>3.05</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AE39" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.66</v>
+        <v>2.06</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AH39" t="n">
-        <v>3.14</v>
+        <v>1.49</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46023.5</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="M41" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="N41" t="n">
-        <v>6.2</v>
+        <v>3.81</v>
       </c>
       <c r="O41" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46023.60416666666</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="M42" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="N42" t="n">
-        <v>3.81</v>
+        <v>6.2</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46023.60416666666</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>5.7</v>
+        <v>2.35</v>
       </c>
       <c r="M43" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="N43" t="n">
-        <v>1.55</v>
+        <v>2.8</v>
       </c>
       <c r="O43" t="n">
-        <v>4.67</v>
+        <v>3.14</v>
       </c>
       <c r="P43" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q43" t="n">
+        <v>3</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V43" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB43" t="n">
         <v>1.85</v>
       </c>
-      <c r="R43" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S43" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V43" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>2.13</v>
-      </c>
       <c r="AC43" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.07</v>
+        <v>1.4</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.25</v>
+        <v>5.7</v>
       </c>
       <c r="M44" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="N44" t="n">
-        <v>3</v>
+        <v>1.55</v>
       </c>
       <c r="O44" t="n">
-        <v>2.92</v>
+        <v>4.67</v>
       </c>
       <c r="P44" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.6</v>
+        <v>1.85</v>
       </c>
       <c r="R44" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="T44" t="n">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
       <c r="U44" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="V44" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="W44" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X44" t="n">
         <v>1.01</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="AC44" t="n">
-        <v>3.08</v>
+        <v>2.55</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.64</v>
+        <v>1.07</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="M45" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="N45" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="O45" t="n">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="P45" t="n">
         <v>2.2</v>
       </c>
       <c r="Q45" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S45" t="n">
         <v>3</v>
       </c>
-      <c r="R45" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S45" t="n">
-        <v>3.16</v>
-      </c>
       <c r="T45" t="n">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="U45" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="V45" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="W45" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X45" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.6</v>
+        <v>3.08</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46023.70833333334</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -662,10 +662,10 @@
         <v>1.7</v>
       </c>
       <c r="M2" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>4.05</v>
+        <v>4.4</v>
       </c>
       <c r="O2" t="n">
         <v>2.15</v>
@@ -704,16 +704,16 @@
         <v>5.65</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AE2" t="n">
         <v>1.44</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="M3" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="N3" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="O3" t="n">
         <v>2.32</v>
@@ -823,10 +823,10 @@
         <v>4.36</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AC3" t="n">
         <v>2.63</v>
@@ -912,31 +912,31 @@
         <v>2.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.22</v>
+        <v>3.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
         <v>2.73</v>
       </c>
       <c r="T4" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="U4" t="n">
         <v>1.36</v>
       </c>
       <c r="V4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="W4" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
         <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z4" t="n">
         <v>3.25</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.92</v>
+        <v>2.47</v>
       </c>
       <c r="M6" t="n">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.47</v>
+        <v>2.56</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46023.5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.39</v>
+        <v>1.92</v>
       </c>
       <c r="M7" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="N7" t="n">
-        <v>1.94</v>
+        <v>3.47</v>
       </c>
       <c r="O7" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46023.5</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="M8" t="n">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="N8" t="n">
-        <v>3.87</v>
+        <v>4.9</v>
       </c>
       <c r="O8" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46023.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.57</v>
+        <v>2.48</v>
       </c>
       <c r="M9" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="O9" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.81</v>
+        <v>2.13</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46023.5</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.58</v>
+        <v>1.78</v>
       </c>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>3.34</v>
       </c>
       <c r="N10" t="n">
-        <v>2.41</v>
+        <v>3.87</v>
       </c>
       <c r="O10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V10" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC10" t="n">
         <v>3.2</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V10" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.95</v>
-      </c>
       <c r="AD10" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.16</v>
+        <v>1.91</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.38</v>
+        <v>1.81</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46023.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="M11" t="n">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>3.03</v>
+        <v>3.15</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.52</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.46</v>
+        <v>1.79</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46023.5</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.4</v>
+        <v>1.57</v>
       </c>
       <c r="M12" t="n">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="N12" t="n">
-        <v>1.92</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
-        <v>3.85</v>
+        <v>2.15</v>
       </c>
       <c r="P12" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.52</v>
+        <v>5.92</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>2.98</v>
+        <v>2.85</v>
       </c>
       <c r="T12" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="U12" t="n">
         <v>1.42</v>
       </c>
       <c r="V12" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.24</v>
+        <v>2.06</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46023.5</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.62</v>
+        <v>3.93</v>
       </c>
       <c r="M13" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="O13" t="n">
-        <v>2.25</v>
+        <v>4.1</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.7</v>
+        <v>2.45</v>
       </c>
       <c r="R13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U13" t="n">
         <v>1.34</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V13" t="n">
-        <v>5.85</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.21</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>2.04</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46023.5</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.47</v>
+        <v>2.17</v>
       </c>
       <c r="M14" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.56</v>
+        <v>2.97</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46023.5</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="M15" t="n">
-        <v>3.87</v>
+        <v>3.13</v>
       </c>
       <c r="N15" t="n">
-        <v>4.75</v>
+        <v>3.66</v>
       </c>
       <c r="O15" t="n">
-        <v>2.14</v>
+        <v>2.48</v>
       </c>
       <c r="P15" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>4.45</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T15" t="n">
         <v>2.99</v>
       </c>
-      <c r="T15" t="n">
-        <v>2.5</v>
-      </c>
       <c r="U15" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="V15" t="n">
-        <v>5.55</v>
+        <v>6.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.74</v>
+        <v>3.25</v>
       </c>
       <c r="AA15" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.71</v>
       </c>
-      <c r="AB15" t="n">
-        <v>2.01</v>
-      </c>
       <c r="AC15" t="n">
-        <v>2.66</v>
+        <v>3.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.27</v>
+        <v>1.79</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46023.5</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.69</v>
+        <v>2.58</v>
       </c>
       <c r="M16" t="n">
-        <v>3.68</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>4.9</v>
+        <v>2.41</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46023.5</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.97</v>
+        <v>1.62</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="N17" t="n">
-        <v>2.15</v>
+        <v>4.3</v>
       </c>
       <c r="O17" t="n">
-        <v>4.01</v>
+        <v>2.25</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.75</v>
+        <v>5.02</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="S17" t="n">
-        <v>2.77</v>
+        <v>2.95</v>
       </c>
       <c r="T17" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="U17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.37</v>
       </c>
-      <c r="V17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AE17" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.3</v>
+        <v>2.02</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46023.5</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.23</v>
+        <v>2.97</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>3.15</v>
+        <v>2.15</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB18" t="n">
         <v>1.79</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46023.5</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,28 +2682,28 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.93</v>
+        <v>2.27</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>3.03</v>
       </c>
       <c r="N19" t="n">
-        <v>1.8</v>
+        <v>2.86</v>
       </c>
       <c r="O19" t="n">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="P19" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="R19" t="n">
         <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="T19" t="n">
         <v>2.99</v>
@@ -2712,43 +2712,43 @@
         <v>1.34</v>
       </c>
       <c r="V19" t="n">
-        <v>7.5</v>
+        <v>6.4</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="AD19" t="n">
         <v>1.23</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.21</v>
+        <v>1.6</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46023.5</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="N20" t="n">
-        <v>2.97</v>
+        <v>3.03</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.07</v>
+        <v>2.52</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46023.5</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.46</v>
+        <v>2.65</v>
       </c>
       <c r="M21" t="n">
-        <v>3.91</v>
+        <v>3.11</v>
       </c>
       <c r="N21" t="n">
-        <v>5.5</v>
+        <v>2.37</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.72</v>
+        <v>1.96</v>
       </c>
       <c r="AB21" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.84</v>
+        <v>1.53</v>
       </c>
       <c r="M22" t="n">
-        <v>3.13</v>
+        <v>3.87</v>
       </c>
       <c r="N22" t="n">
-        <v>2.23</v>
+        <v>4.75</v>
       </c>
       <c r="O22" t="n">
-        <v>3.62</v>
+        <v>2.09</v>
       </c>
       <c r="P22" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.97</v>
+        <v>5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="T22" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="U22" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="V22" t="n">
-        <v>6.25</v>
+        <v>5.55</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.3</v>
+        <v>3.72</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.94</v>
+        <v>1.71</v>
       </c>
       <c r="AB22" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.76</v>
       </c>
-      <c r="AC22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.36</v>
+        <v>2.27</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46023.5</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="M23" t="n">
-        <v>3.13</v>
+        <v>3.28</v>
       </c>
       <c r="N23" t="n">
-        <v>3.66</v>
+        <v>1.92</v>
       </c>
       <c r="O23" t="n">
-        <v>2.48</v>
+        <v>4.28</v>
       </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.45</v>
+        <v>2.52</v>
       </c>
       <c r="R23" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>2.65</v>
+        <v>2.98</v>
       </c>
       <c r="T23" t="n">
-        <v>2.99</v>
+        <v>2.62</v>
       </c>
       <c r="U23" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="V23" t="n">
         <v>6.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X23" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.25</v>
+        <v>3.58</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.7</v>
+        <v>2.92</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.79</v>
+        <v>1.24</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46023.5</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.27</v>
+        <v>3.39</v>
       </c>
       <c r="M24" t="n">
-        <v>3.03</v>
+        <v>3.23</v>
       </c>
       <c r="N24" t="n">
-        <v>2.86</v>
+        <v>1.94</v>
       </c>
       <c r="O24" t="n">
-        <v>2.75</v>
+        <v>3.85</v>
       </c>
       <c r="P24" t="n">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.5</v>
+        <v>2.62</v>
       </c>
       <c r="R24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U24" t="n">
         <v>1.42</v>
       </c>
-      <c r="S24" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.34</v>
-      </c>
       <c r="V24" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z24" t="n">
         <v>3.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AG24" t="n">
         <v>1.28</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.6</v>
+        <v>1.27</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46023.5</v>
@@ -3524,25 +3524,25 @@
         <v>1.98</v>
       </c>
       <c r="O26" t="n">
-        <v>4</v>
+        <v>4.54</v>
       </c>
       <c r="P26" t="n">
         <v>1.96</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.55</v>
+        <v>2.74</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="S26" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="T26" t="n">
         <v>3.1</v>
       </c>
       <c r="U26" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V26" t="n">
         <v>8.300000000000001</v>
@@ -3575,7 +3575,7 @@
         <v>1.85</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
         <v>1.29</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.65</v>
+        <v>1.46</v>
       </c>
       <c r="M27" t="n">
-        <v>3.11</v>
+        <v>3.91</v>
       </c>
       <c r="N27" t="n">
-        <v>2.37</v>
+        <v>5.5</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.96</v>
+        <v>1.72</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.48</v>
+        <v>2.84</v>
       </c>
       <c r="M28" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="N28" t="n">
-        <v>2.9</v>
+        <v>2.23</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.13</v>
+        <v>1.94</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46023.5</v>
@@ -3881,13 +3881,13 @@
         <v>2.86</v>
       </c>
       <c r="O29" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P29" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="R29" t="n">
         <v>1.42</v>
@@ -3935,10 +3935,10 @@
         <v>1.98</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46023.5</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.68</v>
+        <v>2.89</v>
       </c>
       <c r="M31" t="n">
-        <v>3.57</v>
+        <v>3.23</v>
       </c>
       <c r="N31" t="n">
-        <v>5.1</v>
+        <v>2.41</v>
       </c>
       <c r="O31" t="n">
-        <v>2.3</v>
+        <v>3.74</v>
       </c>
       <c r="P31" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.4</v>
+        <v>3.01</v>
       </c>
       <c r="R31" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="S31" t="n">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="T31" t="n">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="U31" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="V31" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="W31" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X31" t="n">
         <v>1.05</v>
       </c>
       <c r="Y31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AD31" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z31" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE31" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.04</v>
+        <v>1.37</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46023.5</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V32" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB32" t="n">
         <v>1.95</v>
       </c>
-      <c r="M32" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="N32" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46023.5</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.41</v>
+        <v>4.2</v>
       </c>
       <c r="M33" t="n">
-        <v>3.18</v>
+        <v>3.55</v>
       </c>
       <c r="N33" t="n">
-        <v>2.56</v>
+        <v>1.81</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46023.5</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,49 +4467,49 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="M34" t="n">
-        <v>4.7</v>
+        <v>3.83</v>
       </c>
       <c r="N34" t="n">
-        <v>8.800000000000001</v>
+        <v>6.3</v>
       </c>
       <c r="O34" t="n">
-        <v>1.83</v>
+        <v>2.11</v>
       </c>
       <c r="P34" t="n">
-        <v>2.55</v>
+        <v>2.19</v>
       </c>
       <c r="Q34" t="n">
-        <v>8.25</v>
+        <v>6.04</v>
       </c>
       <c r="R34" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S34" t="n">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="T34" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="U34" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="V34" t="n">
-        <v>6.05</v>
+        <v>6.25</v>
       </c>
       <c r="W34" t="n">
         <v>1.06</v>
       </c>
       <c r="X34" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="AA34" t="n">
         <v>1.79</v>
@@ -4518,22 +4518,22 @@
         <v>1.95</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AH34" t="n">
-        <v>3.14</v>
+        <v>2.39</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46023.5</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>4.2</v>
+        <v>1.95</v>
       </c>
       <c r="M35" t="n">
-        <v>3.55</v>
+        <v>2.99</v>
       </c>
       <c r="N35" t="n">
-        <v>1.81</v>
+        <v>3.65</v>
       </c>
       <c r="O35" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.87</v>
+        <v>2.27</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.87</v>
+        <v>1.56</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46023.5</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="M36" t="n">
-        <v>3.83</v>
+        <v>3.57</v>
       </c>
       <c r="N36" t="n">
-        <v>6.3</v>
+        <v>5.1</v>
       </c>
       <c r="O36" t="n">
-        <v>2.11</v>
+        <v>2.29</v>
       </c>
       <c r="P36" t="n">
-        <v>2.19</v>
+        <v>2.33</v>
       </c>
       <c r="Q36" t="n">
-        <v>6.04</v>
+        <v>4.5</v>
       </c>
       <c r="R36" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S36" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="T36" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="U36" t="n">
         <v>1.43</v>
       </c>
       <c r="V36" t="n">
-        <v>6.25</v>
+        <v>6.6</v>
       </c>
       <c r="W36" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X36" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.54</v>
+        <v>3.45</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="AD36" t="n">
         <v>1.33</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46023.5</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.83</v>
+        <v>2.41</v>
       </c>
       <c r="M37" t="n">
-        <v>3.68</v>
+        <v>3.18</v>
       </c>
       <c r="N37" t="n">
-        <v>3.99</v>
+        <v>2.56</v>
       </c>
       <c r="O37" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46023.5</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.89</v>
+        <v>2.32</v>
       </c>
       <c r="M38" t="n">
         <v>3.23</v>
       </c>
       <c r="N38" t="n">
-        <v>2.41</v>
+        <v>3.03</v>
       </c>
       <c r="O38" t="n">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="P38" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.01</v>
+        <v>3.42</v>
       </c>
       <c r="R38" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S38" t="n">
-        <v>2.59</v>
+        <v>2.73</v>
       </c>
       <c r="T38" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="U38" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="V38" t="n">
         <v>7</v>
       </c>
       <c r="W38" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X38" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="Z38" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46023.5</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.32</v>
+        <v>1.83</v>
       </c>
       <c r="M39" t="n">
-        <v>3.23</v>
+        <v>3.68</v>
       </c>
       <c r="N39" t="n">
-        <v>3.03</v>
+        <v>3.99</v>
       </c>
       <c r="O39" t="n">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="P39" t="n">
-        <v>2.04</v>
+        <v>2.24</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.42</v>
+        <v>4.3</v>
       </c>
       <c r="R39" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S39" t="n">
-        <v>2.73</v>
+        <v>3.22</v>
       </c>
       <c r="T39" t="n">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="U39" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="V39" t="n">
-        <v>6.45</v>
+        <v>5.95</v>
       </c>
       <c r="W39" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X39" t="n">
         <v>1.03</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.24</v>
+        <v>4.25</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.49</v>
+        <v>1.84</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46023.5</v>
@@ -5196,7 +5196,7 @@
         <v>2.1</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.13</v>
+        <v>4.05</v>
       </c>
       <c r="R40" t="n">
         <v>1.35</v>
@@ -5428,25 +5428,25 @@
         <v>6.2</v>
       </c>
       <c r="O42" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="P42" t="n">
         <v>2.38</v>
       </c>
       <c r="Q42" t="n">
-        <v>6</v>
+        <v>4.64</v>
       </c>
       <c r="R42" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S42" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="T42" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="U42" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="V42" t="n">
         <v>5</v>
@@ -5461,7 +5461,7 @@
         <v>1.17</v>
       </c>
       <c r="Z42" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AA42" t="n">
         <v>1.65</v>
@@ -5470,22 +5470,22 @@
         <v>2.25</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AF42" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46023.60416666666</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="M43" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="N43" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="O43" t="n">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="P43" t="n">
         <v>2.2</v>
       </c>
       <c r="Q43" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="R43" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="S43" t="n">
-        <v>3.16</v>
+        <v>2.98</v>
       </c>
       <c r="T43" t="n">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="U43" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="V43" t="n">
-        <v>5.6</v>
+        <v>7.3</v>
       </c>
       <c r="W43" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X43" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.6</v>
+        <v>3.08</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>5.7</v>
+        <v>2.35</v>
       </c>
       <c r="M44" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="N44" t="n">
-        <v>1.55</v>
+        <v>2.8</v>
       </c>
       <c r="O44" t="n">
-        <v>4.67</v>
+        <v>3.14</v>
       </c>
       <c r="P44" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q44" t="n">
+        <v>3</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V44" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB44" t="n">
         <v>1.85</v>
       </c>
-      <c r="R44" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S44" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V44" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X44" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>2.13</v>
-      </c>
       <c r="AC44" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.07</v>
+        <v>1.4</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.25</v>
+        <v>5.7</v>
       </c>
       <c r="M45" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="N45" t="n">
-        <v>3</v>
+        <v>1.55</v>
       </c>
       <c r="O45" t="n">
-        <v>2.92</v>
+        <v>4.67</v>
       </c>
       <c r="P45" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.6</v>
+        <v>1.85</v>
       </c>
       <c r="R45" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="T45" t="n">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
       <c r="U45" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="V45" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="W45" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X45" t="n">
         <v>1.01</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.08</v>
+        <v>2.55</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.64</v>
+        <v>1.07</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46023.70833333334</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="N2" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="O2" t="n">
         <v>2.15</v>
@@ -683,10 +683,10 @@
         <v>3.75</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V2" t="n">
         <v>4.35</v>
@@ -704,28 +704,28 @@
         <v>5.65</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AE2" t="n">
         <v>1.44</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="AG2" t="n">
         <v>1.24</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46023.04166666666</v>
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="M3" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="N3" t="n">
-        <v>3.8</v>
+        <v>3.97</v>
       </c>
       <c r="O3" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="P3" t="n">
         <v>2.3</v>
@@ -817,16 +817,16 @@
         <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.36</v>
+        <v>4.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="AC3" t="n">
         <v>2.63</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.47</v>
+        <v>1.92</v>
       </c>
       <c r="M6" t="n">
-        <v>3.08</v>
+        <v>3.21</v>
       </c>
       <c r="N6" t="n">
-        <v>2.56</v>
+        <v>3.47</v>
       </c>
       <c r="O6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46023.5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.92</v>
+        <v>2.84</v>
       </c>
       <c r="M7" t="n">
-        <v>3.21</v>
+        <v>3.13</v>
       </c>
       <c r="N7" t="n">
-        <v>3.47</v>
+        <v>2.23</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46023.5</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.69</v>
+        <v>2.25</v>
       </c>
       <c r="M8" t="n">
-        <v>3.68</v>
+        <v>3.07</v>
       </c>
       <c r="N8" t="n">
-        <v>4.9</v>
+        <v>2.86</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46023.5</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.48</v>
+        <v>1.69</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>3.68</v>
       </c>
       <c r="N9" t="n">
-        <v>2.9</v>
+        <v>4.9</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.13</v>
+        <v>1.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.78</v>
+        <v>3.93</v>
       </c>
       <c r="M10" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>3.87</v>
+        <v>1.8</v>
       </c>
       <c r="O10" t="n">
-        <v>2.44</v>
+        <v>4.1</v>
       </c>
       <c r="P10" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.84</v>
+        <v>2.45</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S10" t="n">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="T10" t="n">
-        <v>2.65</v>
+        <v>2.99</v>
       </c>
       <c r="U10" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="V10" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.26</v>
       </c>
-      <c r="Z10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH10" t="n">
-        <v>1.81</v>
+        <v>1.21</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46023.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.23</v>
+        <v>3.4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="N11" t="n">
-        <v>3.15</v>
+        <v>1.92</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46023.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.57</v>
+        <v>2.23</v>
       </c>
       <c r="M12" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="O12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.92</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46023.5</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.93</v>
+        <v>2.17</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>1.8</v>
+        <v>2.97</v>
       </c>
       <c r="O13" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46023.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.17</v>
+        <v>1.9</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="N14" t="n">
-        <v>2.97</v>
+        <v>3.66</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46023.5</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.9</v>
+        <v>1.46</v>
       </c>
       <c r="M15" t="n">
-        <v>3.13</v>
+        <v>3.91</v>
       </c>
       <c r="N15" t="n">
-        <v>3.66</v>
+        <v>5.5</v>
       </c>
       <c r="O15" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.01</v>
+        <v>1.72</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46023.5</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.58</v>
+        <v>2.27</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>3.03</v>
       </c>
       <c r="N16" t="n">
-        <v>2.41</v>
+        <v>2.86</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="P16" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="T16" t="n">
-        <v>2.59</v>
+        <v>2.99</v>
       </c>
       <c r="U16" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="V16" t="n">
-        <v>6.15</v>
+        <v>6.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46023.5</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.62</v>
+        <v>2.28</v>
       </c>
       <c r="M17" t="n">
-        <v>3.75</v>
+        <v>2.84</v>
       </c>
       <c r="N17" t="n">
-        <v>4.3</v>
+        <v>3.03</v>
       </c>
       <c r="O17" t="n">
-        <v>2.25</v>
+        <v>3.08</v>
       </c>
       <c r="P17" t="n">
-        <v>2.19</v>
+        <v>1.86</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.02</v>
+        <v>3.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.34</v>
+        <v>1.56</v>
       </c>
       <c r="S17" t="n">
-        <v>2.95</v>
+        <v>2.31</v>
       </c>
       <c r="T17" t="n">
-        <v>2.56</v>
+        <v>3.52</v>
       </c>
       <c r="U17" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="V17" t="n">
-        <v>5.85</v>
+        <v>11</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.85</v>
+        <v>2.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.79</v>
+        <v>2.52</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.91</v>
+        <v>1.46</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.37</v>
+        <v>1.11</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.73</v>
+        <v>2.11</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.97</v>
+        <v>1.65</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.02</v>
+        <v>1.55</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46023.5</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.97</v>
+        <v>2.48</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="O18" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46023.5</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.27</v>
+        <v>1.53</v>
       </c>
       <c r="M19" t="n">
-        <v>3.03</v>
+        <v>3.87</v>
       </c>
       <c r="N19" t="n">
-        <v>2.86</v>
+        <v>4.75</v>
       </c>
       <c r="O19" t="n">
-        <v>2.75</v>
+        <v>2.09</v>
       </c>
       <c r="P19" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="T19" t="n">
-        <v>2.99</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="V19" t="n">
-        <v>6.4</v>
+        <v>5.55</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.3</v>
+        <v>3.72</v>
       </c>
       <c r="AA19" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.72</v>
+        <v>2.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.3</v>
+        <v>2.66</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="AE19" t="n">
         <v>1.76</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.6</v>
+        <v>2.27</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46023.5</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.28</v>
+        <v>3.47</v>
       </c>
       <c r="M20" t="n">
-        <v>2.84</v>
+        <v>3.04</v>
       </c>
       <c r="N20" t="n">
-        <v>3.03</v>
+        <v>1.98</v>
       </c>
       <c r="O20" t="n">
-        <v>3.08</v>
+        <v>4.54</v>
       </c>
       <c r="P20" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.8</v>
+        <v>2.74</v>
       </c>
       <c r="R20" t="n">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="S20" t="n">
-        <v>2.31</v>
+        <v>2.7</v>
       </c>
       <c r="T20" t="n">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="U20" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>11</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W20" t="n">
         <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.55</v>
+        <v>1.26</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46023.5</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="M21" t="n">
-        <v>3.11</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46023.5</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.53</v>
+        <v>3.39</v>
       </c>
       <c r="M22" t="n">
-        <v>3.87</v>
+        <v>3.23</v>
       </c>
       <c r="N22" t="n">
-        <v>4.75</v>
+        <v>1.94</v>
       </c>
       <c r="O22" t="n">
-        <v>2.09</v>
+        <v>3.85</v>
       </c>
       <c r="P22" t="n">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="Q22" t="n">
-        <v>5</v>
+        <v>2.62</v>
       </c>
       <c r="R22" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>2.99</v>
+        <v>2.81</v>
       </c>
       <c r="T22" t="n">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="U22" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="V22" t="n">
-        <v>5.55</v>
+        <v>6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.72</v>
+        <v>3.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.71</v>
+        <v>1.89</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.01</v>
+        <v>1.81</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.27</v>
+        <v>1.27</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46023.5</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.4</v>
+        <v>2.18</v>
       </c>
       <c r="M23" t="n">
-        <v>3.28</v>
+        <v>3.16</v>
       </c>
       <c r="N23" t="n">
-        <v>1.92</v>
+        <v>2.9</v>
       </c>
       <c r="O23" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46023.5</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.39</v>
+        <v>2.47</v>
       </c>
       <c r="M24" t="n">
-        <v>3.23</v>
+        <v>3.08</v>
       </c>
       <c r="N24" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF24" t="n">
         <v>1.94</v>
       </c>
-      <c r="O24" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V24" t="n">
-        <v>6</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AG24" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46023.5</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.18</v>
+        <v>1.57</v>
       </c>
       <c r="M25" t="n">
-        <v>3.16</v>
+        <v>3.75</v>
       </c>
       <c r="N25" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>5.92</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46023.5</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.47</v>
+        <v>2.97</v>
       </c>
       <c r="M26" t="n">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="N26" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="O26" t="n">
-        <v>4.54</v>
+        <v>4.01</v>
       </c>
       <c r="P26" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="R26" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="S26" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T26" t="n">
         <v>2.7</v>
       </c>
-      <c r="T26" t="n">
-        <v>3.1</v>
-      </c>
       <c r="U26" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="V26" t="n">
-        <v>8.300000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="W26" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X26" t="n">
         <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG26" t="n">
         <v>1.29</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46023.5</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.46</v>
+        <v>1.78</v>
       </c>
       <c r="M27" t="n">
-        <v>3.91</v>
+        <v>3.34</v>
       </c>
       <c r="N27" t="n">
-        <v>5.5</v>
+        <v>3.87</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="AB27" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46023.5</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.84</v>
+        <v>1.62</v>
       </c>
       <c r="M28" t="n">
-        <v>3.13</v>
+        <v>3.75</v>
       </c>
       <c r="N28" t="n">
-        <v>2.23</v>
+        <v>4.3</v>
       </c>
       <c r="O28" t="n">
-        <v>3.62</v>
+        <v>2.25</v>
       </c>
       <c r="P28" t="n">
-        <v>2.04</v>
+        <v>2.19</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.97</v>
+        <v>5.02</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="S28" t="n">
-        <v>2.73</v>
+        <v>2.95</v>
       </c>
       <c r="T28" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="U28" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="V28" t="n">
-        <v>6.25</v>
+        <v>5.85</v>
       </c>
       <c r="W28" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AE28" t="n">
         <v>1.73</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.36</v>
+        <v>2.02</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46023.5</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.25</v>
+        <v>2.65</v>
       </c>
       <c r="M29" t="n">
-        <v>3.07</v>
+        <v>3.11</v>
       </c>
       <c r="N29" t="n">
-        <v>2.86</v>
+        <v>2.37</v>
       </c>
       <c r="O29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46023.5</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.89</v>
+        <v>1.83</v>
       </c>
       <c r="M31" t="n">
-        <v>3.23</v>
+        <v>3.68</v>
       </c>
       <c r="N31" t="n">
-        <v>2.41</v>
+        <v>3.99</v>
       </c>
       <c r="O31" t="n">
-        <v>3.74</v>
+        <v>2.35</v>
       </c>
       <c r="P31" t="n">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.01</v>
+        <v>4.3</v>
       </c>
       <c r="R31" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
-        <v>2.59</v>
+        <v>3.22</v>
       </c>
       <c r="T31" t="n">
-        <v>2.88</v>
+        <v>2.47</v>
       </c>
       <c r="U31" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="V31" t="n">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="W31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X31" t="n">
         <v>1.03</v>
       </c>
-      <c r="X31" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y31" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="Z31" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.85</v>
+        <v>2.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.37</v>
+        <v>1.84</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46023.5</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="O32" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U32" t="n">
         <v>1.35</v>
       </c>
-      <c r="M32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N32" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.49</v>
-      </c>
       <c r="V32" t="n">
-        <v>6.05</v>
+        <v>7</v>
       </c>
       <c r="W32" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.72</v>
+        <v>3</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.05</v>
+        <v>3.85</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AH32" t="n">
-        <v>3.14</v>
+        <v>1.37</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46023.5</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,49 +4348,49 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.2</v>
+        <v>1.68</v>
       </c>
       <c r="M33" t="n">
-        <v>3.55</v>
+        <v>3.57</v>
       </c>
       <c r="N33" t="n">
-        <v>1.81</v>
+        <v>5.1</v>
       </c>
       <c r="O33" t="n">
-        <v>4.2</v>
+        <v>2.29</v>
       </c>
       <c r="P33" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="R33" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S33" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="T33" t="n">
-        <v>2.77</v>
+        <v>2.55</v>
       </c>
       <c r="U33" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="V33" t="n">
-        <v>6.25</v>
+        <v>6.6</v>
       </c>
       <c r="W33" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X33" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y33" t="n">
         <v>1.24</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="AA33" t="n">
         <v>1.87</v>
@@ -4399,22 +4399,22 @@
         <v>1.87</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.18</v>
+        <v>2.06</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46023.5</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.54</v>
+        <v>4.2</v>
       </c>
       <c r="M34" t="n">
-        <v>3.83</v>
+        <v>3.55</v>
       </c>
       <c r="N34" t="n">
-        <v>6.3</v>
+        <v>1.81</v>
       </c>
       <c r="O34" t="n">
-        <v>2.11</v>
+        <v>4.2</v>
       </c>
       <c r="P34" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>6.04</v>
+        <v>2.4</v>
       </c>
       <c r="R34" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S34" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="T34" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="U34" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="V34" t="n">
         <v>6.25</v>
       </c>
       <c r="W34" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.54</v>
+        <v>3.44</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AC34" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.39</v>
+        <v>1.18</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46023.5</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="N35" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V35" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB35" t="n">
         <v>1.95</v>
       </c>
-      <c r="M35" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="N35" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46023.5</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="M36" t="n">
-        <v>3.57</v>
+        <v>2.99</v>
       </c>
       <c r="N36" t="n">
-        <v>5.1</v>
+        <v>3.65</v>
       </c>
       <c r="O36" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.87</v>
+        <v>2.27</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.87</v>
+        <v>1.56</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46023.5</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.32</v>
+        <v>1.35</v>
       </c>
       <c r="M38" t="n">
-        <v>3.23</v>
+        <v>4.7</v>
       </c>
       <c r="N38" t="n">
-        <v>3.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O38" t="n">
-        <v>3.1</v>
+        <v>1.84</v>
       </c>
       <c r="P38" t="n">
-        <v>2.04</v>
+        <v>2.34</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.42</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="R38" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S38" t="n">
-        <v>2.73</v>
+        <v>2.99</v>
       </c>
       <c r="T38" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="U38" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="V38" t="n">
-        <v>7</v>
+        <v>6.05</v>
       </c>
       <c r="W38" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X38" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.24</v>
+        <v>3.72</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC38" t="n">
         <v>3.05</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.7</v>
+        <v>2.08</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.06</v>
+        <v>1.67</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.42</v>
+        <v>1.16</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.49</v>
+        <v>3.14</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46023.5</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.83</v>
+        <v>2.32</v>
       </c>
       <c r="M39" t="n">
-        <v>3.68</v>
+        <v>3.23</v>
       </c>
       <c r="N39" t="n">
-        <v>3.99</v>
+        <v>3.03</v>
       </c>
       <c r="O39" t="n">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="P39" t="n">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.3</v>
+        <v>3.42</v>
       </c>
       <c r="R39" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S39" t="n">
-        <v>3.22</v>
+        <v>2.73</v>
       </c>
       <c r="T39" t="n">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="U39" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="V39" t="n">
-        <v>5.95</v>
+        <v>7</v>
       </c>
       <c r="W39" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X39" t="n">
         <v>1.03</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="Z39" t="n">
-        <v>4.25</v>
+        <v>3.24</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.63</v>
+        <v>1.91</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.84</v>
+        <v>1.49</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46023.5</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N40" t="n">
-        <v>3.7</v>
+        <v>3.81</v>
       </c>
       <c r="O40" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46023.60416666666</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.89</v>
+        <v>2.18</v>
       </c>
       <c r="M41" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>3.81</v>
+        <v>3.3</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46023.60416666666</v>
@@ -5419,22 +5419,22 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="M42" t="n">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="N42" t="n">
-        <v>6.2</v>
+        <v>5.75</v>
       </c>
       <c r="O42" t="n">
         <v>2.02</v>
       </c>
       <c r="P42" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.64</v>
+        <v>5.65</v>
       </c>
       <c r="R42" t="n">
         <v>1.28</v>
@@ -5443,13 +5443,13 @@
         <v>3.36</v>
       </c>
       <c r="T42" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="U42" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="V42" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="W42" t="n">
         <v>1.11</v>
@@ -5461,16 +5461,16 @@
         <v>1.17</v>
       </c>
       <c r="Z42" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AD42" t="n">
         <v>1.52</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.25</v>
+        <v>7.5</v>
       </c>
       <c r="M43" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="N43" t="n">
-        <v>3</v>
+        <v>1.45</v>
       </c>
       <c r="O43" t="n">
-        <v>2.92</v>
+        <v>4.67</v>
       </c>
       <c r="P43" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.6</v>
+        <v>1.85</v>
       </c>
       <c r="R43" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="S43" t="n">
-        <v>2.98</v>
+        <v>3.36</v>
       </c>
       <c r="T43" t="n">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
       <c r="U43" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="V43" t="n">
-        <v>7.3</v>
+        <v>5.1</v>
       </c>
       <c r="W43" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X43" t="n">
         <v>1.01</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AC43" t="n">
-        <v>3.08</v>
+        <v>2.55</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.64</v>
+        <v>1.07</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="M44" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N44" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="O44" t="n">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="P44" t="n">
         <v>2.2</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="R44" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="S44" t="n">
-        <v>3.16</v>
+        <v>2.98</v>
       </c>
       <c r="T44" t="n">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="U44" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="V44" t="n">
-        <v>5.6</v>
+        <v>7.3</v>
       </c>
       <c r="W44" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X44" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.6</v>
+        <v>3.08</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>5.7</v>
+        <v>2.35</v>
       </c>
       <c r="M45" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="N45" t="n">
-        <v>1.55</v>
+        <v>2.8</v>
       </c>
       <c r="O45" t="n">
-        <v>4.67</v>
+        <v>3.14</v>
       </c>
       <c r="P45" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q45" t="n">
+        <v>3</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V45" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB45" t="n">
         <v>1.85</v>
       </c>
-      <c r="R45" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S45" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U45" t="n">
+      <c r="AC45" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE45" t="n">
         <v>1.54</v>
       </c>
-      <c r="V45" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF45" t="n">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.07</v>
+        <v>1.4</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46023.70833333334</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -897,40 +897,40 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="P4" t="n">
         <v>2.06</v>
       </c>
-      <c r="M4" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.05</v>
-      </c>
       <c r="Q4" t="n">
-        <v>3.8</v>
+        <v>4.17</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S4" t="n">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="T4" t="n">
         <v>2.75</v>
       </c>
       <c r="U4" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
         <v>1.06</v>
@@ -942,10 +942,10 @@
         <v>3.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AC4" t="n">
         <v>3.55</v>
@@ -954,16 +954,16 @@
         <v>1.28</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46023.39583333334</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="M6" t="n">
-        <v>3.21</v>
+        <v>3.36</v>
       </c>
       <c r="N6" t="n">
-        <v>3.47</v>
+        <v>3.75</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,7 +1180,7 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB6" t="n">
         <v>1.8</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.84</v>
+        <v>1.65</v>
       </c>
       <c r="M7" t="n">
-        <v>3.13</v>
+        <v>3.6</v>
       </c>
       <c r="N7" t="n">
-        <v>2.23</v>
+        <v>5.08</v>
       </c>
       <c r="O7" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46023.5</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="M8" t="n">
-        <v>3.07</v>
+        <v>3.75</v>
       </c>
       <c r="N8" t="n">
-        <v>2.86</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>2.26</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.81</v>
+        <v>4.7</v>
       </c>
       <c r="R8" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="T8" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="U8" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="V8" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.33</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.26</v>
       </c>
       <c r="AE8" t="n">
         <v>1.74</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.56</v>
+        <v>2.01</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46023.5</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.69</v>
+        <v>2.52</v>
       </c>
       <c r="M9" t="n">
-        <v>3.68</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>4.9</v>
+        <v>2.7</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.93</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC10" t="n">
         <v>3.25</v>
       </c>
-      <c r="N10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.44</v>
-      </c>
       <c r="AD10" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46023.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>1.92</v>
+        <v>3.1</v>
       </c>
       <c r="O11" t="n">
-        <v>4.28</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.52</v>
+        <v>3.81</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="S11" t="n">
-        <v>2.98</v>
+        <v>2.65</v>
       </c>
       <c r="T11" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="V11" t="n">
         <v>6.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.58</v>
+        <v>3.12</v>
       </c>
       <c r="AA11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB11" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB11" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AC11" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46023.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.23</v>
+        <v>1.44</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="N12" t="n">
-        <v>3.15</v>
+        <v>6.6</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="M14" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="N14" t="n">
-        <v>3.66</v>
+        <v>2.75</v>
       </c>
       <c r="O14" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q14" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.01</v>
-      </c>
       <c r="AB14" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46023.5</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.46</v>
+        <v>3.29</v>
       </c>
       <c r="M15" t="n">
-        <v>3.91</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>5.5</v>
+        <v>2.14</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46023.5</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.27</v>
+        <v>2.7</v>
       </c>
       <c r="M16" t="n">
-        <v>3.03</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>2.86</v>
+        <v>2.45</v>
       </c>
       <c r="O16" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="S16" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="T16" t="n">
-        <v>2.99</v>
+        <v>2.59</v>
       </c>
       <c r="U16" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="V16" t="n">
-        <v>6.4</v>
+        <v>6.15</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="AA16" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB16" t="n">
         <v>2</v>
       </c>
-      <c r="AB16" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AC16" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46023.5</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.28</v>
+        <v>1.64</v>
       </c>
       <c r="M17" t="n">
-        <v>2.84</v>
+        <v>3.72</v>
       </c>
       <c r="N17" t="n">
-        <v>3.03</v>
+        <v>5</v>
       </c>
       <c r="O17" t="n">
-        <v>3.08</v>
+        <v>2.16</v>
       </c>
       <c r="P17" t="n">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.8</v>
+        <v>5.86</v>
       </c>
       <c r="R17" t="n">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>2.31</v>
+        <v>2.85</v>
       </c>
       <c r="T17" t="n">
-        <v>3.52</v>
+        <v>2.62</v>
       </c>
       <c r="U17" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="V17" t="n">
-        <v>11</v>
+        <v>6.3</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.4</v>
+        <v>3.45</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.52</v>
+        <v>1.83</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.46</v>
+        <v>1.92</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.11</v>
+        <v>1.83</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.55</v>
+        <v>2.21</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46023.5</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.48</v>
+        <v>1.57</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>5.49</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.13</v>
+        <v>1.73</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46023.5</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.53</v>
+        <v>3.85</v>
       </c>
       <c r="M19" t="n">
-        <v>3.87</v>
+        <v>3.45</v>
       </c>
       <c r="N19" t="n">
-        <v>4.75</v>
+        <v>1.99</v>
       </c>
       <c r="O19" t="n">
-        <v>2.09</v>
+        <v>4.1</v>
       </c>
       <c r="P19" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>2.45</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="S19" t="n">
-        <v>2.99</v>
+        <v>2.65</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="U19" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="V19" t="n">
-        <v>5.55</v>
+        <v>7.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.72</v>
+        <v>3.15</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.71</v>
+        <v>2.07</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.01</v>
+        <v>1.72</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.66</v>
+        <v>3.44</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.27</v>
+        <v>1.21</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46023.5</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.47</v>
+        <v>1.95</v>
       </c>
       <c r="M20" t="n">
-        <v>3.04</v>
+        <v>3.36</v>
       </c>
       <c r="N20" t="n">
-        <v>1.98</v>
+        <v>3.81</v>
       </c>
       <c r="O20" t="n">
-        <v>4.54</v>
+        <v>2.48</v>
       </c>
       <c r="P20" t="n">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.74</v>
+        <v>4.45</v>
       </c>
       <c r="R20" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S20" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="T20" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V20" t="n">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="W20" t="n">
         <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="Z20" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AC20" t="n">
         <v>3.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.26</v>
+        <v>1.8</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46023.5</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>2.41</v>
+        <v>3.05</v>
       </c>
       <c r="O21" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="P21" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S21" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="T21" t="n">
-        <v>2.59</v>
+        <v>2.99</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="V21" t="n">
-        <v>6.15</v>
+        <v>7.9</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46023.5</v>
@@ -3039,19 +3039,19 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.39</v>
+        <v>3.51</v>
       </c>
       <c r="M22" t="n">
-        <v>3.23</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>1.94</v>
+        <v>2.03</v>
       </c>
       <c r="O22" t="n">
         <v>3.85</v>
       </c>
       <c r="P22" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
         <v>2.62</v>
@@ -3084,16 +3084,16 @@
         <v>3.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC22" t="n">
         <v>3.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE22" t="n">
         <v>1.7</v>
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.16</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.47</v>
+        <v>3.68</v>
       </c>
       <c r="M24" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="N24" t="n">
-        <v>2.56</v>
+        <v>2</v>
       </c>
       <c r="O24" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="P24" t="n">
-        <v>2.03</v>
+        <v>1.96</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.2</v>
+        <v>2.73</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="S24" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="T24" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="U24" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="V24" t="n">
-        <v>7.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46023.5</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.57</v>
+        <v>2.55</v>
       </c>
       <c r="M25" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="N25" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="O25" t="n">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="P25" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.92</v>
+        <v>3.2</v>
       </c>
       <c r="R25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U25" t="n">
         <v>1.36</v>
       </c>
-      <c r="S25" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.42</v>
-      </c>
       <c r="V25" t="n">
-        <v>6.3</v>
+        <v>7.4</v>
       </c>
       <c r="W25" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X25" t="n">
         <v>1</v>
       </c>
       <c r="Y25" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z25" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH25" t="n">
-        <v>2.06</v>
+        <v>1.46</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46023.5</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="M26" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>2.15</v>
+        <v>2.49</v>
       </c>
       <c r="O26" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V26" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AB26" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46023.5</v>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="M27" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>3.87</v>
+        <v>4</v>
       </c>
       <c r="O27" t="n">
         <v>2.44</v>
@@ -3652,7 +3652,7 @@
         <v>4.84</v>
       </c>
       <c r="R27" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S27" t="n">
         <v>2.81</v>
@@ -3679,10 +3679,10 @@
         <v>3.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AC27" t="n">
         <v>3.2</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.62</v>
+        <v>2.37</v>
       </c>
       <c r="M28" t="n">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="N28" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="O28" t="n">
-        <v>2.25</v>
+        <v>3.08</v>
       </c>
       <c r="P28" t="n">
-        <v>2.19</v>
+        <v>1.86</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.02</v>
+        <v>3.8</v>
       </c>
       <c r="R28" t="n">
-        <v>1.34</v>
+        <v>1.56</v>
       </c>
       <c r="S28" t="n">
-        <v>2.95</v>
+        <v>2.31</v>
       </c>
       <c r="T28" t="n">
-        <v>2.56</v>
+        <v>3.52</v>
       </c>
       <c r="U28" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="V28" t="n">
-        <v>5.85</v>
+        <v>11</v>
       </c>
       <c r="W28" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.85</v>
+        <v>2.45</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.79</v>
+        <v>2.49</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.91</v>
+        <v>1.43</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.37</v>
+        <v>1.11</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.73</v>
+        <v>2.11</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.97</v>
+        <v>1.65</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.02</v>
+        <v>1.54</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46023.5</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.65</v>
+        <v>3.8</v>
       </c>
       <c r="M29" t="n">
-        <v>3.11</v>
+        <v>3.6</v>
       </c>
       <c r="N29" t="n">
-        <v>2.37</v>
+        <v>1.93</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46023.5</v>
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="M30" t="n">
-        <v>3.13</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4110,22 +4110,22 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="M31" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="N31" t="n">
-        <v>3.99</v>
+        <v>3.88</v>
       </c>
       <c r="O31" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="P31" t="n">
         <v>2.24</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.3</v>
+        <v>4.42</v>
       </c>
       <c r="R31" t="n">
         <v>1.3</v>
@@ -4137,7 +4137,7 @@
         <v>2.47</v>
       </c>
       <c r="U31" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="V31" t="n">
         <v>5.95</v>
@@ -4155,10 +4155,10 @@
         <v>4.25</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AC31" t="n">
         <v>2.6</v>
@@ -4176,7 +4176,7 @@
         <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46023.5</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.89</v>
+        <v>2.5</v>
       </c>
       <c r="M32" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="N32" t="n">
-        <v>2.41</v>
+        <v>2.87</v>
       </c>
       <c r="O32" t="n">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="P32" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.01</v>
+        <v>3.44</v>
       </c>
       <c r="R32" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S32" t="n">
-        <v>2.59</v>
+        <v>2.73</v>
       </c>
       <c r="T32" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="U32" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="V32" t="n">
         <v>7</v>
       </c>
       <c r="W32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X32" t="n">
         <v>1.03</v>
       </c>
-      <c r="X32" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y32" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="Z32" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB32" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE32" t="n">
         <v>1.7</v>
       </c>
-      <c r="AC32" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AF32" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="AG32" t="n">
         <v>1.32</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46023.5</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="M33" t="n">
-        <v>3.57</v>
+        <v>4.2</v>
       </c>
       <c r="N33" t="n">
-        <v>5.1</v>
+        <v>5.75</v>
       </c>
       <c r="O33" t="n">
-        <v>2.29</v>
+        <v>2.11</v>
       </c>
       <c r="P33" t="n">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.5</v>
+        <v>6.04</v>
       </c>
       <c r="R33" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S33" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="T33" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="U33" t="n">
         <v>1.43</v>
       </c>
       <c r="V33" t="n">
-        <v>6.6</v>
+        <v>6.25</v>
       </c>
       <c r="W33" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X33" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.45</v>
+        <v>3.54</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AD33" t="n">
         <v>1.33</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46023.5</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>4.2</v>
+        <v>2.55</v>
       </c>
       <c r="M34" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N34" t="n">
-        <v>1.81</v>
+        <v>2.7</v>
       </c>
       <c r="O34" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46023.5</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.54</v>
+        <v>2.05</v>
       </c>
       <c r="M35" t="n">
-        <v>3.83</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>6.3</v>
+        <v>3.75</v>
       </c>
       <c r="O35" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.79</v>
+        <v>2.35</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AC35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46023.5</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="M36" t="n">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="N36" t="n">
-        <v>3.65</v>
+        <v>2.38</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46023.5</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.41</v>
+        <v>4.33</v>
       </c>
       <c r="M37" t="n">
-        <v>3.18</v>
+        <v>3.7</v>
       </c>
       <c r="N37" t="n">
-        <v>2.56</v>
+        <v>1.8</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA37" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB37" t="n">
         <v>1.9</v>
       </c>
-      <c r="AB37" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46023.5</v>
@@ -4943,22 +4943,22 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M38" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="N38" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="O38" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="P38" t="n">
         <v>2.34</v>
       </c>
       <c r="Q38" t="n">
-        <v>8.050000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="R38" t="n">
         <v>1.34</v>
@@ -4967,10 +4967,10 @@
         <v>2.99</v>
       </c>
       <c r="T38" t="n">
-        <v>2.48</v>
+        <v>2.59</v>
       </c>
       <c r="U38" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="V38" t="n">
         <v>6.05</v>
@@ -4988,22 +4988,22 @@
         <v>3.72</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE38" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG38" t="n">
         <v>1.16</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.32</v>
+        <v>1.69</v>
       </c>
       <c r="M39" t="n">
-        <v>3.23</v>
+        <v>3.6</v>
       </c>
       <c r="N39" t="n">
-        <v>3.03</v>
+        <v>4.6</v>
       </c>
       <c r="O39" t="n">
-        <v>3.1</v>
+        <v>2.28</v>
       </c>
       <c r="P39" t="n">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.42</v>
+        <v>4.4</v>
       </c>
       <c r="R39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V39" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AD39" t="n">
         <v>1.33</v>
       </c>
-      <c r="S39" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V39" t="n">
-        <v>7</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AE39" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.49</v>
+        <v>2.05</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46023.5</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.89</v>
+        <v>2.18</v>
       </c>
       <c r="M40" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>3.81</v>
+        <v>3.3</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46023.60416666666</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.18</v>
+        <v>1.53</v>
       </c>
       <c r="M41" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="N41" t="n">
-        <v>3.3</v>
+        <v>5.75</v>
       </c>
       <c r="O41" t="n">
-        <v>2.59</v>
+        <v>2.02</v>
       </c>
       <c r="P41" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.17</v>
+        <v>5.65</v>
       </c>
       <c r="R41" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="S41" t="n">
-        <v>2.96</v>
+        <v>3.36</v>
       </c>
       <c r="T41" t="n">
-        <v>2.89</v>
+        <v>2.43</v>
       </c>
       <c r="U41" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="V41" t="n">
-        <v>6.95</v>
+        <v>5.25</v>
       </c>
       <c r="W41" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X41" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.26</v>
+        <v>4.4</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.01</v>
+        <v>1.64</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AC41" t="n">
-        <v>3.14</v>
+        <v>2.5</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.72</v>
+        <v>2.56</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46023.60416666666</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.53</v>
+        <v>2.01</v>
       </c>
       <c r="M42" t="n">
-        <v>4.15</v>
+        <v>3.49</v>
       </c>
       <c r="N42" t="n">
-        <v>5.75</v>
+        <v>3.58</v>
       </c>
       <c r="O42" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46023.60416666666</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="M44" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N44" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="O44" t="n">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="P44" t="n">
         <v>2.2</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="R44" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="S44" t="n">
-        <v>2.98</v>
+        <v>3.16</v>
       </c>
       <c r="T44" t="n">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="U44" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="V44" t="n">
-        <v>7.3</v>
+        <v>5.6</v>
       </c>
       <c r="W44" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X44" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC44" t="n">
-        <v>3.08</v>
+        <v>2.6</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.12</v>
+        <v>2.29</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="M45" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N45" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="O45" t="n">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="P45" t="n">
         <v>2.2</v>
       </c>
       <c r="Q45" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="R45" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="S45" t="n">
-        <v>3.16</v>
+        <v>2.98</v>
       </c>
       <c r="T45" t="n">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="U45" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="V45" t="n">
-        <v>5.6</v>
+        <v>7.3</v>
       </c>
       <c r="W45" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X45" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.6</v>
+        <v>3.08</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46023.70833333334</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -897,34 +897,34 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="N4" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O4" t="n">
-        <v>2.68</v>
+        <v>2.59</v>
       </c>
       <c r="P4" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.17</v>
+        <v>4.22</v>
       </c>
       <c r="R4" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="T4" t="n">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="U4" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V4" t="n">
         <v>7.1</v>
@@ -936,25 +936,25 @@
         <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.55</v>
+        <v>3.49</v>
       </c>
       <c r="AD4" t="n">
         <v>1.28</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AF4" t="n">
         <v>1.96</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.99</v>
+        <v>2.38</v>
       </c>
       <c r="M6" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="N6" t="n">
-        <v>3.75</v>
+        <v>2.87</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.65</v>
+        <v>3.8</v>
       </c>
       <c r="M7" t="n">
         <v>3.6</v>
       </c>
       <c r="N7" t="n">
-        <v>5.08</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46023.5</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.75</v>
+        <v>2.53</v>
       </c>
       <c r="M8" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>2.67</v>
       </c>
       <c r="O8" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB8" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AC8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46023.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AA9" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46023.5</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>2.34</v>
+        <v>4.4</v>
       </c>
       <c r="O10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z10" t="n">
         <v>3.62</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V10" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AA10" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.36</v>
+        <v>1.99</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46023.5</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="N11" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9</v>
+        <v>2.48</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.81</v>
+        <v>4.74</v>
       </c>
       <c r="R11" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="S11" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T11" t="n">
         <v>2.65</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U11" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="V11" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="AA11" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.94</v>
       </c>
-      <c r="AB11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.56</v>
+        <v>1.89</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46023.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.44</v>
+        <v>2.04</v>
       </c>
       <c r="M12" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>6.6</v>
+        <v>3.45</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>3.46</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>3.19</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.55</v>
+        <v>3.45</v>
       </c>
       <c r="M14" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46023.5</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.29</v>
+        <v>1.6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N15" t="n">
-        <v>2.14</v>
+        <v>5.33</v>
       </c>
       <c r="O15" t="n">
-        <v>3.55</v>
+        <v>2.12</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.72</v>
+        <v>5.49</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>2.77</v>
+        <v>2.99</v>
       </c>
       <c r="T15" t="n">
-        <v>2.81</v>
+        <v>2.55</v>
       </c>
       <c r="U15" t="n">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="V15" t="n">
-        <v>7.2</v>
+        <v>5.55</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.2</v>
+        <v>4.07</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.28</v>
+        <v>2.67</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.3</v>
+        <v>2.27</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46023.5</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.7</v>
+        <v>1.48</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="N16" t="n">
-        <v>2.45</v>
+        <v>6.6</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB16" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q16" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V16" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2</v>
-      </c>
       <c r="AC16" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46023.5</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.64</v>
+        <v>2.47</v>
       </c>
       <c r="M17" t="n">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>5</v>
+        <v>2.82</v>
       </c>
       <c r="O17" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.86</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46023.5</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.57</v>
+        <v>3</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>2.38</v>
       </c>
       <c r="O18" t="n">
-        <v>2.11</v>
+        <v>3.61</v>
       </c>
       <c r="P18" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.49</v>
+        <v>2.98</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>2.99</v>
+        <v>2.73</v>
       </c>
       <c r="T18" t="n">
-        <v>2.47</v>
+        <v>2.81</v>
       </c>
       <c r="U18" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="V18" t="n">
-        <v>5.55</v>
+        <v>6.25</v>
       </c>
       <c r="W18" t="n">
         <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.74</v>
+        <v>3.51</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.66</v>
+        <v>3.23</v>
       </c>
       <c r="AD18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.37</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>2.27</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46023.5</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="M19" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="O19" t="n">
-        <v>4.1</v>
+        <v>4.96</v>
       </c>
       <c r="P19" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S19" t="n">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="T19" t="n">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="U19" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="W19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X19" t="n">
         <v>1.03</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.15</v>
+        <v>3.61</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.07</v>
+        <v>1.88</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.44</v>
+        <v>3.13</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46023.5</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>3.81</v>
+        <v>2.84</v>
       </c>
       <c r="O20" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
         <v>1.95</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46023.5</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.4</v>
+        <v>3.62</v>
       </c>
       <c r="M21" t="n">
         <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>3.05</v>
+        <v>2.05</v>
       </c>
       <c r="O21" t="n">
-        <v>2.75</v>
+        <v>4.08</v>
       </c>
       <c r="P21" t="n">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.5</v>
+        <v>2.76</v>
       </c>
       <c r="R21" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="T21" t="n">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="U21" t="n">
         <v>1.34</v>
       </c>
       <c r="V21" t="n">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W21" t="n">
         <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AG21" t="n">
         <v>1.29</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.6</v>
+        <v>1.26</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46023.5</v>
@@ -3039,22 +3039,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
         <v>2.03</v>
       </c>
       <c r="O22" t="n">
-        <v>3.85</v>
+        <v>4.05</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="R22" t="n">
         <v>1.38</v>
@@ -3063,10 +3063,10 @@
         <v>2.81</v>
       </c>
       <c r="T22" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="U22" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="V22" t="n">
         <v>6</v>
@@ -3078,22 +3078,22 @@
         <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.3</v>
+        <v>3.74</v>
       </c>
       <c r="AA22" t="n">
         <v>1.88</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE22" t="n">
         <v>1.7</v>
@@ -3105,7 +3105,7 @@
         <v>1.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46023.5</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46023.5</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.68</v>
+        <v>2.4</v>
       </c>
       <c r="M24" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="O24" t="n">
-        <v>4.6</v>
+        <v>3.03</v>
       </c>
       <c r="P24" t="n">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.73</v>
+        <v>3.62</v>
       </c>
       <c r="R24" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="T24" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="U24" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="V24" t="n">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="W24" t="n">
         <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.38</v>
       </c>
-      <c r="Z24" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46023.5</v>
@@ -3399,7 +3399,7 @@
         <v>2.55</v>
       </c>
       <c r="M25" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="N25" t="n">
         <v>2.7</v>
@@ -3408,19 +3408,19 @@
         <v>3.2</v>
       </c>
       <c r="P25" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.2</v>
+        <v>3.37</v>
       </c>
       <c r="R25" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="T25" t="n">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="U25" t="n">
         <v>1.36</v>
@@ -3438,22 +3438,22 @@
         <v>1.27</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.15</v>
+        <v>3.27</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB25" t="n">
         <v>1.78</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AF25" t="n">
         <v>1.94</v>
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="M26" t="n">
         <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
       <c r="N27" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O27" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="P27" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.84</v>
+        <v>4.56</v>
       </c>
       <c r="R27" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S27" t="n">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="T27" t="n">
-        <v>2.65</v>
+        <v>3.07</v>
       </c>
       <c r="U27" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="V27" t="n">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="W27" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.2</v>
+        <v>3.69</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE27" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.76</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.81</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46023.5</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.37</v>
+        <v>1.53</v>
       </c>
       <c r="M28" t="n">
-        <v>2.95</v>
+        <v>4.2</v>
       </c>
       <c r="N28" t="n">
-        <v>3.25</v>
+        <v>5.75</v>
       </c>
       <c r="O28" t="n">
-        <v>3.08</v>
+        <v>2.11</v>
       </c>
       <c r="P28" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V28" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF28" t="n">
         <v>1.86</v>
       </c>
-      <c r="Q28" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="U28" t="n">
+      <c r="AG28" t="n">
         <v>1.23</v>
       </c>
-      <c r="V28" t="n">
-        <v>11</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH28" t="n">
-        <v>1.54</v>
+        <v>2.4</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46023.5</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,28 +3872,28 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="M29" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="N29" t="n">
-        <v>1.93</v>
+        <v>4.29</v>
       </c>
       <c r="O29" t="n">
-        <v>4.28</v>
+        <v>2.25</v>
       </c>
       <c r="P29" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.52</v>
+        <v>5.71</v>
       </c>
       <c r="R29" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S29" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="T29" t="n">
         <v>2.62</v>
@@ -3902,43 +3902,43 @@
         <v>1.42</v>
       </c>
       <c r="V29" t="n">
-        <v>6.55</v>
+        <v>6.3</v>
       </c>
       <c r="W29" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X29" t="n">
         <v>1.05</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG29" t="n">
         <v>1.21</v>
       </c>
-      <c r="Z29" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH29" t="n">
-        <v>1.25</v>
+        <v>2.16</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46023.5</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.31</v>
+        <v>2.7</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46023.5</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.85</v>
+        <v>2.37</v>
       </c>
       <c r="M31" t="n">
-        <v>3.8</v>
+        <v>2.98</v>
       </c>
       <c r="N31" t="n">
-        <v>3.88</v>
+        <v>3.25</v>
       </c>
       <c r="O31" t="n">
-        <v>2.37</v>
+        <v>3.11</v>
       </c>
       <c r="P31" t="n">
-        <v>2.24</v>
+        <v>1.86</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.42</v>
+        <v>4.2</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="S31" t="n">
-        <v>3.22</v>
+        <v>2.45</v>
       </c>
       <c r="T31" t="n">
-        <v>2.47</v>
+        <v>3.52</v>
       </c>
       <c r="U31" t="n">
-        <v>1.49</v>
+        <v>1.26</v>
       </c>
       <c r="V31" t="n">
-        <v>5.95</v>
+        <v>11</v>
       </c>
       <c r="W31" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X31" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>4.25</v>
+        <v>2.64</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.73</v>
+        <v>2.58</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.13</v>
+        <v>1.52</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.6</v>
+        <v>5.04</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.61</v>
+        <v>2.11</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.18</v>
+        <v>1.65</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.92</v>
+        <v>1.54</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46023.5</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.5</v>
+        <v>3.22</v>
       </c>
       <c r="M32" t="n">
-        <v>3.22</v>
+        <v>3.27</v>
       </c>
       <c r="N32" t="n">
-        <v>2.87</v>
+        <v>2.11</v>
       </c>
       <c r="O32" t="n">
-        <v>3.1</v>
+        <v>4.54</v>
       </c>
       <c r="P32" t="n">
         <v>2.04</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.44</v>
+        <v>2.6</v>
       </c>
       <c r="R32" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="S32" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="T32" t="n">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="U32" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="V32" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="W32" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG32" t="n">
         <v>1.26</v>
       </c>
-      <c r="Z32" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH32" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46023.5</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="M33" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="N33" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="O33" t="n">
-        <v>2.11</v>
+        <v>2.35</v>
       </c>
       <c r="P33" t="n">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="Q33" t="n">
-        <v>6.04</v>
+        <v>4.85</v>
       </c>
       <c r="R33" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S33" t="n">
-        <v>2.89</v>
+        <v>3.03</v>
       </c>
       <c r="T33" t="n">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="U33" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="V33" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="W33" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X33" t="n">
         <v>1.06</v>
       </c>
-      <c r="X33" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y33" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="AB33" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AC33" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AD33" t="n">
         <v>1.33</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46023.5</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="M34" t="n">
-        <v>3.45</v>
+        <v>3.08</v>
       </c>
       <c r="N34" t="n">
         <v>2.7</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.05</v>
+        <v>3.05</v>
       </c>
       <c r="M35" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="N35" t="n">
-        <v>3.75</v>
+        <v>2.38</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46023.5</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.9</v>
+        <v>2.33</v>
       </c>
       <c r="M36" t="n">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="N36" t="n">
-        <v>2.38</v>
+        <v>2.98</v>
       </c>
       <c r="O36" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AC36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46023.5</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4.33</v>
+        <v>1.67</v>
       </c>
       <c r="M37" t="n">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="N37" t="n">
-        <v>1.8</v>
+        <v>4.35</v>
       </c>
       <c r="O37" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46023.5</v>
@@ -4943,40 +4943,40 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M38" t="n">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="N38" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="O38" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="P38" t="n">
-        <v>2.34</v>
+        <v>2.69</v>
       </c>
       <c r="Q38" t="n">
-        <v>8.25</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="R38" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S38" t="n">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="T38" t="n">
-        <v>2.59</v>
+        <v>2.46</v>
       </c>
       <c r="U38" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="V38" t="n">
-        <v>6.05</v>
+        <v>5.85</v>
       </c>
       <c r="W38" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X38" t="n">
         <v>1.02</v>
@@ -4985,31 +4985,31 @@
         <v>1.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.72</v>
+        <v>4.3</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.03</v>
+        <v>2.21</v>
       </c>
       <c r="AC38" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AE38" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AG38" t="n">
         <v>1.16</v>
       </c>
       <c r="AH38" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46023.5</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="M39" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="N39" t="n">
-        <v>4.6</v>
+        <v>3.36</v>
       </c>
       <c r="O39" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="P39" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.4</v>
+        <v>4.42</v>
       </c>
       <c r="R39" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S39" t="n">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="T39" t="n">
         <v>2.73</v>
       </c>
       <c r="U39" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V39" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="W39" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X39" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="AA39" t="n">
         <v>1.85</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.99</v>
+        <v>3.07</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46023.5</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N40" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="O40" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46023.60416666666</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="M42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O42" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V42" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AA42" t="n">
         <v>2.01</v>
       </c>
-      <c r="M42" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="N42" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AB42" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46023.60416666666</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O7" t="n">
         <v>3.8</v>
       </c>
-      <c r="M7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2</v>
-      </c>
-      <c r="O7" t="n">
-        <v>4.29</v>
-      </c>
       <c r="P7" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA7" t="n">
         <v>2.12</v>
       </c>
-      <c r="Q7" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V7" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AA7" t="n">
+      <c r="AB7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.9</v>
       </c>
-      <c r="AB7" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AG7" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46023.5</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.53</v>
+        <v>1.74</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="N8" t="n">
-        <v>2.67</v>
+        <v>5</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46023.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
-        <v>3.05</v>
+        <v>3.11</v>
       </c>
       <c r="P9" t="n">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.58</v>
+        <v>4.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.39</v>
+        <v>1.54</v>
       </c>
       <c r="S9" t="n">
-        <v>2.81</v>
+        <v>2.45</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>3.52</v>
       </c>
       <c r="U9" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="V9" t="n">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.22</v>
+        <v>2.64</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.05</v>
+        <v>2.58</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.56</v>
+        <v>5.04</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.74</v>
+        <v>2.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46023.5</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N10" t="n">
-        <v>4.4</v>
+        <v>2.38</v>
       </c>
       <c r="O10" t="n">
-        <v>2.28</v>
+        <v>3.34</v>
       </c>
       <c r="P10" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.01</v>
+        <v>2.98</v>
       </c>
       <c r="R10" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S10" t="n">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="T10" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U10" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="V10" t="n">
-        <v>6</v>
+        <v>6.15</v>
       </c>
       <c r="W10" t="n">
         <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z10" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH10" t="n">
-        <v>1.99</v>
+        <v>1.41</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46023.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="M11" t="n">
-        <v>3.48</v>
+        <v>3.68</v>
       </c>
       <c r="N11" t="n">
-        <v>4.2</v>
+        <v>4.29</v>
       </c>
       <c r="O11" t="n">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="P11" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.74</v>
+        <v>5.71</v>
       </c>
       <c r="R11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="T11" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>7.1</v>
+        <v>6.3</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.4</v>
+        <v>3.61</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.38</v>
+        <v>3.02</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE11" t="n">
         <v>1.81</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.89</v>
+        <v>2.16</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46023.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>3.46</v>
       </c>
       <c r="N12" t="n">
-        <v>3.45</v>
+        <v>3.19</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.12</v>
+        <v>3.45</v>
       </c>
       <c r="M13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z13" t="n">
         <v>3.46</v>
       </c>
-      <c r="N13" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
       <c r="AA13" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46023.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.45</v>
+        <v>2.62</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.1</v>
+        <v>2.47</v>
       </c>
       <c r="O14" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46023.5</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="M16" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>6.6</v>
+        <v>3.45</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.47</v>
+        <v>1.87</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="N17" t="n">
-        <v>2.82</v>
+        <v>4.2</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46023.5</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="M18" t="n">
         <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>2.38</v>
+        <v>2.9</v>
       </c>
       <c r="O18" t="n">
-        <v>3.61</v>
+        <v>3.03</v>
       </c>
       <c r="P18" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.98</v>
+        <v>3.62</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="T18" t="n">
-        <v>2.81</v>
+        <v>2.99</v>
       </c>
       <c r="U18" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="V18" t="n">
-        <v>6.25</v>
+        <v>7.8</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.51</v>
+        <v>3.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.23</v>
+        <v>3.59</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46023.5</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>1.8</v>
+        <v>2.84</v>
       </c>
       <c r="O19" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46023.5</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N20" t="n">
-        <v>2.84</v>
+        <v>5.75</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46023.5</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.62</v>
+        <v>2.65</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="N21" t="n">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="O21" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46023.5</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.5</v>
+        <v>2.55</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="N22" t="n">
-        <v>2.03</v>
+        <v>2.7</v>
       </c>
       <c r="O22" t="n">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.61</v>
+        <v>3.37</v>
       </c>
       <c r="R22" t="n">
         <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="T22" t="n">
-        <v>2.77</v>
+        <v>2.93</v>
       </c>
       <c r="U22" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="V22" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.74</v>
+        <v>3.27</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.24</v>
+        <v>3.42</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46023.5</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.49</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="O23" t="n">
-        <v>3.1</v>
+        <v>2.44</v>
       </c>
       <c r="P23" t="n">
-        <v>2.03</v>
+        <v>2.18</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.46</v>
+        <v>4.42</v>
       </c>
       <c r="R23" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>2.94</v>
+        <v>3.04</v>
       </c>
       <c r="T23" t="n">
-        <v>2.87</v>
+        <v>2.73</v>
       </c>
       <c r="U23" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="V23" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.46</v>
+        <v>3.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.34</v>
+        <v>3.07</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46023.5</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.4</v>
+        <v>1.48</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="N24" t="n">
-        <v>2.9</v>
+        <v>6.6</v>
       </c>
       <c r="O24" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46023.5</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="M25" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="O25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46023.5</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="T26" t="n">
         <v>2.62</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AB26" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE26" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46023.5</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.93</v>
+        <v>3.8</v>
       </c>
       <c r="M27" t="n">
-        <v>3.27</v>
+        <v>3.6</v>
       </c>
       <c r="N27" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="O27" t="n">
-        <v>2.48</v>
+        <v>4.29</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.56</v>
+        <v>2.53</v>
       </c>
       <c r="R27" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="S27" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="T27" t="n">
-        <v>3.07</v>
+        <v>2.86</v>
       </c>
       <c r="U27" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="V27" t="n">
-        <v>7.9</v>
+        <v>6.65</v>
       </c>
       <c r="W27" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X27" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD27" t="n">
         <v>1.34</v>
       </c>
-      <c r="Z27" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE27" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.76</v>
+        <v>1.26</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46023.5</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,61 +3753,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.53</v>
+        <v>3.62</v>
       </c>
       <c r="M28" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>5.75</v>
+        <v>2.05</v>
       </c>
       <c r="O28" t="n">
-        <v>2.11</v>
+        <v>4.08</v>
       </c>
       <c r="P28" t="n">
-        <v>2.19</v>
+        <v>1.96</v>
       </c>
       <c r="Q28" t="n">
-        <v>6.04</v>
+        <v>2.76</v>
       </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>2.89</v>
+        <v>2.77</v>
       </c>
       <c r="T28" t="n">
-        <v>2.73</v>
+        <v>3.04</v>
       </c>
       <c r="U28" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="V28" t="n">
-        <v>6.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W28" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.26</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.35</v>
       </c>
       <c r="AE28" t="n">
         <v>1.84</v>
@@ -3816,10 +3816,10 @@
         <v>1.86</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.4</v>
+        <v>1.26</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46023.5</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.7</v>
+        <v>2.53</v>
       </c>
       <c r="M29" t="n">
-        <v>3.68</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>4.29</v>
+        <v>2.67</v>
       </c>
       <c r="O29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.71</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46023.5</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="M30" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="O30" t="n">
-        <v>3.34</v>
+        <v>4.96</v>
       </c>
       <c r="P30" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.98</v>
+        <v>2.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="S30" t="n">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="T30" t="n">
-        <v>2.59</v>
+        <v>2.77</v>
       </c>
       <c r="U30" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="V30" t="n">
-        <v>6.15</v>
+        <v>6.25</v>
       </c>
       <c r="W30" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.77</v>
+        <v>3.61</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.91</v>
+        <v>3.13</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46023.5</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.37</v>
+        <v>1.33</v>
       </c>
       <c r="M31" t="n">
-        <v>2.98</v>
+        <v>4.85</v>
       </c>
       <c r="N31" t="n">
-        <v>3.25</v>
+        <v>9.1</v>
       </c>
       <c r="O31" t="n">
-        <v>3.11</v>
+        <v>1.71</v>
       </c>
       <c r="P31" t="n">
-        <v>1.86</v>
+        <v>2.69</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.2</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="R31" t="n">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="S31" t="n">
-        <v>2.45</v>
+        <v>3.04</v>
       </c>
       <c r="T31" t="n">
-        <v>3.52</v>
+        <v>2.46</v>
       </c>
       <c r="U31" t="n">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="V31" t="n">
-        <v>11</v>
+        <v>5.85</v>
       </c>
       <c r="W31" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X31" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.64</v>
+        <v>4.3</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.58</v>
+        <v>1.66</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.52</v>
+        <v>2.21</v>
       </c>
       <c r="AC31" t="n">
-        <v>5.04</v>
+        <v>2.63</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.17</v>
+        <v>1.46</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.54</v>
+        <v>3.5</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46023.5</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="M33" t="n">
-        <v>3.7</v>
+        <v>3.27</v>
       </c>
       <c r="N33" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="O33" t="n">
-        <v>2.35</v>
+        <v>2.48</v>
       </c>
       <c r="P33" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.85</v>
+        <v>4.56</v>
       </c>
       <c r="R33" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S33" t="n">
-        <v>3.03</v>
+        <v>2.65</v>
       </c>
       <c r="T33" t="n">
-        <v>2.79</v>
+        <v>3.07</v>
       </c>
       <c r="U33" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V33" t="n">
-        <v>6.5</v>
+        <v>7.9</v>
       </c>
       <c r="W33" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X33" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.56</v>
+        <v>3.1</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.18</v>
+        <v>3.69</v>
       </c>
       <c r="AD33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG33" t="n">
         <v>1.33</v>
       </c>
-      <c r="AE33" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH33" t="n">
-        <v>2.03</v>
+        <v>1.76</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46023.5</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="M34" t="n">
-        <v>3.08</v>
+        <v>3.38</v>
       </c>
       <c r="N34" t="n">
-        <v>2.7</v>
+        <v>2.98</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.05</v>
+        <v>2.49</v>
       </c>
       <c r="M35" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="N35" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="O35" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="P35" t="n">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.01</v>
+        <v>3.46</v>
       </c>
       <c r="R35" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="S35" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="T35" t="n">
-        <v>3.09</v>
+        <v>2.87</v>
       </c>
       <c r="U35" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="V35" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X35" t="n">
         <v>1.03</v>
       </c>
-      <c r="X35" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y35" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.14</v>
+        <v>3.46</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.74</v>
+        <v>3.34</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46023.5</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.33</v>
+        <v>1.67</v>
       </c>
       <c r="M36" t="n">
-        <v>3.38</v>
+        <v>3.74</v>
       </c>
       <c r="N36" t="n">
-        <v>2.98</v>
+        <v>4.35</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.67</v>
+        <v>3.5</v>
       </c>
       <c r="M37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="O37" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V37" t="n">
+        <v>6</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z37" t="n">
         <v>3.74</v>
       </c>
-      <c r="N37" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
       <c r="AA37" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46023.5</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>3</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V38" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AG38" t="n">
         <v>1.33</v>
       </c>
-      <c r="M38" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="N38" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>8.529999999999999</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V38" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AH38" t="n">
-        <v>3.5</v>
+        <v>1.37</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46023.5</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="M39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q39" t="n">
         <v>3.58</v>
       </c>
-      <c r="N39" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="O39" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>4.42</v>
-      </c>
       <c r="R39" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V39" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AG39" t="n">
         <v>1.33</v>
       </c>
-      <c r="S39" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V39" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH39" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46023.5</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="M44" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N44" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="O44" t="n">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="P44" t="n">
         <v>2.2</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="R44" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="S44" t="n">
-        <v>3.16</v>
+        <v>2.98</v>
       </c>
       <c r="T44" t="n">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="U44" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="V44" t="n">
-        <v>5.6</v>
+        <v>7.3</v>
       </c>
       <c r="W44" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X44" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.6</v>
+        <v>3.08</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46023.70833333334</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="M45" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N45" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="O45" t="n">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="P45" t="n">
         <v>2.2</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="R45" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="S45" t="n">
-        <v>2.98</v>
+        <v>3.16</v>
       </c>
       <c r="T45" t="n">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="U45" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="V45" t="n">
-        <v>7.3</v>
+        <v>5.6</v>
       </c>
       <c r="W45" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X45" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.08</v>
+        <v>2.6</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.12</v>
+        <v>2.29</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46023.70833333334</v>

--- a/jogos_2026-01-01.xlsx
+++ b/jogos_2026-01-01.xlsx
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="M2" t="n">
         <v>4.3</v>
       </c>
       <c r="N2" t="n">
-        <v>4.1</v>
+        <v>4.52</v>
       </c>
       <c r="O2" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="P2" t="n">
-        <v>2.51</v>
+        <v>2.43</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="R2" t="n">
         <v>1.21</v>
@@ -683,10 +683,10 @@
         <v>3.75</v>
       </c>
       <c r="T2" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V2" t="n">
         <v>4.35</v>
@@ -701,31 +701,31 @@
         <v>1.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.65</v>
+        <v>6.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="AC2" t="n">
         <v>2.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AE2" t="n">
         <v>1.44</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="AG2" t="n">
         <v>1.24</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46023.04166666666</v>
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="M3" t="n">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="N3" t="n">
-        <v>3.97</v>
+        <v>3.92</v>
       </c>
       <c r="O3" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="P3" t="n">
         <v>2.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="R3" t="n">
         <v>1.28</v>
@@ -820,7 +820,7 @@
         <v>1.16</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="AA3" t="n">
         <v>1.66</v>
@@ -829,7 +829,7 @@
         <v>2.26</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AD3" t="n">
         <v>1.44</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="M4" t="n">
-        <v>3.37</v>
+        <v>3.32</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="O4" t="n">
         <v>2.59</v>
@@ -942,7 +942,7 @@
         <v>3.29</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
         <v>1.79</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.38</v>
+        <v>2.84</v>
       </c>
       <c r="M6" t="n">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="N6" t="n">
-        <v>2.87</v>
+        <v>2.23</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46023.5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O7" t="n">
         <v>3.05</v>
       </c>
-      <c r="M7" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="O7" t="n">
-        <v>3.8</v>
-      </c>
       <c r="P7" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.01</v>
+        <v>3.58</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>2.76</v>
+        <v>2.81</v>
       </c>
       <c r="T7" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W7" t="n">
         <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.14</v>
+        <v>3.22</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.74</v>
+        <v>3.56</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AG7" t="n">
         <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46023.5</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.74</v>
+        <v>2.41</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7</v>
+        <v>3.18</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>2.56</v>
       </c>
       <c r="O8" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46023.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="N9" t="n">
         <v>2.37</v>
       </c>
-      <c r="M9" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.25</v>
-      </c>
       <c r="O9" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.58</v>
+        <v>1.96</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.52</v>
+        <v>1.74</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46023.5</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.7</v>
+        <v>3.93</v>
       </c>
       <c r="M10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC10" t="n">
         <v>3.45</v>
       </c>
-      <c r="N10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V10" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y10" t="n">
+      <c r="AD10" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z10" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AE10" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46023.5</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,28 +1730,28 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="M11" t="n">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="N11" t="n">
-        <v>4.29</v>
+        <v>4.3</v>
       </c>
       <c r="O11" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="P11" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.71</v>
+        <v>5.01</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S11" t="n">
-        <v>2.85</v>
+        <v>3.07</v>
       </c>
       <c r="T11" t="n">
         <v>2.62</v>
@@ -1760,43 +1760,43 @@
         <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="W11" t="n">
         <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z11" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH11" t="n">
-        <v>2.16</v>
+        <v>1.99</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46023.5</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="P12" t="n">
         <v>2.12</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46023.5</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.45</v>
+        <v>2.27</v>
       </c>
       <c r="M13" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z13" t="n">
         <v>3.2</v>
       </c>
-      <c r="N13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.46</v>
-      </c>
       <c r="AA13" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.46</v>
+        <v>3.59</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AF13" t="n">
         <v>1.95</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.29</v>
+        <v>1.52</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46023.5</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.62</v>
+        <v>3.39</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="N14" t="n">
-        <v>2.47</v>
+        <v>1.94</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46023.5</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.6</v>
+        <v>2.28</v>
       </c>
       <c r="M15" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q15" t="n">
         <v>4.2</v>
       </c>
-      <c r="N15" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>5.49</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="S15" t="n">
-        <v>2.99</v>
+        <v>2.45</v>
       </c>
       <c r="T15" t="n">
-        <v>2.55</v>
+        <v>3.52</v>
       </c>
       <c r="U15" t="n">
-        <v>1.51</v>
+        <v>1.26</v>
       </c>
       <c r="V15" t="n">
-        <v>5.55</v>
+        <v>11</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.07</v>
+        <v>2.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.68</v>
+        <v>2.52</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.12</v>
+        <v>1.46</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.67</v>
+        <v>5.04</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.43</v>
+        <v>1.17</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.7</v>
+        <v>2.11</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.97</v>
+        <v>1.65</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.27</v>
+        <v>1.54</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46023.5</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="N16" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.35</v>
+        <v>1.88</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.87</v>
+        <v>2.58</v>
       </c>
       <c r="M17" t="n">
-        <v>3.48</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>4.2</v>
+        <v>2.41</v>
       </c>
       <c r="O17" t="n">
-        <v>2.48</v>
+        <v>3.34</v>
       </c>
       <c r="P17" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.74</v>
+        <v>2.98</v>
       </c>
       <c r="R17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V17" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.37</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U17" t="n">
+      <c r="AE17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.41</v>
-      </c>
-      <c r="V17" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.89</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46023.5</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="O18" t="n">
-        <v>3.03</v>
+        <v>2.25</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.62</v>
+        <v>5.71</v>
       </c>
       <c r="R18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U18" t="n">
         <v>1.42</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.34</v>
-      </c>
       <c r="V18" t="n">
-        <v>7.8</v>
+        <v>6.3</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.2</v>
+        <v>3.61</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.59</v>
+        <v>3.02</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.52</v>
+        <v>2.16</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46023.5</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.3</v>
+        <v>3.47</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="N19" t="n">
-        <v>2.84</v>
+        <v>1.98</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46023.5</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,40 +2801,40 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="M20" t="n">
-        <v>4.2</v>
+        <v>3.34</v>
       </c>
       <c r="N20" t="n">
-        <v>5.75</v>
+        <v>3.87</v>
       </c>
       <c r="O20" t="n">
-        <v>2.11</v>
+        <v>2.48</v>
       </c>
       <c r="P20" t="n">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.04</v>
+        <v>4.74</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S20" t="n">
         <v>2.89</v>
       </c>
       <c r="T20" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="U20" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="V20" t="n">
-        <v>6.25</v>
+        <v>7.1</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X20" t="n">
         <v>1.01</v>
@@ -2843,31 +2843,31 @@
         <v>1.26</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="AA20" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AB20" t="n">
         <v>1.84</v>
       </c>
-      <c r="AB20" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AC20" t="n">
-        <v>3.09</v>
+        <v>3.38</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.4</v>
+        <v>1.89</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46023.5</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.65</v>
+        <v>1.95</v>
       </c>
       <c r="M21" t="n">
-        <v>3.08</v>
+        <v>2.99</v>
       </c>
       <c r="N21" t="n">
-        <v>2.7</v>
+        <v>3.65</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="M22" t="n">
-        <v>3.24</v>
+        <v>3.13</v>
       </c>
       <c r="N22" t="n">
-        <v>2.7</v>
+        <v>3.66</v>
       </c>
       <c r="O22" t="n">
-        <v>3.2</v>
+        <v>2.48</v>
       </c>
       <c r="P22" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.37</v>
+        <v>4.56</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S22" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="T22" t="n">
-        <v>2.93</v>
+        <v>3.07</v>
       </c>
       <c r="U22" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V22" t="n">
-        <v>7.4</v>
+        <v>7.9</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.27</v>
+        <v>3.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.42</v>
+        <v>3.69</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.46</v>
+        <v>1.76</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46023.5</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>2.47</v>
       </c>
       <c r="M23" t="n">
-        <v>3.58</v>
+        <v>3.08</v>
       </c>
       <c r="N23" t="n">
-        <v>3.36</v>
+        <v>2.56</v>
       </c>
       <c r="O23" t="n">
-        <v>2.44</v>
+        <v>3.2</v>
       </c>
       <c r="P23" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.42</v>
+        <v>3.37</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
-        <v>3.04</v>
+        <v>2.85</v>
       </c>
       <c r="T23" t="n">
-        <v>2.73</v>
+        <v>2.93</v>
       </c>
       <c r="U23" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="V23" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.7</v>
+        <v>3.27</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.07</v>
+        <v>3.42</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.14</v>
+        <v>1.94</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.87</v>
+        <v>1.46</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46023.5</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="M24" t="n">
-        <v>4.5</v>
+        <v>3.87</v>
       </c>
       <c r="N24" t="n">
-        <v>6.6</v>
+        <v>4.75</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>5.49</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="AA24" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1.7</v>
       </c>
-      <c r="AB24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0</v>
-      </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46023.5</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.47</v>
+        <v>1.83</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>3.68</v>
       </c>
       <c r="N25" t="n">
-        <v>2.82</v>
+        <v>3.99</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46023.5</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.75</v>
+        <v>2.89</v>
       </c>
       <c r="M26" t="n">
-        <v>3.6</v>
+        <v>3.23</v>
       </c>
       <c r="N26" t="n">
-        <v>4.4</v>
+        <v>2.41</v>
       </c>
       <c r="O26" t="n">
-        <v>2.28</v>
+        <v>3.8</v>
       </c>
       <c r="P26" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.01</v>
+        <v>3.01</v>
       </c>
       <c r="R26" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>3.07</v>
+        <v>2.76</v>
       </c>
       <c r="T26" t="n">
-        <v>2.62</v>
+        <v>3.09</v>
       </c>
       <c r="U26" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="V26" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.62</v>
+        <v>3.14</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.26</v>
+        <v>3.74</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.99</v>
+        <v>1.36</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46023.5</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.8</v>
+        <v>1.68</v>
       </c>
       <c r="M27" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="N27" t="n">
-        <v>2</v>
+        <v>5.1</v>
       </c>
       <c r="O27" t="n">
-        <v>4.29</v>
+        <v>2.35</v>
       </c>
       <c r="P27" t="n">
-        <v>2.12</v>
+        <v>2.29</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.53</v>
+        <v>4.85</v>
       </c>
       <c r="R27" t="n">
         <v>1.35</v>
       </c>
       <c r="S27" t="n">
-        <v>2.9</v>
+        <v>3.03</v>
       </c>
       <c r="T27" t="n">
-        <v>2.86</v>
+        <v>2.79</v>
       </c>
       <c r="U27" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>6.65</v>
+        <v>6.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X27" t="n">
         <v>1.06</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AB27" t="n">
         <v>1.87</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AG27" t="n">
         <v>1.27</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.26</v>
+        <v>2.03</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46023.5</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.62</v>
+        <v>1.35</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="N28" t="n">
-        <v>2.05</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O28" t="n">
-        <v>4.08</v>
+        <v>1.71</v>
       </c>
       <c r="P28" t="n">
-        <v>1.96</v>
+        <v>2.69</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.76</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S28" t="n">
-        <v>2.77</v>
+        <v>3.04</v>
       </c>
       <c r="T28" t="n">
-        <v>3.04</v>
+        <v>2.46</v>
       </c>
       <c r="U28" t="n">
-        <v>1.34</v>
+        <v>1.51</v>
       </c>
       <c r="V28" t="n">
-        <v>8.199999999999999</v>
+        <v>5.85</v>
       </c>
       <c r="W28" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X28" t="n">
         <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.14</v>
+        <v>4.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.07</v>
+        <v>1.79</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.64</v>
+        <v>3.05</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.86</v>
+        <v>1.69</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.26</v>
+        <v>3.5</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46023.5</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.53</v>
+        <v>4.2</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N29" t="n">
-        <v>2.67</v>
+        <v>1.81</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46023.5</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.2</v>
+        <v>1.54</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>3.83</v>
       </c>
       <c r="N30" t="n">
-        <v>1.8</v>
+        <v>6.3</v>
       </c>
       <c r="O30" t="n">
-        <v>4.96</v>
+        <v>2.11</v>
       </c>
       <c r="P30" t="n">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.5</v>
+        <v>6.04</v>
       </c>
       <c r="R30" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="T30" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="U30" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V30" t="n">
         <v>6.25</v>
       </c>
       <c r="W30" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.61</v>
+        <v>3.65</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.13</v>
+        <v>3.09</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AF30" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46023.5</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="M31" t="n">
-        <v>4.85</v>
+        <v>3.91</v>
       </c>
       <c r="N31" t="n">
-        <v>9.1</v>
+        <v>5.5</v>
       </c>
       <c r="O31" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>8.529999999999999</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46023.5</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.22</v>
+        <v>2.97</v>
       </c>
       <c r="M32" t="n">
-        <v>3.27</v>
+        <v>3.15</v>
       </c>
       <c r="N32" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="O32" t="n">
-        <v>4.54</v>
+        <v>4.05</v>
       </c>
       <c r="P32" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="R32" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S32" t="n">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="T32" t="n">
-        <v>2.99</v>
+        <v>2.81</v>
       </c>
       <c r="U32" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="V32" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="W32" t="n">
         <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.03</v>
+        <v>3.46</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46023.5</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.93</v>
+        <v>2.48</v>
       </c>
       <c r="M33" t="n">
-        <v>3.27</v>
+        <v>3.1</v>
       </c>
       <c r="N33" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="O33" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46023.5</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="M34" t="n">
-        <v>3.38</v>
+        <v>3.23</v>
       </c>
       <c r="N34" t="n">
-        <v>2.98</v>
+        <v>3.03</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AA34" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46023.5</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-      